--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>INDOCO.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>263.0199890136719</v>
+      </c>
+      <c r="D272" t="n">
+        <v>263.0199890136719</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9654140472412109</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>175.9199981689453</v>
+      </c>
+      <c r="D273" t="n">
+        <v>175.9199981689453</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9522957801818848</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>MUKKA.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>32.16999816894531</v>
+      </c>
+      <c r="D274" t="n">
+        <v>32.16999816894531</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9416624903678894</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>207.6799926757812</v>
+      </c>
+      <c r="D275" t="n">
+        <v>207.6799926757812</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.8184664249420166</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>BODALCHEM.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>172.3999938964844</v>
+      </c>
+      <c r="D276" t="n">
+        <v>172.3999938964844</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.8150469064712524</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>AIROLAM.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="D277" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.7319454550743103</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>IFBIND.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>1300.099975585938</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1300.099975585938</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.7180214524269104</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SIKKO.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>5.829999923706055</v>
+      </c>
+      <c r="D279" t="n">
+        <v>5.829999923706055</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.715453028678894</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>GARFIBRES.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>795.7000122070312</v>
+      </c>
+      <c r="D280" t="n">
+        <v>795.7000122070312</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.6256636381149292</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>KIRLOSBROS.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>1784</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1784</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.6253299713134766</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,396 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>INDOCO.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>263.0199890136719</v>
-      </c>
-      <c r="D272" t="n">
-        <v>263.0199890136719</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9654140472412109</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>KRONOX.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>175.9199981689453</v>
-      </c>
-      <c r="D273" t="n">
-        <v>175.9199981689453</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9522957801818848</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>MUKKA.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>32.16999816894531</v>
-      </c>
-      <c r="D274" t="n">
-        <v>32.16999816894531</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9416624903678894</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>WELSPUNLIV.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>207.6799926757812</v>
-      </c>
-      <c r="D275" t="n">
-        <v>207.6799926757812</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.8184664249420166</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>BODALCHEM.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>172.3999938964844</v>
-      </c>
-      <c r="D276" t="n">
-        <v>172.3999938964844</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.8150469064712524</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>AIROLAM.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>84.25</v>
-      </c>
-      <c r="D277" t="n">
-        <v>84.25</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.7319454550743103</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>IFBIND.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>1300.099975585938</v>
-      </c>
-      <c r="D278" t="n">
-        <v>1300.099975585938</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.7180214524269104</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>SIKKO.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>5.829999923706055</v>
-      </c>
-      <c r="D279" t="n">
-        <v>5.829999923706055</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.715453028678894</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>GARFIBRES.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>795.7000122070312</v>
-      </c>
-      <c r="D280" t="n">
-        <v>795.7000122070312</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.6256636381149292</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>KIRLOSBROS.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>1784</v>
-      </c>
-      <c r="D281" t="n">
-        <v>1784</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.6253299713134766</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>NEULANDLAB.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>22650</v>
+      </c>
+      <c r="D272" t="n">
+        <v>22650</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9840558767318726</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>HDFCLIFE.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>521.75</v>
+      </c>
+      <c r="D273" t="n">
+        <v>521.75</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.8367236256599426</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>INDUSINDBK.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>959.7000122070312</v>
+      </c>
+      <c r="D274" t="n">
+        <v>959.7000122070312</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.7519829869270325</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>KALYANIFRG.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1067.949951171875</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1067.949951171875</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.7288623452186584</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>GARUDA.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>176.5099945068359</v>
+      </c>
+      <c r="D276" t="n">
+        <v>176.5099945068359</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.6999892592430115</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>BANG.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>33.4900016784668</v>
+      </c>
+      <c r="D277" t="n">
+        <v>33.4900016784668</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.6402856707572937</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>MEDANTA.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>1420.5</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1420.5</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.6186453700065613</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>YASHO.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>3889.89990234375</v>
+      </c>
+      <c r="D279" t="n">
+        <v>3889.89990234375</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.5249437689781189</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>NITCO.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>88.62999725341797</v>
+      </c>
+      <c r="D280" t="n">
+        <v>88.62999725341797</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.4541184306144714</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>WIPRO.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>169.6199951171875</v>
+      </c>
+      <c r="D281" t="n">
+        <v>169.6199951171875</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.4201404452323914</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>22650</v>
       </c>
       <c r="D272" t="n">
-        <v>22650</v>
+        <v>22715</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.2869757174392936</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>521.75</v>
       </c>
       <c r="D273" t="n">
-        <v>521.75</v>
+        <v>521.0499877929688</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-0.70001220703125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-0.1341662112182559</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>959.7000122070312</v>
       </c>
       <c r="D274" t="n">
-        <v>959.7000122070312</v>
+        <v>959.4000244140625</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-0.29998779296875</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.03125849631687148</v>
       </c>
     </row>
     <row r="275">
@@ -11637,28 +11637,32 @@
         <v>1067.949951171875</v>
       </c>
       <c r="D275" t="n">
-        <v>1067.949951171875</v>
+        <v>1035</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-32.949951171875</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H275" t="n">
         <v>0.7288623452186584</v>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-3.08534600668492</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11680,13 @@
         <v>176.5099945068359</v>
       </c>
       <c r="D276" t="n">
-        <v>176.5099945068359</v>
+        <v>176.8500061035156</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>0.3400115966797159</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11701,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.192630223364801</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11719,13 @@
         <v>33.4900016784668</v>
       </c>
       <c r="D277" t="n">
-        <v>33.4900016784668</v>
+        <v>33.40000152587891</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-0.09000015258789062</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.2687373785524723</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11758,13 @@
         <v>1420.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1420.5</v>
+        <v>1420.599975585938</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>0.0999755859375</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.00703805603220697</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11797,13 @@
         <v>3889.89990234375</v>
       </c>
       <c r="D279" t="n">
-        <v>3889.89990234375</v>
+        <v>3882</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>-7.89990234375</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>-0.2030875483194345</v>
       </c>
     </row>
     <row r="280">
@@ -11832,28 +11836,32 @@
         <v>88.62999725341797</v>
       </c>
       <c r="D280" t="n">
-        <v>88.62999725341797</v>
+        <v>89.22000122070312</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>89.22000122070312</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>0.5900039672851562</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H280" t="n">
         <v>0.4541184306144714</v>
       </c>
-      <c r="I280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>0.6656933155466199</v>
       </c>
     </row>
     <row r="281">
@@ -11871,28 +11879,32 @@
         <v>169.6199951171875</v>
       </c>
       <c r="D281" t="n">
-        <v>169.6199951171875</v>
+        <v>169.8099975585938</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>169.8099975585938</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>0.19000244140625</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H281" t="n">
         <v>0.4201404452323914</v>
       </c>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>0.112016535123103</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>521.75</v>
       </c>
       <c r="D273" t="n">
-        <v>521.0499877929688</v>
+        <v>520.4500122070312</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.70001220703125</v>
+        <v>-1.29998779296875</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.1341662112182559</v>
+        <v>-0.2491591361703402</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>959.7000122070312</v>
       </c>
       <c r="D274" t="n">
-        <v>959.4000244140625</v>
+        <v>958.5</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.29998779296875</v>
+        <v>-1.20001220703125</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.03125849631687148</v>
+        <v>-0.1250403450836236</v>
       </c>
     </row>
     <row r="275">
@@ -11680,13 +11680,13 @@
         <v>176.5099945068359</v>
       </c>
       <c r="D276" t="n">
-        <v>176.8500061035156</v>
+        <v>176.6399993896484</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.3400115966797159</v>
+        <v>0.1300048828125284</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.192630223364801</v>
+        <v>0.07365298671939711</v>
       </c>
     </row>
     <row r="277">
@@ -11758,13 +11758,13 @@
         <v>1420.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1420.599975585938</v>
+        <v>1420.5</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.0999755859375</v>
+        <v>0</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.00703805603220697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -11797,13 +11797,13 @@
         <v>3889.89990234375</v>
       </c>
       <c r="D279" t="n">
-        <v>3882</v>
+        <v>3879.89990234375</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-7.89990234375</v>
+        <v>-10</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.2030875483194345</v>
+        <v>-0.2570760238322529</v>
       </c>
     </row>
     <row r="280">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>22650</v>
       </c>
       <c r="D272" t="n">
-        <v>22715</v>
+        <v>22700</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.2869757174392936</v>
+        <v>0.2207505518763797</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>521.75</v>
       </c>
       <c r="D273" t="n">
-        <v>520.4500122070312</v>
+        <v>520.3499755859375</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-1.29998779296875</v>
+        <v>-1.4000244140625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.2491591361703402</v>
+        <v>-0.2683324224365118</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>959.7000122070312</v>
       </c>
       <c r="D274" t="n">
-        <v>958.5</v>
+        <v>958.2999877929688</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-1.20001220703125</v>
+        <v>-1.4000244140625</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.1250403450836236</v>
+        <v>-0.1458814625669172</v>
       </c>
     </row>
     <row r="275">
@@ -11680,13 +11680,13 @@
         <v>176.5099945068359</v>
       </c>
       <c r="D276" t="n">
-        <v>176.6399993896484</v>
+        <v>176.8899993896484</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.1300048828125284</v>
+        <v>0.3800048828125284</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.07365298671939711</v>
+        <v>0.2152880259694368</v>
       </c>
     </row>
     <row r="277">
@@ -11719,13 +11719,13 @@
         <v>33.4900016784668</v>
       </c>
       <c r="D277" t="n">
-        <v>33.40000152587891</v>
+        <v>33.47999954223633</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.09000015258789062</v>
+        <v>-0.01000213623046875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.2687373785524723</v>
+        <v>-0.02986603681450355</v>
       </c>
     </row>
     <row r="278">
@@ -11758,13 +11758,13 @@
         <v>1420.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1420.5</v>
+        <v>1423.300048828125</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>2.800048828125</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.1971171297518479</v>
       </c>
     </row>
     <row r="279">
@@ -11797,13 +11797,13 @@
         <v>3889.89990234375</v>
       </c>
       <c r="D279" t="n">
-        <v>3879.89990234375</v>
+        <v>3899.39990234375</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-10</v>
+        <v>9.5</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.2570760238322529</v>
+        <v>0.2442222226406402</v>
       </c>
     </row>
     <row r="280">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>22650</v>
       </c>
       <c r="D272" t="n">
-        <v>22700</v>
+        <v>22670</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.2207505518763797</v>
+        <v>0.08830022075055188</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>521.75</v>
       </c>
       <c r="D273" t="n">
-        <v>520.3499755859375</v>
+        <v>521.0499877929688</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-1.4000244140625</v>
+        <v>-0.70001220703125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.2683324224365118</v>
+        <v>-0.1341662112182559</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>959.7000122070312</v>
       </c>
       <c r="D274" t="n">
-        <v>958.2999877929688</v>
+        <v>957.2999877929688</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-1.4000244140625</v>
+        <v>-2.4000244140625</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.1458814625669172</v>
+        <v>-0.2500806901672473</v>
       </c>
     </row>
     <row r="275">
@@ -11680,13 +11680,13 @@
         <v>176.5099945068359</v>
       </c>
       <c r="D276" t="n">
-        <v>176.8899993896484</v>
+        <v>176.3000030517578</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.3800048828125284</v>
+        <v>-0.2099914550780966</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.2152880259694368</v>
+        <v>-0.1189685919286366</v>
       </c>
     </row>
     <row r="277">
@@ -11758,13 +11758,13 @@
         <v>1420.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1423.300048828125</v>
+        <v>1422</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>2.800048828125</v>
+        <v>1.5</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.1971171297518479</v>
+        <v>0.1055966209081309</v>
       </c>
     </row>
     <row r="279">
@@ -11797,13 +11797,13 @@
         <v>3889.89990234375</v>
       </c>
       <c r="D279" t="n">
-        <v>3899.39990234375</v>
+        <v>3878.60009765625</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>9.5</v>
+        <v>-11.2998046875</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.2442222226406402</v>
+        <v>-0.2904908859143552</v>
       </c>
     </row>
     <row r="280">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>22650</v>
       </c>
       <c r="D272" t="n">
-        <v>22670</v>
+        <v>22700</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.08830022075055188</v>
+        <v>0.2207505518763797</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>521.75</v>
       </c>
       <c r="D273" t="n">
-        <v>521.0499877929688</v>
+        <v>521.2999877929688</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.70001220703125</v>
+        <v>-0.45001220703125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.1341662112182559</v>
+        <v>-0.08625054279468136</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>959.7000122070312</v>
       </c>
       <c r="D274" t="n">
-        <v>957.2999877929688</v>
+        <v>956.4000244140625</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-2.4000244140625</v>
+        <v>-3.29998779296875</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.2500806901672473</v>
+        <v>-0.3438561791178617</v>
       </c>
     </row>
     <row r="275">
@@ -11680,13 +11680,13 @@
         <v>176.5099945068359</v>
       </c>
       <c r="D276" t="n">
-        <v>176.3000030517578</v>
+        <v>176.3999938964844</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.2099914550780966</v>
+        <v>-0.1100006103515341</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.1189685919286366</v>
+        <v>-0.06231976305867142</v>
       </c>
     </row>
     <row r="277">
@@ -11719,28 +11719,32 @@
         <v>33.4900016784668</v>
       </c>
       <c r="D277" t="n">
-        <v>33.47999954223633</v>
+        <v>32.56000137329102</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>32.56000137329102</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.01000213623046875</v>
+        <v>-0.9300003051757812</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H277" t="n">
         <v>0.6402856707572937</v>
       </c>
-      <c r="I277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.02986603681450355</v>
+        <v>-2.776949114857009</v>
       </c>
     </row>
     <row r="278">
@@ -11758,13 +11762,13 @@
         <v>1420.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1422</v>
+        <v>1420.599975585938</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>1.5</v>
+        <v>0.0999755859375</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11783,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.1055966209081309</v>
+        <v>0.00703805603220697</v>
       </c>
     </row>
     <row r="279">
@@ -11797,13 +11801,13 @@
         <v>3889.89990234375</v>
       </c>
       <c r="D279" t="n">
-        <v>3878.60009765625</v>
+        <v>3879.5</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-11.2998046875</v>
+        <v>-10.39990234375</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11822,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.2904908859143552</v>
+        <v>-0.2673565542774978</v>
       </c>
     </row>
     <row r="280">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,412 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>NEULANDLAB.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>22650</v>
-      </c>
-      <c r="D272" t="n">
-        <v>22700</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>50</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9840558767318726</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.2207505518763797</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>HDFCLIFE.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>521.75</v>
-      </c>
-      <c r="D273" t="n">
-        <v>521.2999877929688</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>-0.45001220703125</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.8367236256599426</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>-0.08625054279468136</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>INDUSINDBK.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>959.7000122070312</v>
-      </c>
-      <c r="D274" t="n">
-        <v>956.4000244140625</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>-3.29998779296875</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.7519829869270325</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>-0.3438561791178617</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>KALYANIFRG.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>1067.949951171875</v>
-      </c>
-      <c r="D275" t="n">
-        <v>1035</v>
-      </c>
-      <c r="E275" t="n">
-        <v>1035</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-32.949951171875</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.7288623452186584</v>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-3.08534600668492</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>GARUDA.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>176.5099945068359</v>
-      </c>
-      <c r="D276" t="n">
-        <v>176.3999938964844</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>-0.1100006103515341</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.6999892592430115</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>-0.06231976305867142</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>BANG.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>33.4900016784668</v>
-      </c>
-      <c r="D277" t="n">
-        <v>32.56000137329102</v>
-      </c>
-      <c r="E277" t="n">
-        <v>32.56000137329102</v>
-      </c>
-      <c r="F277" t="n">
-        <v>-0.9300003051757812</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.6402856707572937</v>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>-2.776949114857009</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>MEDANTA.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>1420.5</v>
-      </c>
-      <c r="D278" t="n">
-        <v>1420.599975585938</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0.0999755859375</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.6186453700065613</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0.00703805603220697</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>YASHO.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>3889.89990234375</v>
-      </c>
-      <c r="D279" t="n">
-        <v>3879.5</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-10.39990234375</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.5249437689781189</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-0.2673565542774978</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>NITCO.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>88.62999725341797</v>
-      </c>
-      <c r="D280" t="n">
-        <v>89.22000122070312</v>
-      </c>
-      <c r="E280" t="n">
-        <v>89.22000122070312</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0.5900039672851562</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.4541184306144714</v>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0.6656933155466199</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>WIPRO.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>169.6199951171875</v>
-      </c>
-      <c r="D281" t="n">
-        <v>169.8099975585938</v>
-      </c>
-      <c r="E281" t="n">
-        <v>169.8099975585938</v>
-      </c>
-      <c r="F281" t="n">
-        <v>0.19000244140625</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.4201404452323914</v>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>0.112016535123103</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>PGHH.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>7607.5</v>
+      </c>
+      <c r="D272" t="n">
+        <v>7607.5</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9792145490646362</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>NHPC.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>75.62000274658203</v>
+      </c>
+      <c r="D273" t="n">
+        <v>75.62000274658203</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9406907558441162</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1627.900024414062</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1627.900024414062</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9071062803268433</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>UPL.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>553</v>
+      </c>
+      <c r="D275" t="n">
+        <v>553</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.8800886273384094</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>HUHTAMAKI.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>243.6499938964844</v>
+      </c>
+      <c r="D276" t="n">
+        <v>243.6499938964844</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.8647973537445068</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>FINOPB.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>137.5899963378906</v>
+      </c>
+      <c r="D277" t="n">
+        <v>137.5899963378906</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.8014042973518372</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>BLUESTARCO.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>1504</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1504</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.7780766487121582</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SUPREME.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>32.47999954223633</v>
+      </c>
+      <c r="D279" t="n">
+        <v>32.47999954223633</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.7726674675941467</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SEAMECLTD.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1704</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1704</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.7703231573104858</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>KIRIINDUS.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>514.6500244140625</v>
+      </c>
+      <c r="D281" t="n">
+        <v>514.6500244140625</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.7686712741851807</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7607.5</v>
       </c>
       <c r="D272" t="n">
-        <v>7607.5</v>
+        <v>7624.5</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.223463687150838</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>75.62000274658203</v>
       </c>
       <c r="D273" t="n">
-        <v>75.62000274658203</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-0.03000640869140625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-0.03968051785446744</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1627.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1627.900024414062</v>
+        <v>1630.400024414062</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>2.500000000000455</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>0.1535720844343799</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>553</v>
       </c>
       <c r="D275" t="n">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-0.1808318264014467</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>243.6499938964844</v>
       </c>
       <c r="D276" t="n">
-        <v>243.6499938964844</v>
+        <v>243.6999969482422</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>0.05000305175778408</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.02052249251400682</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>137.5899963378906</v>
       </c>
       <c r="D277" t="n">
-        <v>137.5899963378906</v>
+        <v>137.1399993896484</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-0.4499969482421591</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.3270564432148585</v>
       </c>
     </row>
     <row r="278">
@@ -11754,28 +11754,32 @@
         <v>1504</v>
       </c>
       <c r="D278" t="n">
-        <v>1504</v>
+        <v>1511.300048828125</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>1511.300048828125</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>7.300048828125</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H278" t="n">
         <v>0.7780766487121582</v>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.4853755869763963</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11797,13 @@
         <v>32.47999954223633</v>
       </c>
       <c r="D279" t="n">
-        <v>32.47999954223633</v>
+        <v>32.4900016784668</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>0.01000213623046875</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>0.03079475483816487</v>
       </c>
     </row>
     <row r="280">
@@ -11832,28 +11836,32 @@
         <v>1704</v>
       </c>
       <c r="D280" t="n">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>1703</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H280" t="n">
         <v>0.7703231573104858</v>
       </c>
-      <c r="I280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>-0.05868544600938967</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11879,13 @@
         <v>514.6500244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>514.6500244140625</v>
+        <v>515.3499755859375</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>0.699951171875</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>0.1360052732285218</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>75.62000274658203</v>
       </c>
       <c r="D273" t="n">
-        <v>75.58999633789062</v>
+        <v>75.58000183105469</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.03000640869140625</v>
+        <v>-0.04000091552734375</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.03968051785446744</v>
+        <v>-0.05289726801702842</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1627.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1630.400024414062</v>
+        <v>1631.699951171875</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>2.500000000000455</v>
+        <v>3.799926757812955</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.1535720844343799</v>
+        <v>0.2334250691580818</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>553</v>
       </c>
       <c r="D275" t="n">
-        <v>552</v>
+        <v>552.1500244140625</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-1</v>
+        <v>-0.8499755859375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.1808318264014467</v>
+        <v>-0.1537026376017179</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>243.6499938964844</v>
       </c>
       <c r="D276" t="n">
-        <v>243.6999969482422</v>
+        <v>243.75</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.05000305175778408</v>
+        <v>0.1000061035155966</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.02052249251400682</v>
+        <v>0.0410449850280253</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>137.5899963378906</v>
       </c>
       <c r="D277" t="n">
-        <v>137.1399993896484</v>
+        <v>137</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.4499969482421591</v>
+        <v>-0.5899963378905966</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.3270564432148585</v>
+        <v>-0.4288075831048763</v>
       </c>
     </row>
     <row r="278">
@@ -11879,13 +11879,13 @@
         <v>514.6500244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>515.3499755859375</v>
+        <v>515</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0.699951171875</v>
+        <v>0.3499755859375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.1360052732285218</v>
+        <v>0.06800263661426091</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7607.5</v>
       </c>
       <c r="D272" t="n">
-        <v>7624.5</v>
+        <v>7624</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.223463687150838</v>
+        <v>0.2168912257640487</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>75.62000274658203</v>
       </c>
       <c r="D273" t="n">
-        <v>75.58000183105469</v>
+        <v>75.48999786376953</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.04000091552734375</v>
+        <v>-0.1300048828125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.05289726801702842</v>
+        <v>-0.1719186433359078</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1627.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1631.699951171875</v>
+        <v>1629.800048828125</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>3.799926757812955</v>
+        <v>1.900024414062955</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.2334250691580818</v>
+        <v>0.1167162838975225</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>553</v>
       </c>
       <c r="D275" t="n">
-        <v>552.1500244140625</v>
+        <v>552.5</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.8499755859375</v>
+        <v>-0.5</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.1537026376017179</v>
+        <v>-0.09041591320072333</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>243.6499938964844</v>
       </c>
       <c r="D276" t="n">
-        <v>243.75</v>
+        <v>243.6999969482422</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.1000061035155966</v>
+        <v>0.05000305175778408</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.0410449850280253</v>
+        <v>0.02052249251400682</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>137.5899963378906</v>
       </c>
       <c r="D277" t="n">
-        <v>137</v>
+        <v>135.6699981689453</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.5899963378905966</v>
+        <v>-1.919998168945284</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.4288075831048763</v>
+        <v>-1.395448957081293</v>
       </c>
     </row>
     <row r="278">
@@ -11797,13 +11797,13 @@
         <v>32.47999954223633</v>
       </c>
       <c r="D279" t="n">
-        <v>32.4900016784668</v>
+        <v>32.16999816894531</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.01000213623046875</v>
+        <v>-0.3100013732910156</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.03079475483816487</v>
+        <v>-0.9544377391012465</v>
       </c>
     </row>
     <row r="280">
@@ -11879,13 +11879,13 @@
         <v>514.6500244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>515</v>
+        <v>512.5999755859375</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0.3499755859375</v>
+        <v>-2.050048828125</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.06800263661426091</v>
+        <v>-0.3983384301708747</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7607.5</v>
       </c>
       <c r="D272" t="n">
-        <v>7624</v>
+        <v>7625</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.2168912257640487</v>
+        <v>0.2300361485376273</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>75.62000274658203</v>
       </c>
       <c r="D273" t="n">
-        <v>75.48999786376953</v>
+        <v>75.37999725341797</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.1300048828125</v>
+        <v>-0.2400054931640625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.1719186433359078</v>
+        <v>-0.3173836081021705</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1627.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1629.800048828125</v>
+        <v>1624.400024414062</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>1.900024414062955</v>
+        <v>-3.499999999999545</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.1167162838975225</v>
+        <v>-0.2150009182080648</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>553</v>
       </c>
       <c r="D275" t="n">
-        <v>552.5</v>
+        <v>551.2000122070312</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.5</v>
+        <v>-1.79998779296875</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.09041591320072333</v>
+        <v>-0.3254950801028481</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>243.6499938964844</v>
       </c>
       <c r="D276" t="n">
-        <v>243.6999969482422</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.05000305175778408</v>
+        <v>-0.7999877929687784</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.02052249251400682</v>
+        <v>-0.3283348298825142</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>137.5899963378906</v>
       </c>
       <c r="D277" t="n">
-        <v>135.6699981689453</v>
+        <v>135.7200012207031</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-1.919998168945284</v>
+        <v>-1.869995117187472</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-1.395448957081293</v>
+        <v>-1.359106887825752</v>
       </c>
     </row>
     <row r="278">
@@ -11797,13 +11797,13 @@
         <v>32.47999954223633</v>
       </c>
       <c r="D279" t="n">
-        <v>32.16999816894531</v>
+        <v>32.15999984741211</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.3100013732910156</v>
+        <v>-0.3199996948242188</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.9544377391012465</v>
+        <v>-0.9852207491816546</v>
       </c>
     </row>
     <row r="280">
@@ -11879,13 +11879,13 @@
         <v>514.6500244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>512.5999755859375</v>
+        <v>512.4000244140625</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-2.050048828125</v>
+        <v>-2.25</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.3983384301708747</v>
+        <v>-0.4371903027813245</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7607.5</v>
       </c>
       <c r="D272" t="n">
-        <v>7625</v>
+        <v>7618</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.2300361485376273</v>
+        <v>0.1380216891225764</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>75.62000274658203</v>
       </c>
       <c r="D273" t="n">
-        <v>75.37999725341797</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.2400054931640625</v>
+        <v>-0.1700057983398438</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.3173836081021705</v>
+        <v>-0.2248159113529362</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1627.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1624.400024414062</v>
+        <v>1620</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-3.499999999999545</v>
+        <v>-7.900024414062045</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.2150009182080648</v>
+        <v>-0.4852892865399114</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>553</v>
       </c>
       <c r="D275" t="n">
-        <v>551.2000122070312</v>
+        <v>551.1500244140625</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-1.79998779296875</v>
+        <v>-1.8499755859375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.3254950801028481</v>
+        <v>-0.3345344640031646</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>243.6499938964844</v>
       </c>
       <c r="D276" t="n">
-        <v>242.8500061035156</v>
+        <v>242.8999938964844</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.7999877929687784</v>
+        <v>-0.7500000000000284</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.3283348298825142</v>
+        <v>-0.3078185999539441</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>137.5899963378906</v>
       </c>
       <c r="D277" t="n">
-        <v>135.7200012207031</v>
+        <v>136.3500061035156</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-1.869995117187472</v>
+        <v>-1.239990234374972</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-1.359106887825752</v>
+        <v>-0.9012212132994246</v>
       </c>
     </row>
     <row r="278">
@@ -11797,13 +11797,13 @@
         <v>32.47999954223633</v>
       </c>
       <c r="D279" t="n">
-        <v>32.15999984741211</v>
+        <v>32.29999923706055</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.3199996948242188</v>
+        <v>-0.1800003051757812</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.9852207491816546</v>
+        <v>-0.5541881395094003</v>
       </c>
     </row>
     <row r="280">
@@ -11879,13 +11879,13 @@
         <v>514.6500244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>512.4000244140625</v>
+        <v>512.6500244140625</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-2.25</v>
+        <v>-2</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.4371903027813245</v>
+        <v>-0.3886136024722884</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7607.5</v>
       </c>
       <c r="D272" t="n">
-        <v>7618</v>
+        <v>7600.5</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>10.5</v>
+        <v>-7</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.1380216891225764</v>
+        <v>-0.09201445941505094</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>75.62000274658203</v>
       </c>
       <c r="D273" t="n">
-        <v>75.44999694824219</v>
+        <v>75.45999908447266</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.1700057983398438</v>
+        <v>-0.160003662109375</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.2248159113529362</v>
+        <v>-0.2115890720681137</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1627.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1620</v>
+        <v>1623.699951171875</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-7.900024414062045</v>
+        <v>-4.200073242187045</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.4852892865399114</v>
+        <v>-0.2580056010318446</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>553</v>
       </c>
       <c r="D275" t="n">
-        <v>551.1500244140625</v>
+        <v>551.5999755859375</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-1.8499755859375</v>
+        <v>-1.4000244140625</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.3345344640031646</v>
+        <v>-0.2531689718015371</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>243.6499938964844</v>
       </c>
       <c r="D276" t="n">
-        <v>242.8999938964844</v>
+        <v>243</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.7500000000000284</v>
+        <v>-0.6499938964844034</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.3078185999539441</v>
+        <v>-0.2667736149259071</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>137.5899963378906</v>
       </c>
       <c r="D277" t="n">
-        <v>136.3500061035156</v>
+        <v>135.8000030517578</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-1.239990234374972</v>
+        <v>-1.789993286132784</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.9012212132994246</v>
+        <v>-1.300961795025386</v>
       </c>
     </row>
     <row r="278">
@@ -11797,13 +11797,13 @@
         <v>32.47999954223633</v>
       </c>
       <c r="D279" t="n">
-        <v>32.29999923706055</v>
+        <v>32</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.1800003051757812</v>
+        <v>-0.4799995422363281</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.5541881395094003</v>
+        <v>-1.477831123772482</v>
       </c>
     </row>
     <row r="280">
@@ -11879,13 +11879,13 @@
         <v>514.6500244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>512.6500244140625</v>
+        <v>514.2999877929688</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-2</v>
+        <v>-0.35003662109375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.3886136024722884</v>
+        <v>-0.06801449616023481</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,404 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>PGHH.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>7607.5</v>
-      </c>
-      <c r="D272" t="n">
-        <v>7600.5</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9792145490646362</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>-0.09201445941505094</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>NHPC.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>75.62000274658203</v>
-      </c>
-      <c r="D273" t="n">
-        <v>75.45999908447266</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>-0.160003662109375</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9406907558441162</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>-0.2115890720681137</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>ASTRAMICRO.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>1627.900024414062</v>
-      </c>
-      <c r="D274" t="n">
-        <v>1623.699951171875</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>-4.200073242187045</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9071062803268433</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>-0.2580056010318446</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>UPL.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>553</v>
-      </c>
-      <c r="D275" t="n">
-        <v>551.5999755859375</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-1.4000244140625</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.8800886273384094</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-0.2531689718015371</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>HUHTAMAKI.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>243.6499938964844</v>
-      </c>
-      <c r="D276" t="n">
-        <v>243</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>-0.6499938964844034</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.8647973537445068</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>-0.2667736149259071</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>FINOPB.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>137.5899963378906</v>
-      </c>
-      <c r="D277" t="n">
-        <v>135.8000030517578</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>-1.789993286132784</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.8014042973518372</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>-1.300961795025386</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>BLUESTARCO.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>1504</v>
-      </c>
-      <c r="D278" t="n">
-        <v>1511.300048828125</v>
-      </c>
-      <c r="E278" t="n">
-        <v>1511.300048828125</v>
-      </c>
-      <c r="F278" t="n">
-        <v>7.300048828125</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.7780766487121582</v>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0.4853755869763963</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>SUPREME.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>32.47999954223633</v>
-      </c>
-      <c r="D279" t="n">
-        <v>32</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-0.4799995422363281</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.7726674675941467</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-1.477831123772482</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>SEAMECLTD.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>1704</v>
-      </c>
-      <c r="D280" t="n">
-        <v>1703</v>
-      </c>
-      <c r="E280" t="n">
-        <v>1703</v>
-      </c>
-      <c r="F280" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.7703231573104858</v>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>-0.05868544600938967</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>KIRIINDUS.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>514.6500244140625</v>
-      </c>
-      <c r="D281" t="n">
-        <v>514.2999877929688</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-0.35003662109375</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.7686712741851807</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>-0.06801449616023481</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>HESTERBIO.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2236.60009765625</v>
+      </c>
+      <c r="D272" t="n">
+        <v>2236.60009765625</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.985684871673584</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>GALAXYSURF.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2251.699951171875</v>
+      </c>
+      <c r="D273" t="n">
+        <v>2251.699951171875</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9606516361236572</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HEIDELBERG.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>141.3200073242188</v>
+      </c>
+      <c r="D274" t="n">
+        <v>141.3200073242188</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9592073559761047</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>JIOFIN.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>228.5200042724609</v>
+      </c>
+      <c r="D275" t="n">
+        <v>228.5200042724609</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9447881579399109</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ALPHAETF.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>26</v>
+      </c>
+      <c r="D276" t="n">
+        <v>26</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.9182758927345276</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>VPRPL.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>32.9900016784668</v>
+      </c>
+      <c r="D277" t="n">
+        <v>32.9900016784668</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.9117557406425476</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>FORCEMOT.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>17750</v>
+      </c>
+      <c r="D278" t="n">
+        <v>17750</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.8831790685653687</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SUDARSCHEM.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>1210.199951171875</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1210.199951171875</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.8570437431335449</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>210.7799987792969</v>
+      </c>
+      <c r="D280" t="n">
+        <v>210.7799987792969</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.8416935205459595</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>OMAXE.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>118.7699966430664</v>
+      </c>
+      <c r="D281" t="n">
+        <v>118.7699966430664</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.7856654524803162</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2236.60009765625</v>
       </c>
       <c r="D272" t="n">
-        <v>2236.60009765625</v>
+        <v>2250</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>13.39990234375</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.5991192774153885</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>2251.699951171875</v>
       </c>
       <c r="D273" t="n">
-        <v>2251.699951171875</v>
+        <v>2246.60009765625</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-5.099853515625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-0.2264890361156171</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>141.3200073242188</v>
       </c>
       <c r="D274" t="n">
-        <v>141.3200073242188</v>
+        <v>141.4400024414062</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>0.1199951171874432</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>0.08491021155422691</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>228.5200042724609</v>
       </c>
       <c r="D275" t="n">
-        <v>228.5200042724609</v>
+        <v>229.0899963378906</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>0.5699920654297159</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>0.2494276451833613</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>32.9900016784668</v>
       </c>
       <c r="D277" t="n">
-        <v>32.9900016784668</v>
+        <v>33.02000045776367</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>0.029998779296875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>0.0909329426207813</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>17750</v>
       </c>
       <c r="D278" t="n">
-        <v>17750</v>
+        <v>17751</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.005633802816901409</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>1210.199951171875</v>
       </c>
       <c r="D279" t="n">
-        <v>1210.199951171875</v>
+        <v>1211</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>0.800048828125</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>0.0661088134527098</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>210.7799987792969</v>
       </c>
       <c r="D280" t="n">
-        <v>210.7799987792969</v>
+        <v>211.1199951171875</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>0.3399963378905966</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>0.1613038902455822</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>118.7699966430664</v>
       </c>
       <c r="D281" t="n">
-        <v>118.7699966430664</v>
+        <v>120.2900009155273</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>1.520004272460938</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>1.279788090782667</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2236.60009765625</v>
       </c>
       <c r="D272" t="n">
-        <v>2250</v>
+        <v>2254</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>13.39990234375</v>
+        <v>17.39990234375</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.5991192774153885</v>
+        <v>0.7779621561307937</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>2251.699951171875</v>
       </c>
       <c r="D273" t="n">
-        <v>2246.60009765625</v>
+        <v>2250.5</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-5.099853515625</v>
+        <v>-1.199951171875</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.2264890361156171</v>
+        <v>-0.05329090011528833</v>
       </c>
     </row>
     <row r="274">
@@ -11637,13 +11637,13 @@
         <v>228.5200042724609</v>
       </c>
       <c r="D275" t="n">
-        <v>229.0899963378906</v>
+        <v>228.8899993896484</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.5699920654297159</v>
+        <v>0.3699951171875284</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.2494276451833613</v>
+        <v>0.1619092903334576</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>32.9900016784668</v>
       </c>
       <c r="D277" t="n">
-        <v>33.02000045776367</v>
+        <v>32.90999984741211</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.029998779296875</v>
+        <v>-0.0800018310546875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.0909329426207813</v>
+        <v>-0.2425032645782077</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>17750</v>
       </c>
       <c r="D278" t="n">
-        <v>17751</v>
+        <v>17748</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.005633802816901409</v>
+        <v>-0.01126760563380282</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>1210.199951171875</v>
       </c>
       <c r="D279" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.800048828125</v>
+        <v>1.800048828125</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.0661088134527098</v>
+        <v>0.1487397868742232</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>210.7799987792969</v>
       </c>
       <c r="D280" t="n">
-        <v>211.1199951171875</v>
+        <v>211.0599975585938</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.3399963378905966</v>
+        <v>0.2799987792968466</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.1613038902455822</v>
+        <v>0.1328393495200781</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>118.7699966430664</v>
       </c>
       <c r="D281" t="n">
-        <v>120.2900009155273</v>
+        <v>120.5100021362305</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>1.520004272460938</v>
+        <v>1.740005493164062</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.279788090782667</v>
+        <v>1.465021084738442</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2236.60009765625</v>
       </c>
       <c r="D272" t="n">
-        <v>2254</v>
+        <v>2246</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>17.39990234375</v>
+        <v>9.39990234375</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.7779621561307937</v>
+        <v>0.4202763986999835</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>2251.699951171875</v>
       </c>
       <c r="D273" t="n">
-        <v>2250.5</v>
+        <v>2258.39990234375</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-1.199951171875</v>
+        <v>6.699951171875</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.05329090011528833</v>
+        <v>0.2975507979377126</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>141.3200073242188</v>
       </c>
       <c r="D274" t="n">
-        <v>141.4400024414062</v>
+        <v>141.7899932861328</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.1199951171874432</v>
+        <v>0.4699859619140057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.08491021155422691</v>
+        <v>0.3325685943645302</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>228.5200042724609</v>
       </c>
       <c r="D275" t="n">
-        <v>228.8899993896484</v>
+        <v>229.6499938964844</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.3699951171875284</v>
+        <v>1.129989624023466</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.1619092903334576</v>
+        <v>0.4944817096520778</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>26</v>
       </c>
       <c r="D276" t="n">
-        <v>26</v>
+        <v>25.97999954223633</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>-0.02000045776367188</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>-0.07692483755258414</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>32.9900016784668</v>
       </c>
       <c r="D277" t="n">
-        <v>32.90999984741211</v>
+        <v>33.04999923706055</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.0800018310546875</v>
+        <v>0.05999755859375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.2425032645782077</v>
+        <v>0.1818658852415626</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>17750</v>
       </c>
       <c r="D278" t="n">
-        <v>17748</v>
+        <v>17715</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-2</v>
+        <v>-35</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.01126760563380282</v>
+        <v>-0.1971830985915493</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>1210.199951171875</v>
       </c>
       <c r="D279" t="n">
-        <v>1212</v>
+        <v>1210.800048828125</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>1.800048828125</v>
+        <v>0.60009765625</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.1487397868742232</v>
+        <v>0.04958665348390622</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>210.7799987792969</v>
       </c>
       <c r="D280" t="n">
-        <v>211.0599975585938</v>
+        <v>211.3699951171875</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.2799987792968466</v>
+        <v>0.5899963378905966</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.1328393495200781</v>
+        <v>0.2799109694029218</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>118.7699966430664</v>
       </c>
       <c r="D281" t="n">
-        <v>120.5100021362305</v>
+        <v>120.5400009155273</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>1.740005493164062</v>
+        <v>1.770004272460938</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.465021084738442</v>
+        <v>1.490278961428486</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2236.60009765625</v>
       </c>
       <c r="D272" t="n">
-        <v>2246</v>
+        <v>2230.10009765625</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>9.39990234375</v>
+        <v>-6.5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.4202763986999835</v>
+        <v>-0.2906196779125333</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>2251.699951171875</v>
       </c>
       <c r="D273" t="n">
-        <v>2258.39990234375</v>
+        <v>2256.10009765625</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>6.699951171875</v>
+        <v>4.400146484375</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.2975507979377126</v>
+        <v>0.1954144237594795</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>141.3200073242188</v>
       </c>
       <c r="D274" t="n">
-        <v>141.7899932861328</v>
+        <v>141.5500030517578</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.4699859619140057</v>
+        <v>0.2299957275390057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.3325685943645302</v>
+        <v>0.162748171255996</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>228.5200042724609</v>
       </c>
       <c r="D275" t="n">
-        <v>229.6499938964844</v>
+        <v>229.4400024414062</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>1.129989624023466</v>
+        <v>0.9199981689453409</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.4944817096520778</v>
+        <v>0.4025897740875416</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>26</v>
       </c>
       <c r="D276" t="n">
-        <v>25.97999954223633</v>
+        <v>25.98999977111816</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.02000045776367188</v>
+        <v>-0.01000022888183594</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.07692483755258414</v>
+        <v>-0.03846241877629207</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>32.9900016784668</v>
       </c>
       <c r="D277" t="n">
-        <v>33.04999923706055</v>
+        <v>33.29999923706055</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.05999755859375</v>
+        <v>0.30999755859375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.1818658852415626</v>
+        <v>0.9396712422603219</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>17750</v>
       </c>
       <c r="D278" t="n">
-        <v>17715</v>
+        <v>17680</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-35</v>
+        <v>-70</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.1971830985915493</v>
+        <v>-0.3943661971830986</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>1210.199951171875</v>
       </c>
       <c r="D279" t="n">
-        <v>1210.800048828125</v>
+        <v>1211.300048828125</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.60009765625</v>
+        <v>1.10009765625</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.04958665348390622</v>
+        <v>0.09090214019466292</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>210.7799987792969</v>
       </c>
       <c r="D280" t="n">
-        <v>211.3699951171875</v>
+        <v>211.4499969482422</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.5899963378905966</v>
+        <v>0.6699981689452841</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.2799109694029218</v>
+        <v>0.3178661034374635</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>118.7699966430664</v>
       </c>
       <c r="D281" t="n">
-        <v>120.5400009155273</v>
+        <v>120.629997253418</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>1.770004272460938</v>
+        <v>1.860000610351562</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.490278961428486</v>
+        <v>1.566052591498617</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2236.60009765625</v>
       </c>
       <c r="D272" t="n">
-        <v>2230.10009765625</v>
+        <v>2225.10009765625</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-6.5</v>
+        <v>-11.5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.2906196779125333</v>
+        <v>-0.5141732763067898</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>2251.699951171875</v>
       </c>
       <c r="D273" t="n">
-        <v>2256.10009765625</v>
+        <v>2255.60009765625</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>4.400146484375</v>
+        <v>3.900146484375</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.1954144237594795</v>
+        <v>0.1732089785028954</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>141.3200073242188</v>
       </c>
       <c r="D274" t="n">
-        <v>141.5500030517578</v>
+        <v>141.8000030517578</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.2299957275390057</v>
+        <v>0.4799957275390057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.162748171255996</v>
+        <v>0.3396516435481008</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>228.5200042724609</v>
       </c>
       <c r="D275" t="n">
-        <v>229.4400024414062</v>
+        <v>229.5</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.9199981689453409</v>
+        <v>0.9799957275390909</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.4025897740875416</v>
+        <v>0.4288446128202663</v>
       </c>
     </row>
     <row r="276">
@@ -11754,13 +11754,13 @@
         <v>17750</v>
       </c>
       <c r="D278" t="n">
-        <v>17680</v>
+        <v>17678</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-70</v>
+        <v>-72</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.3943661971830986</v>
+        <v>-0.4056338028169014</v>
       </c>
     </row>
     <row r="279">
@@ -11793,28 +11793,32 @@
         <v>1210.199951171875</v>
       </c>
       <c r="D279" t="n">
-        <v>1211.300048828125</v>
+        <v>1210.099975585938</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>1210.099975585938</v>
       </c>
       <c r="F279" t="n">
-        <v>1.10009765625</v>
+        <v>-0.0999755859375</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H279" t="n">
         <v>0.8570437431335449</v>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.09090214019466292</v>
+        <v>-0.00826107998440179</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11836,13 @@
         <v>210.7799987792969</v>
       </c>
       <c r="D280" t="n">
-        <v>211.4499969482422</v>
+        <v>212.2599945068359</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.6699981689452841</v>
+        <v>1.479995727539034</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.3178661034374635</v>
+        <v>0.7021518816349862</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11875,13 @@
         <v>118.7699966430664</v>
       </c>
       <c r="D281" t="n">
-        <v>120.629997253418</v>
+        <v>120.9499969482422</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>1.860000610351562</v>
+        <v>2.180000305175781</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.566052591498617</v>
+        <v>1.835480648978402</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2236.60009765625</v>
       </c>
       <c r="D272" t="n">
-        <v>2225.10009765625</v>
+        <v>2250</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-11.5</v>
+        <v>13.39990234375</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.5141732763067898</v>
+        <v>0.5991192774153885</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>2251.699951171875</v>
       </c>
       <c r="D273" t="n">
-        <v>2255.60009765625</v>
+        <v>2264</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>3.900146484375</v>
+        <v>12.300048828125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.1732089785028954</v>
+        <v>0.5462561218124804</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>141.3200073242188</v>
       </c>
       <c r="D274" t="n">
-        <v>141.8000030517578</v>
+        <v>141.8999938964844</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.4799957275390057</v>
+        <v>0.5799865722655682</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.3396516435481008</v>
+        <v>0.4104065540662993</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>228.5200042724609</v>
       </c>
       <c r="D275" t="n">
-        <v>229.5</v>
+        <v>229.5899963378906</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.9799957275390909</v>
+        <v>1.069992065429716</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.4288446128202663</v>
+        <v>0.4682268709193532</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>26</v>
       </c>
       <c r="D276" t="n">
-        <v>25.98999977111816</v>
+        <v>26.13999938964844</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.01000022888183594</v>
+        <v>0.1399993896484375</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.03846241877629207</v>
+        <v>0.5384591909555289</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>32.9900016784668</v>
       </c>
       <c r="D277" t="n">
-        <v>33.29999923706055</v>
+        <v>33.40000152587891</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.30999755859375</v>
+        <v>0.4099998474121094</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.9396712422603219</v>
+        <v>1.242800322983082</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>17750</v>
       </c>
       <c r="D278" t="n">
-        <v>17678</v>
+        <v>17648</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-72</v>
+        <v>-102</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.4056338028169014</v>
+        <v>-0.5746478873239437</v>
       </c>
     </row>
     <row r="279">
@@ -11836,13 +11836,13 @@
         <v>210.7799987792969</v>
       </c>
       <c r="D280" t="n">
-        <v>212.2599945068359</v>
+        <v>212.3000030517578</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>1.479995727539034</v>
+        <v>1.520004272460909</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.7021518816349862</v>
+        <v>0.7211330682530613</v>
       </c>
     </row>
     <row r="281">
@@ -11875,13 +11875,13 @@
         <v>118.7699966430664</v>
       </c>
       <c r="D281" t="n">
-        <v>120.9499969482422</v>
+        <v>121.1999969482422</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>2.180000305175781</v>
+        <v>2.430000305175781</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.835480648978402</v>
+        <v>2.04597151962422</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,400 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>HESTERBIO.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>2236.60009765625</v>
-      </c>
-      <c r="D272" t="n">
-        <v>2250</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>13.39990234375</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.985684871673584</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.5991192774153885</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>GALAXYSURF.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>2251.699951171875</v>
-      </c>
-      <c r="D273" t="n">
-        <v>2264</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>12.300048828125</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9606516361236572</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0.5462561218124804</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>HEIDELBERG.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>141.3200073242188</v>
-      </c>
-      <c r="D274" t="n">
-        <v>141.8999938964844</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0.5799865722655682</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9592073559761047</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0.4104065540662993</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>JIOFIN.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>228.5200042724609</v>
-      </c>
-      <c r="D275" t="n">
-        <v>229.5899963378906</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>1.069992065429716</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9447881579399109</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0.4682268709193532</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>ALPHAETF.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>26</v>
-      </c>
-      <c r="D276" t="n">
-        <v>26.13999938964844</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0.1399993896484375</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.9182758927345276</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0.5384591909555289</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>VPRPL.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>32.9900016784668</v>
-      </c>
-      <c r="D277" t="n">
-        <v>33.40000152587891</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0.4099998474121094</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.9117557406425476</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>1.242800322983082</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>FORCEMOT.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>17750</v>
-      </c>
-      <c r="D278" t="n">
-        <v>17648</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>-102</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.8831790685653687</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>-0.5746478873239437</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>SUDARSCHEM.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>1210.199951171875</v>
-      </c>
-      <c r="D279" t="n">
-        <v>1210.099975585938</v>
-      </c>
-      <c r="E279" t="n">
-        <v>1210.099975585938</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-0.0999755859375</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.8570437431335449</v>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-0.00826107998440179</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>WELSPUNLIV.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>210.7799987792969</v>
-      </c>
-      <c r="D280" t="n">
-        <v>212.3000030517578</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>1.520004272460909</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.8416935205459595</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0.7211330682530613</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>OMAXE.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>118.7699966430664</v>
-      </c>
-      <c r="D281" t="n">
-        <v>121.1999969482422</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>2.430000305175781</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.7856654524803162</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>2.04597151962422</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>GALAXYSURF.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2207.89990234375</v>
+      </c>
+      <c r="D272" t="n">
+        <v>2207.89990234375</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9933295845985413</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>REPL.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>58</v>
+      </c>
+      <c r="D273" t="n">
+        <v>58</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9660857915878296</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ETERNAL.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>327.0499877929688</v>
+      </c>
+      <c r="D274" t="n">
+        <v>327.0499877929688</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9568834900856018</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>LODHA.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1144</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1144</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.8786716461181641</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>AETHER.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>1632.699951171875</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1632.699951171875</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.8400193452835083</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>TBZ.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>603.5499877929688</v>
+      </c>
+      <c r="D277" t="n">
+        <v>603.5499877929688</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.8365848660469055</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>MOL.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>62.5099983215332</v>
+      </c>
+      <c r="D278" t="n">
+        <v>62.5099983215332</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.8249038457870483</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>DHANUKA.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>975.5</v>
+      </c>
+      <c r="D279" t="n">
+        <v>975.5</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.7883707284927368</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>RPEL.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1667</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1667</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.7855374217033386</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>MANINDS.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>841.4000244140625</v>
+      </c>
+      <c r="D281" t="n">
+        <v>841.4000244140625</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.7717611193656921</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2207.89990234375</v>
       </c>
       <c r="D272" t="n">
-        <v>2207.89990234375</v>
+        <v>2209.10009765625</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>1.2001953125</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.05435913608338665</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>327.0499877929688</v>
       </c>
       <c r="D274" t="n">
-        <v>327.0499877929688</v>
+        <v>327.7999877929688</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>0.7499999999999432</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>0.2293227420863604</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>1144</v>
       </c>
       <c r="D275" t="n">
-        <v>1144</v>
+        <v>1144.5</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>0.0437062937062937</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>1632.699951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>1632.699951171875</v>
+        <v>1635</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>2.300048828125</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.140873944809892</v>
       </c>
     </row>
     <row r="277">
@@ -11754,13 +11754,13 @@
         <v>62.5099983215332</v>
       </c>
       <c r="D278" t="n">
-        <v>62.5099983215332</v>
+        <v>62.68999862670898</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>0.1800003051757812</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.2879544233066719</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>975.5</v>
       </c>
       <c r="D279" t="n">
-        <v>975.5</v>
+        <v>973</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>-0.2562788313685289</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>1667</v>
       </c>
       <c r="D280" t="n">
-        <v>1667</v>
+        <v>1658.300048828125</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>-8.699951171875</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>-0.5218926917741452</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>841.4000244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>841.4000244140625</v>
+        <v>848</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>6.5999755859375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>0.7844040164526519</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2207.89990234375</v>
       </c>
       <c r="D272" t="n">
-        <v>2209.10009765625</v>
+        <v>2209</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>1.2001953125</v>
+        <v>1.10009765625</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.05435913608338665</v>
+        <v>0.04982552221150126</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>327.0499877929688</v>
       </c>
       <c r="D274" t="n">
-        <v>327.7999877929688</v>
+        <v>327.8500061035156</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.7499999999999432</v>
+        <v>0.8000183105468182</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.2293227420863604</v>
+        <v>0.2446165235918769</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>1144</v>
       </c>
       <c r="D275" t="n">
-        <v>1144.5</v>
+        <v>1140.599975585938</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.5</v>
+        <v>-3.4000244140625</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.0437062937062937</v>
+        <v>-0.2972049312991696</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>1632.699951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>1635</v>
+        <v>1634.900024414062</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>2.300048828125</v>
+        <v>2.2000732421875</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.140873944809892</v>
+        <v>0.1347506160337906</v>
       </c>
     </row>
     <row r="277">
@@ -11754,13 +11754,13 @@
         <v>62.5099983215332</v>
       </c>
       <c r="D278" t="n">
-        <v>62.68999862670898</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.1800003051757812</v>
+        <v>0.2900009155273438</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.2879544233066719</v>
+        <v>0.4639272489429028</v>
       </c>
     </row>
     <row r="279">
@@ -11832,13 +11832,13 @@
         <v>1667</v>
       </c>
       <c r="D280" t="n">
-        <v>1658.300048828125</v>
+        <v>1659.099975585938</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-8.699951171875</v>
+        <v>-7.9000244140625</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.5218926917741452</v>
+        <v>-0.4739066835070486</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>841.4000244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>848</v>
+        <v>847.2000122070312</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>6.5999755859375</v>
+        <v>5.79998779296875</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.7844040164526519</v>
+        <v>0.6893258408220001</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2207.89990234375</v>
       </c>
       <c r="D272" t="n">
-        <v>2209</v>
+        <v>2209.10009765625</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>1.10009765625</v>
+        <v>1.2001953125</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.04982552221150126</v>
+        <v>0.05435913608338665</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>327.0499877929688</v>
       </c>
       <c r="D274" t="n">
-        <v>327.8500061035156</v>
+        <v>327.75</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.8000183105468182</v>
+        <v>0.7000122070311932</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.2446165235918769</v>
+        <v>0.2140382917471072</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>1144</v>
       </c>
       <c r="D275" t="n">
-        <v>1140.599975585938</v>
+        <v>1139.400024414062</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-3.4000244140625</v>
+        <v>-4.5999755859375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.2972049312991696</v>
+        <v>-0.4020957680015297</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>1632.699951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>1634.900024414062</v>
+        <v>1633.800048828125</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>2.2000732421875</v>
+        <v>1.10009765625</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.1347506160337906</v>
+        <v>0.06737904631285141</v>
       </c>
     </row>
     <row r="277">
@@ -11754,13 +11754,13 @@
         <v>62.5099983215332</v>
       </c>
       <c r="D278" t="n">
-        <v>62.79999923706055</v>
+        <v>63.18999862670898</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.2900009155273438</v>
+        <v>0.6800003051757812</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.4639272489429028</v>
+        <v>1.087826465260898</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>975.5</v>
       </c>
       <c r="D279" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.2562788313685289</v>
+        <v>-0.05125576627370579</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>1667</v>
       </c>
       <c r="D280" t="n">
-        <v>1659.099975585938</v>
+        <v>1649.400024414062</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-7.9000244140625</v>
+        <v>-17.5999755859375</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.4739066835070486</v>
+        <v>-1.055787377680714</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>841.4000244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>847.2000122070312</v>
+        <v>850.5</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>5.79998779296875</v>
+        <v>9.0999755859375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.6893258408220001</v>
+        <v>1.081527849048326</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11598,13 +11598,13 @@
         <v>327.0499877929688</v>
       </c>
       <c r="D274" t="n">
-        <v>327.75</v>
+        <v>327.8999938964844</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.7000122070311932</v>
+        <v>0.8500061035155682</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.2140382917471072</v>
+        <v>0.2599009739311301</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>1144</v>
       </c>
       <c r="D275" t="n">
-        <v>1139.400024414062</v>
+        <v>1139.900024414062</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-4.5999755859375</v>
+        <v>-4.0999755859375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.4020957680015297</v>
+        <v>-0.358389474295236</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>1632.699951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>1633.800048828125</v>
+        <v>1633.699951171875</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>1.10009765625</v>
+        <v>1</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.06737904631285141</v>
+        <v>0.06124824094483786</v>
       </c>
     </row>
     <row r="277">
@@ -11754,13 +11754,13 @@
         <v>62.5099983215332</v>
       </c>
       <c r="D278" t="n">
-        <v>63.18999862670898</v>
+        <v>62.95000076293945</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.6800003051757812</v>
+        <v>0.44000244140625</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>1.087826465260898</v>
+        <v>0.7038913025449237</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>975.5</v>
       </c>
       <c r="D279" t="n">
-        <v>975</v>
+        <v>974.7999877929688</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.5</v>
+        <v>-0.70001220703125</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.05125576627370579</v>
+        <v>-0.0717593241446694</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>1667</v>
       </c>
       <c r="D280" t="n">
-        <v>1649.400024414062</v>
+        <v>1644.800048828125</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-17.5999755859375</v>
+        <v>-22.199951171875</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-1.055787377680714</v>
+        <v>-1.331730724167667</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>841.4000244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>850.5</v>
+        <v>848.5999755859375</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>9.0999755859375</v>
+        <v>7.199951171875</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.081527849048326</v>
+        <v>0.855710834675686</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2207.89990234375</v>
       </c>
       <c r="D272" t="n">
-        <v>2209.10009765625</v>
+        <v>2211</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>1.2001953125</v>
+        <v>3.10009765625</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.05435913608338665</v>
+        <v>0.1404093388907331</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>327.0499877929688</v>
       </c>
       <c r="D274" t="n">
-        <v>327.8999938964844</v>
+        <v>328.3500061035156</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.8500061035155682</v>
+        <v>1.300018310546818</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.2599009739311301</v>
+        <v>0.3974983516494621</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>1144</v>
       </c>
       <c r="D275" t="n">
-        <v>1139.900024414062</v>
+        <v>1140</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-4.0999755859375</v>
+        <v>-4</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.358389474295236</v>
+        <v>-0.3496503496503496</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>1632.699951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>1633.699951171875</v>
+        <v>1635</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>1</v>
+        <v>2.300048828125</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.06124824094483786</v>
+        <v>0.140873944809892</v>
       </c>
     </row>
     <row r="277">
@@ -11754,13 +11754,13 @@
         <v>62.5099983215332</v>
       </c>
       <c r="D278" t="n">
-        <v>62.95000076293945</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.44000244140625</v>
+        <v>0.2900009155273438</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.7038913025449237</v>
+        <v>0.4639272489429028</v>
       </c>
     </row>
     <row r="279">
@@ -11832,13 +11832,13 @@
         <v>1667</v>
       </c>
       <c r="D280" t="n">
-        <v>1644.800048828125</v>
+        <v>1647.599975585938</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-22.199951171875</v>
+        <v>-19.4000244140625</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-1.331730724167667</v>
+        <v>-1.16376871110153</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>841.4000244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>848.5999755859375</v>
+        <v>849.5</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>7.199951171875</v>
+        <v>8.0999755859375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.855710834675686</v>
+        <v>0.9626783160100563</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2207.89990234375</v>
       </c>
       <c r="D272" t="n">
-        <v>2211</v>
+        <v>2216.60009765625</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>3.10009765625</v>
+        <v>8.7001953125</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.1404093388907331</v>
+        <v>0.3940484486305058</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>58</v>
       </c>
       <c r="D273" t="n">
-        <v>58</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>1.200000762939453</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>2.06896683265423</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>327.0499877929688</v>
       </c>
       <c r="D274" t="n">
-        <v>328.3500061035156</v>
+        <v>327.7999877929688</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>1.300018310546818</v>
+        <v>0.7499999999999432</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.3974983516494621</v>
+        <v>0.2293227420863604</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>1144</v>
       </c>
       <c r="D275" t="n">
-        <v>1140</v>
+        <v>1134.800048828125</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-4</v>
+        <v>-9.199951171875</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.3496503496503496</v>
+        <v>-0.8041915360030594</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>1632.699951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>2.300048828125</v>
+        <v>-0.699951171875</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.140873944809892</v>
+        <v>-0.04287077802462161</v>
       </c>
     </row>
     <row r="277">
@@ -11754,13 +11754,13 @@
         <v>62.5099983215332</v>
       </c>
       <c r="D278" t="n">
-        <v>62.79999923706055</v>
+        <v>63.2400016784668</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.2900009155273438</v>
+        <v>0.7300033569335938</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.4639272489429028</v>
+        <v>1.167818551487827</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>975.5</v>
       </c>
       <c r="D279" t="n">
-        <v>974.7999877929688</v>
+        <v>972</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.70001220703125</v>
+        <v>-3.5</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.0717593241446694</v>
+        <v>-0.3587903639159405</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>1667</v>
       </c>
       <c r="D280" t="n">
-        <v>1647.599975585938</v>
+        <v>1653</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-19.4000244140625</v>
+        <v>-14</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-1.16376871110153</v>
+        <v>-0.8398320335932814</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>841.4000244140625</v>
       </c>
       <c r="D281" t="n">
-        <v>849.5</v>
+        <v>850.5</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>8.0999755859375</v>
+        <v>9.0999755859375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.9626783160100563</v>
+        <v>1.081527849048326</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,396 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>GALAXYSURF.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>2207.89990234375</v>
-      </c>
-      <c r="D272" t="n">
-        <v>2216.60009765625</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>8.7001953125</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9933295845985413</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.3940484486305058</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>REPL.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>58</v>
-      </c>
-      <c r="D273" t="n">
-        <v>59.20000076293945</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>1.200000762939453</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9660857915878296</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>2.06896683265423</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>ETERNAL.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>327.0499877929688</v>
-      </c>
-      <c r="D274" t="n">
-        <v>327.7999877929688</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0.7499999999999432</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9568834900856018</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0.2293227420863604</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>LODHA.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>1144</v>
-      </c>
-      <c r="D275" t="n">
-        <v>1134.800048828125</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-9.199951171875</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.8786716461181641</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-0.8041915360030594</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>AETHER.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>1632.699951171875</v>
-      </c>
-      <c r="D276" t="n">
-        <v>1632</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>-0.699951171875</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.8400193452835083</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>-0.04287077802462161</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>TBZ.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>603.5499877929688</v>
-      </c>
-      <c r="D277" t="n">
-        <v>603.5499877929688</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.8365848660469055</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>MOL.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>62.5099983215332</v>
-      </c>
-      <c r="D278" t="n">
-        <v>63.2400016784668</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0.7300033569335938</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.8249038457870483</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>1.167818551487827</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>DHANUKA.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>975.5</v>
-      </c>
-      <c r="D279" t="n">
-        <v>972</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.7883707284927368</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-0.3587903639159405</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>RPEL.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>1667</v>
-      </c>
-      <c r="D280" t="n">
-        <v>1653</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>-14</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.7855374217033386</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>-0.8398320335932814</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>MANINDS.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>841.4000244140625</v>
-      </c>
-      <c r="D281" t="n">
-        <v>850.5</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>9.0999755859375</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.7717611193656921</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>1.081527849048326</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ALOKINDS.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>7.130000114440918</v>
+      </c>
+      <c r="D272" t="n">
+        <v>7.130000114440918</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9773619771003723</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>REPL.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>58.31000137329102</v>
+      </c>
+      <c r="D273" t="n">
+        <v>58.31000137329102</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9762330055236816</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>DHANUKA.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>972.7999877929688</v>
+      </c>
+      <c r="D274" t="n">
+        <v>972.7999877929688</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9611049890518188</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>JITFINFRA.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>282.7000122070312</v>
+      </c>
+      <c r="D275" t="n">
+        <v>282.7000122070312</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9562970399856567</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>AFIL.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>8.649999618530273</v>
+      </c>
+      <c r="D276" t="n">
+        <v>8.649999618530273</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.9450677037239075</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>PLAZACABLE.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>60.20000076293945</v>
+      </c>
+      <c r="D277" t="n">
+        <v>60.20000076293945</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.8396979570388794</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>INDOCO.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>256.0599975585938</v>
+      </c>
+      <c r="D278" t="n">
+        <v>256.0599975585938</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.8144761323928833</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>MHLXMIRU.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>157</v>
+      </c>
+      <c r="D279" t="n">
+        <v>157</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.8070068955421448</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>127.8600006103516</v>
+      </c>
+      <c r="D280" t="n">
+        <v>127.8600006103516</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.8028380870819092</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>176.8000030517578</v>
+      </c>
+      <c r="D281" t="n">
+        <v>176.8000030517578</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.7908303737640381</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7.130000114440918</v>
       </c>
       <c r="D272" t="n">
-        <v>7.130000114440918</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>0.01999998092651367</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.2805046368233042</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>58.31000137329102</v>
       </c>
       <c r="D273" t="n">
-        <v>58.31000137329102</v>
+        <v>59.34999847412109</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>1.039997100830071</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>1.783565557085449</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>972.7999877929688</v>
       </c>
       <c r="D274" t="n">
-        <v>972.7999877929688</v>
+        <v>978</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>5.20001220703125</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>0.5345407352264396</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>282.7000122070312</v>
       </c>
       <c r="D275" t="n">
-        <v>282.7000122070312</v>
+        <v>282.8500061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>0.1499938964844318</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>0.05305761938722026</v>
       </c>
     </row>
     <row r="276">
@@ -11676,28 +11676,32 @@
         <v>8.649999618530273</v>
       </c>
       <c r="D276" t="n">
-        <v>8.649999618530273</v>
+        <v>8.729999542236328</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>8.729999542236328</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>0.07999992370605469</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H276" t="n">
         <v>0.9450677037239075</v>
       </c>
-      <c r="I276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.9248546501051468</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11719,13 @@
         <v>60.20000076293945</v>
       </c>
       <c r="D277" t="n">
-        <v>60.20000076293945</v>
+        <v>61.18999862670898</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>0.9899978637695312</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>1.64451470302804</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11758,13 @@
         <v>256.0599975585938</v>
       </c>
       <c r="D278" t="n">
-        <v>256.0599975585938</v>
+        <v>257.5</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>1.440002441406193</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.5623691537670501</v>
       </c>
     </row>
     <row r="279">
@@ -11832,28 +11836,32 @@
         <v>127.8600006103516</v>
       </c>
       <c r="D280" t="n">
-        <v>127.8600006103516</v>
+        <v>129.6900024414062</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>129.6900024414062</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>1.830001831054645</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H280" t="n">
         <v>0.8028380870819092</v>
       </c>
-      <c r="I280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>1.431254358140905</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11879,13 @@
         <v>176.8000030517578</v>
       </c>
       <c r="D281" t="n">
-        <v>176.8000030517578</v>
+        <v>175</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>-1.800003051757812</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>-1.018101256045151</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,404 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>ALOKINDS.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>7.130000114440918</v>
-      </c>
-      <c r="D272" t="n">
-        <v>7.150000095367432</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>0.01999998092651367</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9773619771003723</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.2805046368233042</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>REPL.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>58.31000137329102</v>
-      </c>
-      <c r="D273" t="n">
-        <v>59.34999847412109</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>1.039997100830071</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9762330055236816</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>1.783565557085449</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>DHANUKA.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>972.7999877929688</v>
-      </c>
-      <c r="D274" t="n">
-        <v>978</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>5.20001220703125</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9611049890518188</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0.5345407352264396</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>JITFINFRA.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>282.7000122070312</v>
-      </c>
-      <c r="D275" t="n">
-        <v>282.8500061035156</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>0.1499938964844318</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9562970399856567</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0.05305761938722026</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>AFIL.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>8.649999618530273</v>
-      </c>
-      <c r="D276" t="n">
-        <v>8.729999542236328</v>
-      </c>
-      <c r="E276" t="n">
-        <v>8.729999542236328</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0.07999992370605469</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.9450677037239075</v>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0.9248546501051468</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>PLAZACABLE.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>60.20000076293945</v>
-      </c>
-      <c r="D277" t="n">
-        <v>61.18999862670898</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0.9899978637695312</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.8396979570388794</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>1.64451470302804</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>INDOCO.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>256.0599975585938</v>
-      </c>
-      <c r="D278" t="n">
-        <v>257.5</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>1.440002441406193</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.8144761323928833</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0.5623691537670501</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>MHLXMIRU.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>157</v>
-      </c>
-      <c r="D279" t="n">
-        <v>157</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.8070068955421448</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>GHCLTEXTIL.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>127.8600006103516</v>
-      </c>
-      <c r="D280" t="n">
-        <v>129.6900024414062</v>
-      </c>
-      <c r="E280" t="n">
-        <v>129.6900024414062</v>
-      </c>
-      <c r="F280" t="n">
-        <v>1.830001831054645</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.8028380870819092</v>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>1.431254358140905</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>KRONOX.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>176.8000030517578</v>
-      </c>
-      <c r="D281" t="n">
-        <v>175</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-1.800003051757812</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.7908303737640381</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>-1.018101256045151</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>PGHH.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>7233</v>
+      </c>
+      <c r="D272" t="n">
+        <v>7233</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9802266359329224</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>KOKUYOCMLN.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>76.27999877929688</v>
+      </c>
+      <c r="D273" t="n">
+        <v>76.27999877929688</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9630603194236755</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>BHARATRAS.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1134.900024414062</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1134.900024414062</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9584550857543945</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>BORANA.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>292.6000061035156</v>
+      </c>
+      <c r="D275" t="n">
+        <v>292.6000061035156</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9279066324234009</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>1590</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1590</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.9138698577880859</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>IIFL.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="D277" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.8779357671737671</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>BHAGCHEM.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>248.4499969482422</v>
+      </c>
+      <c r="D278" t="n">
+        <v>248.4499969482422</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.8189293742179871</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>MHRIL.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>199.8000030517578</v>
+      </c>
+      <c r="D279" t="n">
+        <v>199.8000030517578</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.8088040947914124</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>CARYSIL.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1068.099975585938</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1068.099975585938</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.7970602512359619</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>JINDRILL.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>586.4500122070312</v>
+      </c>
+      <c r="D281" t="n">
+        <v>586.4500122070312</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.7944300770759583</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7233</v>
       </c>
       <c r="D272" t="n">
-        <v>7233</v>
+        <v>7281.5</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.6705378128024333</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>76.27999877929688</v>
       </c>
       <c r="D273" t="n">
-        <v>76.27999877929688</v>
+        <v>76.11000061035156</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-0.1699981689453125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-0.2228607389430788</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1134.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1134.900024414062</v>
+        <v>1134</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-0.9000244140620453</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.079304290660027</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>292.6000061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>292.6000061035156</v>
+        <v>293.6000061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>0.3417634925291906</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>616.5</v>
       </c>
       <c r="D277" t="n">
-        <v>616.5</v>
+        <v>614.2000122070312</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-2.29998779296875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.3730718236770073</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>248.4499969482422</v>
       </c>
       <c r="D278" t="n">
-        <v>248.4499969482422</v>
+        <v>246.6000061035156</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>-1.849990844726562</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>-0.7446129472531078</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>199.8000030517578</v>
       </c>
       <c r="D279" t="n">
-        <v>199.8000030517578</v>
+        <v>199.6199951171875</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>-0.1800079345703125</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>-0.09009405997040039</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>1068.099975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1068.099975585938</v>
+        <v>1067.300048828125</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>-0.7999267578129547</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>-0.07489249846430632</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>586.4500122070312</v>
       </c>
       <c r="D281" t="n">
-        <v>586.4500122070312</v>
+        <v>585.25</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>-1.20001220703125</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>-0.204623102063747</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11637,13 +11637,13 @@
         <v>292.6000061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>293.6000061035156</v>
+        <v>293.1000061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.3417634925291906</v>
+        <v>0.1708817462645953</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>616.5</v>
       </c>
       <c r="D277" t="n">
-        <v>614.2000122070312</v>
+        <v>614.1500244140625</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-2.29998779296875</v>
+        <v>-2.3499755859375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.3730718236770073</v>
+        <v>-0.3811801437043796</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>248.4499969482422</v>
       </c>
       <c r="D278" t="n">
-        <v>246.6000061035156</v>
+        <v>246.5500030517578</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-1.849990844726562</v>
+        <v>-1.899993896484375</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.7446129472531078</v>
+        <v>-0.7647389494153173</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>199.8000030517578</v>
       </c>
       <c r="D279" t="n">
-        <v>199.6199951171875</v>
+        <v>199.25</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.1800079345703125</v>
+        <v>-0.5500030517578125</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.09009405997040039</v>
+        <v>-0.2752767984769927</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>1068.099975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1067.300048828125</v>
+        <v>1066.800048828125</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.7999267578129547</v>
+        <v>-1.299926757812955</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.07489249846430632</v>
+        <v>-0.1217045957799822</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>586.4500122070312</v>
       </c>
       <c r="D281" t="n">
-        <v>585.25</v>
+        <v>584.9000244140625</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-1.20001220703125</v>
+        <v>-1.54998779296875</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.204623102063747</v>
+        <v>-0.2643000700324935</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7233</v>
       </c>
       <c r="D272" t="n">
-        <v>7281.5</v>
+        <v>7283.5</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.6705378128024333</v>
+        <v>0.6981888566293378</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>76.27999877929688</v>
       </c>
       <c r="D273" t="n">
-        <v>76.11000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.1699981689453125</v>
+        <v>0.5900039672851562</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.2228607389430788</v>
+        <v>0.7734713905701962</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1134.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1134</v>
+        <v>1138.5</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.9000244140620453</v>
+        <v>3.599975585937955</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.079304290660027</v>
+        <v>0.3172064065992586</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>292.6000061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>293.1000061035156</v>
+        <v>293</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.5</v>
+        <v>0.399993896484375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.1708817462645953</v>
+        <v>0.1367033110528595</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>1590</v>
       </c>
       <c r="D276" t="n">
-        <v>1590</v>
+        <v>1585.099975585938</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>-4.9000244140625</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>-0.3081776361045597</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>616.5</v>
       </c>
       <c r="D277" t="n">
-        <v>614.1500244140625</v>
+        <v>617.5999755859375</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-2.3499755859375</v>
+        <v>1.0999755859375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.3811801437043796</v>
+        <v>0.1784226416768045</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>248.4499969482422</v>
       </c>
       <c r="D278" t="n">
-        <v>246.5500030517578</v>
+        <v>245.9499969482422</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-1.899993896484375</v>
+        <v>-2.5</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.7647389494153173</v>
+        <v>-1.00623869217467</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>199.8000030517578</v>
       </c>
       <c r="D279" t="n">
-        <v>199.25</v>
+        <v>199.2599945068359</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.5500030517578125</v>
+        <v>-0.540008544921875</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.2752767984769927</v>
+        <v>-0.2702745428797551</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>1068.099975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1066.800048828125</v>
+        <v>1068.900024414062</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-1.299926757812955</v>
+        <v>0.8000488281245453</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.1217045957799822</v>
+        <v>0.07490392719891738</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>586.4500122070312</v>
       </c>
       <c r="D281" t="n">
-        <v>584.9000244140625</v>
+        <v>585.5499877929688</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-1.54998779296875</v>
+        <v>-0.9000244140625</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.2643000700324935</v>
+        <v>-0.1534699284386355</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7233</v>
       </c>
       <c r="D272" t="n">
-        <v>7283.5</v>
+        <v>7289</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>50.5</v>
+        <v>56</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.6981888566293378</v>
+        <v>0.774229227153325</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>1134.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1138.5</v>
+        <v>1136.800048828125</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>3.599975585937955</v>
+        <v>1.900024414062955</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.3172064065992586</v>
+        <v>0.1674177789399484</v>
       </c>
     </row>
     <row r="275">
@@ -11676,13 +11676,13 @@
         <v>1590</v>
       </c>
       <c r="D276" t="n">
-        <v>1585.099975585938</v>
+        <v>1590.900024414062</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-4.9000244140625</v>
+        <v>0.9000244140625</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.3081776361045597</v>
+        <v>0.05660530906053459</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>616.5</v>
       </c>
       <c r="D277" t="n">
-        <v>617.5999755859375</v>
+        <v>617.2000122070312</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>1.0999755859375</v>
+        <v>0.70001220703125</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.1784226416768045</v>
+        <v>0.1135461811891727</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>248.4499969482422</v>
       </c>
       <c r="D278" t="n">
-        <v>245.9499969482422</v>
+        <v>245.6999969482422</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-2.5</v>
+        <v>-2.75</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-1.00623869217467</v>
+        <v>-1.106862561392137</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>199.8000030517578</v>
       </c>
       <c r="D279" t="n">
-        <v>199.2599945068359</v>
+        <v>199.5099945068359</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.540008544921875</v>
+        <v>-0.290008544921875</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.2702745428797551</v>
+        <v>-0.1451494196657989</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>1068.099975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1068.900024414062</v>
+        <v>1068</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.8000488281245453</v>
+        <v>-0.09997558593795475</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.07490392719891738</v>
+        <v>-0.009360133716238518</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>586.4500122070312</v>
       </c>
       <c r="D281" t="n">
-        <v>585.5499877929688</v>
+        <v>585.7000122070312</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.9000244140625</v>
+        <v>-0.75</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.1534699284386355</v>
+        <v>-0.1278881378444292</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7233</v>
       </c>
       <c r="D272" t="n">
-        <v>7289</v>
+        <v>7285</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.774229227153325</v>
+        <v>0.7189271394995161</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>1134.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1136.800048828125</v>
+        <v>1129.800048828125</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>1.900024414062955</v>
+        <v>-5.099975585937045</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.1674177789399484</v>
+        <v>-0.4493766390189403</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>292.6000061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>293</v>
+        <v>293.2000122070312</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.399993896484375</v>
+        <v>0.600006103515625</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.1367033110528595</v>
+        <v>0.2050601814763311</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>616.5</v>
       </c>
       <c r="D277" t="n">
-        <v>617.2000122070312</v>
+        <v>616.5</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.70001220703125</v>
+        <v>0</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.1135461811891727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -11793,13 +11793,13 @@
         <v>199.8000030517578</v>
       </c>
       <c r="D279" t="n">
-        <v>199.5099945068359</v>
+        <v>199.4799957275391</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.290008544921875</v>
+        <v>-0.32000732421875</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.1451494196657989</v>
+        <v>-0.160163823488958</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>1068.099975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1068</v>
+        <v>1066.699951171875</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.09997558593795475</v>
+        <v>-1.400024414062955</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.009360133716238518</v>
+        <v>-0.1310761582308744</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>586.4500122070312</v>
       </c>
       <c r="D281" t="n">
-        <v>585.7000122070312</v>
+        <v>587.75</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.75</v>
+        <v>1.29998779296875</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.1278881378444292</v>
+        <v>0.2216706907510171</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>7233</v>
       </c>
       <c r="D272" t="n">
-        <v>7285</v>
+        <v>7273.5</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>52</v>
+        <v>40.5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.7189271394995161</v>
+        <v>0.5599336374948154</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>76.27999877929688</v>
       </c>
       <c r="D273" t="n">
-        <v>76.87000274658203</v>
+        <v>75.69000244140625</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.5900039672851562</v>
+        <v>-0.589996337890625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.7734713905701962</v>
+        <v>-0.773461388741862</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1134.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1129.800048828125</v>
+        <v>1129.5</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-5.099975585937045</v>
+        <v>-5.400024414062045</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.4493766390189403</v>
+        <v>-0.4758149879193126</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>292.6000061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>293.2000122070312</v>
+        <v>291.3999938964844</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.600006103515625</v>
+        <v>-1.20001220703125</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.2050601814763311</v>
+        <v>-0.4101203629526622</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>1590</v>
       </c>
       <c r="D276" t="n">
-        <v>1590.900024414062</v>
+        <v>1581</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.9000244140625</v>
+        <v>-9</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.05660530906053459</v>
+        <v>-0.5660377358490566</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>616.5</v>
       </c>
       <c r="D277" t="n">
-        <v>616.5</v>
+        <v>617.7999877929688</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>1.29998779296875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>0.2108658220549473</v>
       </c>
     </row>
     <row r="278">
@@ -11754,28 +11754,32 @@
         <v>248.4499969482422</v>
       </c>
       <c r="D278" t="n">
-        <v>245.6999969482422</v>
+        <v>242.5</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>242.5</v>
       </c>
       <c r="F278" t="n">
-        <v>-2.75</v>
+        <v>-5.949996948242188</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H278" t="n">
         <v>0.8189293742179871</v>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-1.106862561392137</v>
+        <v>-2.394846859056999</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11797,13 @@
         <v>199.8000030517578</v>
       </c>
       <c r="D279" t="n">
-        <v>199.4799957275391</v>
+        <v>199.2299957275391</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.32000732421875</v>
+        <v>-0.57000732421875</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.160163823488958</v>
+        <v>-0.285288946702914</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11836,13 @@
         <v>1068.099975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1066.699951171875</v>
+        <v>1068.099975585938</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-1.400024414062955</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.1310761582308744</v>
+        <v>-4.257535448748597e-14</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11875,13 @@
         <v>586.4500122070312</v>
       </c>
       <c r="D281" t="n">
-        <v>587.75</v>
+        <v>588.7999877929688</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>1.29998779296875</v>
+        <v>2.3499755859375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.2216706907510171</v>
+        <v>0.4007120022205577</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,400 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>PGHH.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>7233</v>
-      </c>
-      <c r="D272" t="n">
-        <v>7273.5</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9802266359329224</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.5599336374948154</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>KOKUYOCMLN.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>76.27999877929688</v>
-      </c>
-      <c r="D273" t="n">
-        <v>75.69000244140625</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>-0.589996337890625</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9630603194236755</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>-0.773461388741862</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>BHARATRAS.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>1134.900024414062</v>
-      </c>
-      <c r="D274" t="n">
-        <v>1129.5</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>-5.400024414062045</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9584550857543945</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>-0.4758149879193126</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>BORANA.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>292.6000061035156</v>
-      </c>
-      <c r="D275" t="n">
-        <v>291.3999938964844</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-1.20001220703125</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9279066324234009</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-0.4101203629526622</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>RANEHOLDIN.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>1590</v>
-      </c>
-      <c r="D276" t="n">
-        <v>1581</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.9138698577880859</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>-0.5660377358490566</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>IIFL.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="D277" t="n">
-        <v>617.7999877929688</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>1.29998779296875</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.8779357671737671</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>0.2108658220549473</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>BHAGCHEM.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>248.4499969482422</v>
-      </c>
-      <c r="D278" t="n">
-        <v>242.5</v>
-      </c>
-      <c r="E278" t="n">
-        <v>242.5</v>
-      </c>
-      <c r="F278" t="n">
-        <v>-5.949996948242188</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.8189293742179871</v>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>-2.394846859056999</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>MHRIL.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>199.8000030517578</v>
-      </c>
-      <c r="D279" t="n">
-        <v>199.2299957275391</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-0.57000732421875</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.8088040947914124</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-0.285288946702914</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>CARYSIL.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>1068.099975585938</v>
-      </c>
-      <c r="D280" t="n">
-        <v>1068.099975585938</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>-4.547473508864641e-13</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.7970602512359619</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>-4.257535448748597e-14</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>JINDRILL.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>586.4500122070312</v>
-      </c>
-      <c r="D281" t="n">
-        <v>588.7999877929688</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>2.3499755859375</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.7944300770759583</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>0.4007120022205577</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>SREEL.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>293.8900146484375</v>
+      </c>
+      <c r="D272" t="n">
+        <v>293.8900146484375</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9959039092063904</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>VPRPL.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>33.27999877929688</v>
+      </c>
+      <c r="D273" t="n">
+        <v>33.27999877929688</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9649399518966675</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>GHCL.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>425</v>
+      </c>
+      <c r="D274" t="n">
+        <v>425</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.889218270778656</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>AYMSYNTEX.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>296.3500061035156</v>
+      </c>
+      <c r="D275" t="n">
+        <v>296.3500061035156</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.8876714706420898</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>MHLXMIRU.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>157.9499969482422</v>
+      </c>
+      <c r="D276" t="n">
+        <v>157.9499969482422</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.8234480023384094</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>PIIND.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>2389.89990234375</v>
+      </c>
+      <c r="D277" t="n">
+        <v>2389.89990234375</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.8232495188713074</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>SBFC.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>90.91999816894531</v>
+      </c>
+      <c r="D278" t="n">
+        <v>90.91999816894531</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.8138964176177979</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>HEIDELBERG.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>141.7299957275391</v>
+      </c>
+      <c r="D279" t="n">
+        <v>141.7299957275391</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.7826009392738342</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ROSSARI.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>446.5499877929688</v>
+      </c>
+      <c r="D280" t="n">
+        <v>446.5499877929688</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.6560904383659363</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>GOPAL.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>262.2999877929688</v>
+      </c>
+      <c r="D281" t="n">
+        <v>262.2999877929688</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.6233786940574646</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>33.27999877929688</v>
       </c>
       <c r="D273" t="n">
-        <v>33.27999877929688</v>
+        <v>33.2400016784668</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-0.03999710083008523</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-0.1201836006525547</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>425</v>
       </c>
       <c r="D274" t="n">
-        <v>425</v>
+        <v>424.3500061035156</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-0.649993896484375</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.1529397403492647</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>296.3500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>296.3500061035156</v>
+        <v>295.3999938964844</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-0.95001220703125</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-0.320571009773966</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>2389.89990234375</v>
       </c>
       <c r="D277" t="n">
-        <v>2389.89990234375</v>
+        <v>2389.199951171875</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-0.699951171875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.02928788654238469</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>90.91999816894531</v>
       </c>
       <c r="D278" t="n">
-        <v>90.91999816894531</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>0.3899993896484375</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.4289478635093571</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>141.7299957275391</v>
       </c>
       <c r="D279" t="n">
-        <v>141.7299957275391</v>
+        <v>141.5800018310547</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>-0.1499938964844034</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>-0.1058307352049532</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>446.5499877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>446.5499877929688</v>
+        <v>446.25</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>-0.2999877929688068</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>-0.06717899477535946</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>262.2999877929688</v>
       </c>
       <c r="D281" t="n">
-        <v>262.2999877929688</v>
+        <v>262.1000061035156</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>-0.1999816894531818</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>-0.0762415931223854</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>33.27999877929688</v>
       </c>
       <c r="D273" t="n">
-        <v>33.2400016784668</v>
+        <v>33.18999862670898</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.03999710083008523</v>
+        <v>-0.09000015258789773</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.1201836006525547</v>
+        <v>-0.2704331607244103</v>
       </c>
     </row>
     <row r="274">
@@ -11637,13 +11637,13 @@
         <v>296.3500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>295.3999938964844</v>
+        <v>295.25</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.95001220703125</v>
+        <v>-1.100006103515625</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.320571009773966</v>
+        <v>-0.3711847750498749</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>2389.89990234375</v>
       </c>
       <c r="D277" t="n">
-        <v>2389.199951171875</v>
+        <v>2387</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.699951171875</v>
+        <v>-2.89990234375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.02928788654238469</v>
+        <v>-0.1213399080399181</v>
       </c>
     </row>
     <row r="278">
@@ -11754,28 +11754,32 @@
         <v>90.91999816894531</v>
       </c>
       <c r="D278" t="n">
-        <v>91.30999755859375</v>
+        <v>91.44000244140625</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>91.44000244140625</v>
       </c>
       <c r="F278" t="n">
-        <v>0.3899993896484375</v>
+        <v>0.5200042724609375</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H278" t="n">
         <v>0.8138964176177979</v>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.4289478635093571</v>
+        <v>0.5719360788972722</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11797,13 @@
         <v>141.7299957275391</v>
       </c>
       <c r="D279" t="n">
-        <v>141.5800018310547</v>
+        <v>141.5700073242188</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.1499938964844034</v>
+        <v>-0.1599884033203409</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.1058307352049532</v>
+        <v>-0.1128825288528913</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11836,13 @@
         <v>446.5499877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>446.25</v>
+        <v>446.8500061035156</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.2999877929688068</v>
+        <v>0.3000183105468182</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.06717899477535946</v>
+        <v>0.06718582885415143</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11875,13 @@
         <v>262.2999877929688</v>
       </c>
       <c r="D281" t="n">
-        <v>262.1000061035156</v>
+        <v>262.7000122070312</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.1999816894531818</v>
+        <v>0.4000244140624432</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.0762415931223854</v>
+        <v>0.1525064554628112</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>33.27999877929688</v>
       </c>
       <c r="D273" t="n">
-        <v>33.18999862670898</v>
+        <v>33.11999893188477</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.09000015258789773</v>
+        <v>-0.1599998474121165</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.2704331607244103</v>
+        <v>-0.4807687899064786</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>425</v>
       </c>
       <c r="D274" t="n">
-        <v>424.3500061035156</v>
+        <v>424.6000061035156</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.649993896484375</v>
+        <v>-0.399993896484375</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.1529397403492647</v>
+        <v>-0.0941162109375</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>296.3500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>295.25</v>
+        <v>294.3500061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-1.100006103515625</v>
+        <v>-2</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.3711847750498749</v>
+        <v>-0.674877664521254</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>157.9499969482422</v>
       </c>
       <c r="D276" t="n">
-        <v>157.9499969482422</v>
+        <v>155.1000061035156</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>-2.849990844726562</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>-1.804362709586162</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>2389.89990234375</v>
       </c>
       <c r="D277" t="n">
-        <v>2387</v>
+        <v>2386.89990234375</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-2.89990234375</v>
+        <v>-3</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.1213399080399181</v>
+        <v>-0.1255282699102976</v>
       </c>
     </row>
     <row r="278">
@@ -11797,13 +11797,13 @@
         <v>141.7299957275391</v>
       </c>
       <c r="D279" t="n">
-        <v>141.5700073242188</v>
+        <v>141.4799957275391</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.1599884033203409</v>
+        <v>-0.2500000000000284</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.1128825288528913</v>
+        <v>-0.1763917360730236</v>
       </c>
     </row>
     <row r="280">
@@ -11836,13 +11836,13 @@
         <v>446.5499877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>446.8500061035156</v>
+        <v>446.7000122070312</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.3000183105468182</v>
+        <v>0.1500244140624432</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.06718582885415143</v>
+        <v>0.03359633146647807</v>
       </c>
     </row>
     <row r="281">
@@ -11875,13 +11875,13 @@
         <v>262.2999877929688</v>
       </c>
       <c r="D281" t="n">
-        <v>262.7000122070312</v>
+        <v>262.5499877929688</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0.4000244140624432</v>
+        <v>0.2499999999999432</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.1525064554628112</v>
+        <v>0.09531071735972252</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>33.27999877929688</v>
       </c>
       <c r="D273" t="n">
-        <v>33.11999893188477</v>
+        <v>33.15000152587891</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.1599998474121165</v>
+        <v>-0.1299972534179759</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.4807687899064786</v>
+        <v>-0.3906167613769436</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>425</v>
       </c>
       <c r="D274" t="n">
-        <v>424.6000061035156</v>
+        <v>424.3999938964844</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.399993896484375</v>
+        <v>-0.600006103515625</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.0941162109375</v>
+        <v>-0.1411779067095588</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>296.3500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>294.3500061035156</v>
+        <v>294.2999877929688</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-2</v>
+        <v>-2.050018310546875</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.674877664521254</v>
+        <v>-0.6917557848238409</v>
       </c>
     </row>
     <row r="276">
@@ -11715,28 +11715,32 @@
         <v>2389.89990234375</v>
       </c>
       <c r="D277" t="n">
-        <v>2386.89990234375</v>
+        <v>2383.5</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>2383.5</v>
       </c>
       <c r="F277" t="n">
-        <v>-3</v>
+        <v>-6.39990234375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H277" t="n">
         <v>0.8232495188713074</v>
       </c>
-      <c r="I277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.1255282699102976</v>
+        <v>-0.2677895562685986</v>
       </c>
     </row>
     <row r="278">
@@ -11797,13 +11801,13 @@
         <v>141.7299957275391</v>
       </c>
       <c r="D279" t="n">
-        <v>141.4799957275391</v>
+        <v>141.5700073242188</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.2500000000000284</v>
+        <v>-0.1599884033203409</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11822,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.1763917360730236</v>
+        <v>-0.1128825288528913</v>
       </c>
     </row>
     <row r="280">
@@ -11836,13 +11840,13 @@
         <v>446.5499877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>446.7000122070312</v>
+        <v>446</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.1500244140624432</v>
+        <v>-0.5499877929688068</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.03359633146647807</v>
+        <v>-0.1231637684477542</v>
       </c>
     </row>
     <row r="281">
@@ -11875,13 +11879,13 @@
         <v>262.2999877929688</v>
       </c>
       <c r="D281" t="n">
-        <v>262.5499877929688</v>
+        <v>262.1499938964844</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0.2499999999999432</v>
+        <v>-0.1499938964844318</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.09531071735972252</v>
+        <v>-0.05718410349405764</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>33.27999877929688</v>
       </c>
       <c r="D273" t="n">
-        <v>33.15000152587891</v>
+        <v>33.20000076293945</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.1299972534179759</v>
+        <v>-0.07999801635742898</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.3906167613769436</v>
+        <v>-0.240378663737196</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>425</v>
       </c>
       <c r="D274" t="n">
-        <v>424.3999938964844</v>
+        <v>425</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.600006103515625</v>
+        <v>0</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.1411779067095588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>296.3500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>294.2999877929688</v>
+        <v>294.1000061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-2.050018310546875</v>
+        <v>-2.25</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.6917557848238409</v>
+        <v>-0.7592373725864108</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>157.9499969482422</v>
       </c>
       <c r="D276" t="n">
-        <v>155.1000061035156</v>
+        <v>157.9499969482422</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-2.849990844726562</v>
+        <v>0</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-1.804362709586162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -11801,13 +11801,13 @@
         <v>141.7299957275391</v>
       </c>
       <c r="D279" t="n">
-        <v>141.5700073242188</v>
+        <v>141.3099975585938</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.1599884033203409</v>
+        <v>-0.4199981689453409</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.1128825288528913</v>
+        <v>-0.2963368246710054</v>
       </c>
     </row>
     <row r="280">
@@ -11840,13 +11840,13 @@
         <v>446.5499877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.5499877929688068</v>
+        <v>3.450012207031193</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.1231637684477542</v>
+        <v>0.7725926103105619</v>
       </c>
     </row>
     <row r="281">
@@ -11879,13 +11879,13 @@
         <v>262.2999877929688</v>
       </c>
       <c r="D281" t="n">
-        <v>262.1499938964844</v>
+        <v>262.9500122070312</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.1499938964844318</v>
+        <v>0.6500244140624432</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.05718410349405764</v>
+        <v>0.2478171728225554</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>33.27999877929688</v>
       </c>
       <c r="D273" t="n">
-        <v>33.20000076293945</v>
+        <v>32.93999862670898</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.07999801635742898</v>
+        <v>-0.3400001525878977</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.240378663737196</v>
+        <v>-1.021635111355256</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>425</v>
       </c>
       <c r="D274" t="n">
-        <v>425</v>
+        <v>423.8999938964844</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-1.100006103515625</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.2588249655330883</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>296.3500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>294.1000061035156</v>
+        <v>291.7000122070312</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-2.25</v>
+        <v>-4.649993896484375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.7592373725864108</v>
+        <v>-1.569088510448731</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>157.9499969482422</v>
       </c>
       <c r="D276" t="n">
-        <v>157.9499969482422</v>
+        <v>159.8999938964844</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>1.949996948242188</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>1.234565992983952</v>
       </c>
     </row>
     <row r="277">
@@ -11801,13 +11801,13 @@
         <v>141.7299957275391</v>
       </c>
       <c r="D279" t="n">
-        <v>141.3099975585938</v>
+        <v>141.6900024414062</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.4199981689453409</v>
+        <v>-0.03999328613284092</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.2963368246710054</v>
+        <v>-0.02821794068894476</v>
       </c>
     </row>
     <row r="280">
@@ -11840,13 +11840,13 @@
         <v>446.5499877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>450</v>
+        <v>450.9500122070312</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>3.450012207031193</v>
+        <v>4.400024414062443</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.7725926103105619</v>
+        <v>0.985337483897189</v>
       </c>
     </row>
     <row r="281">
@@ -11879,13 +11879,13 @@
         <v>262.2999877929688</v>
       </c>
       <c r="D281" t="n">
-        <v>262.9500122070312</v>
+        <v>262.2999877929688</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0.6500244140624432</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.2478171728225554</v>
+        <v>-2.16711481152161e-14</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,404 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>SREEL.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>293.8900146484375</v>
-      </c>
-      <c r="D272" t="n">
-        <v>293.8900146484375</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9959039092063904</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>VPRPL.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>33.27999877929688</v>
-      </c>
-      <c r="D273" t="n">
-        <v>32.93999862670898</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>-0.3400001525878977</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9649399518966675</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>-1.021635111355256</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>GHCL.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>425</v>
-      </c>
-      <c r="D274" t="n">
-        <v>423.8999938964844</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>-1.100006103515625</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.889218270778656</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>-0.2588249655330883</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>AYMSYNTEX.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>296.3500061035156</v>
-      </c>
-      <c r="D275" t="n">
-        <v>291.7000122070312</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-4.649993896484375</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.8876714706420898</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-1.569088510448731</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>MHLXMIRU.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>157.9499969482422</v>
-      </c>
-      <c r="D276" t="n">
-        <v>159.8999938964844</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>1.949996948242188</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.8234480023384094</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>1.234565992983952</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>PIIND.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>2389.89990234375</v>
-      </c>
-      <c r="D277" t="n">
-        <v>2383.5</v>
-      </c>
-      <c r="E277" t="n">
-        <v>2383.5</v>
-      </c>
-      <c r="F277" t="n">
-        <v>-6.39990234375</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.8232495188713074</v>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>-0.2677895562685986</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>SBFC.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>90.91999816894531</v>
-      </c>
-      <c r="D278" t="n">
-        <v>91.44000244140625</v>
-      </c>
-      <c r="E278" t="n">
-        <v>91.44000244140625</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0.5200042724609375</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.8138964176177979</v>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0.5719360788972722</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>HEIDELBERG.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>141.7299957275391</v>
-      </c>
-      <c r="D279" t="n">
-        <v>141.6900024414062</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-0.03999328613284092</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.7826009392738342</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-0.02821794068894476</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>ROSSARI.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>446.5499877929688</v>
-      </c>
-      <c r="D280" t="n">
-        <v>450.9500122070312</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>4.400024414062443</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.6560904383659363</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0.985337483897189</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>GOPAL.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>262.2999877929688</v>
-      </c>
-      <c r="D281" t="n">
-        <v>262.2999877929688</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-5.684341886080801e-14</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.6233786940574646</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>-2.16711481152161e-14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>TCS.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2076.300048828125</v>
+      </c>
+      <c r="D272" t="n">
+        <v>2076.300048828125</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.8861837983131409</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>BASML.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>24.48999977111816</v>
+      </c>
+      <c r="D273" t="n">
+        <v>24.48999977111816</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.8738353848457336</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>KRITIKA.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>5.050000190734863</v>
+      </c>
+      <c r="D274" t="n">
+        <v>5.050000190734863</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.870434582233429</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SUMMITSEC.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1387</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1387</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.8668215274810791</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>IIFL.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>620.3499755859375</v>
+      </c>
+      <c r="D276" t="n">
+        <v>620.3499755859375</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.8119785189628601</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ALIVUS.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>1367.900024414062</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1367.900024414062</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.7810046076774597</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>BORANA.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>291.3999938964844</v>
+      </c>
+      <c r="D278" t="n">
+        <v>291.3999938964844</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.748387336730957</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>GRAPHITE.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>808.2999877929688</v>
+      </c>
+      <c r="D279" t="n">
+        <v>808.2999877929688</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.7122712135314941</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>REMSONSIND.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>110.2600021362305</v>
+      </c>
+      <c r="D280" t="n">
+        <v>110.2600021362305</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.6846562623977661</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>RELIANCE.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>1223.900024414062</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1223.900024414062</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.6765978932380676</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2076.300048828125</v>
       </c>
       <c r="D272" t="n">
-        <v>2076.300048828125</v>
+        <v>2072.199951171875</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>-4.10009765625</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>-0.1974713461363215</v>
       </c>
     </row>
     <row r="273">
@@ -11565,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>1.450679343407071e-14</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>5.050000190734863</v>
       </c>
       <c r="D274" t="n">
-        <v>5.050000190734863</v>
+        <v>5.010000228881836</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-0.03999996185302734</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.7920784226189633</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>1387</v>
       </c>
       <c r="D275" t="n">
-        <v>1387</v>
+        <v>1383.099975585938</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-3.9000244140625</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-0.2811841682813627</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>620.3499755859375</v>
       </c>
       <c r="D276" t="n">
-        <v>620.3499755859375</v>
+        <v>617.7999877929688</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>-2.54998779296875</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>-0.4110563219673245</v>
       </c>
     </row>
     <row r="277">
@@ -11715,28 +11715,32 @@
         <v>1367.900024414062</v>
       </c>
       <c r="D277" t="n">
-        <v>1367.900024414062</v>
+        <v>1369.699951171875</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>1369.699951171875</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>1.799926757812955</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H277" t="n">
         <v>0.7810046076774597</v>
       </c>
-      <c r="I277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>0.1315832097147561</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11758,13 @@
         <v>291.3999938964844</v>
       </c>
       <c r="D278" t="n">
-        <v>291.3999938964844</v>
+        <v>291.5499877929688</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>0.149993896484375</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.05147354139535712</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11797,13 @@
         <v>808.2999877929688</v>
       </c>
       <c r="D279" t="n">
-        <v>808.2999877929688</v>
+        <v>810.4000244140625</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>2.10003662109375</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>0.2598090625768555</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11836,13 @@
         <v>110.2600021362305</v>
       </c>
       <c r="D280" t="n">
-        <v>110.2600021362305</v>
+        <v>111.2099990844727</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>0.9499969482421591</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>0.8615970704121709</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11875,13 @@
         <v>1223.900024414062</v>
       </c>
       <c r="D281" t="n">
-        <v>1223.900024414062</v>
+        <v>1223</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>-0.9000244140620453</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>-0.0735374128693991</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2076.300048828125</v>
       </c>
       <c r="D272" t="n">
-        <v>2072.199951171875</v>
+        <v>2071.300048828125</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-4.10009765625</v>
+        <v>-5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.1974713461363215</v>
+        <v>-0.2408129789729585</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>5.050000190734863</v>
       </c>
       <c r="D274" t="n">
-        <v>5.010000228881836</v>
+        <v>5.019999980926514</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.03999996185302734</v>
+        <v>-0.03000020980834961</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.7920784226189633</v>
+        <v>-0.5940635381240263</v>
       </c>
     </row>
     <row r="275">
@@ -11676,13 +11676,13 @@
         <v>620.3499755859375</v>
       </c>
       <c r="D276" t="n">
-        <v>617.7999877929688</v>
+        <v>618.25</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-2.54998779296875</v>
+        <v>-2.0999755859375</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.4110563219673245</v>
+        <v>-0.3385146560139727</v>
       </c>
     </row>
     <row r="277">
@@ -11797,13 +11797,13 @@
         <v>808.2999877929688</v>
       </c>
       <c r="D279" t="n">
-        <v>810.4000244140625</v>
+        <v>810.0499877929688</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>2.10003662109375</v>
+        <v>1.75</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.2598090625768555</v>
+        <v>0.2165037766211411</v>
       </c>
     </row>
     <row r="280">
@@ -11836,13 +11836,13 @@
         <v>110.2600021362305</v>
       </c>
       <c r="D280" t="n">
-        <v>111.2099990844727</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.9499969482421591</v>
+        <v>1.019996643066378</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.8615970704121709</v>
+        <v>0.9250830975008802</v>
       </c>
     </row>
     <row r="281">
@@ -11875,13 +11875,13 @@
         <v>1223.900024414062</v>
       </c>
       <c r="D281" t="n">
-        <v>1223</v>
+        <v>1223.199951171875</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.9000244140620453</v>
+        <v>-0.7000732421870453</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.0735374128693991</v>
+        <v>-0.05720019840037203</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2076.300048828125</v>
       </c>
       <c r="D272" t="n">
-        <v>2071.300048828125</v>
+        <v>2071.699951171875</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-5</v>
+        <v>-4.60009765625</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.2408129789729585</v>
+        <v>-0.2215526440336174</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>24.48999977111816</v>
       </c>
       <c r="D273" t="n">
-        <v>24.48999977111816</v>
+        <v>24.47999954223633</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>-0.01000022888183238</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>1.450679343407071e-14</v>
+        <v>-0.04083392803304953</v>
       </c>
     </row>
     <row r="274">
@@ -11637,13 +11637,13 @@
         <v>1387</v>
       </c>
       <c r="D275" t="n">
-        <v>1383.099975585938</v>
+        <v>1383</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-3.9000244140625</v>
+        <v>-4</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.2811841682813627</v>
+        <v>-0.2883922134102379</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>620.3499755859375</v>
       </c>
       <c r="D276" t="n">
-        <v>618.25</v>
+        <v>618.75</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-2.0999755859375</v>
+        <v>-1.5999755859375</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.3385146560139727</v>
+        <v>-0.2579149913605266</v>
       </c>
     </row>
     <row r="277">
@@ -11758,13 +11758,13 @@
         <v>291.3999938964844</v>
       </c>
       <c r="D278" t="n">
-        <v>291.5499877929688</v>
+        <v>292</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.149993896484375</v>
+        <v>0.600006103515625</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.05147354139535712</v>
+        <v>0.2059046383263716</v>
       </c>
     </row>
     <row r="279">
@@ -11797,28 +11797,32 @@
         <v>808.2999877929688</v>
       </c>
       <c r="D279" t="n">
-        <v>810.0499877929688</v>
+        <v>813.4500122070312</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>813.4500122070312</v>
       </c>
       <c r="F279" t="n">
-        <v>1.75</v>
+        <v>5.1500244140625</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H279" t="n">
         <v>0.7122712135314941</v>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.2165037766211411</v>
+        <v>0.6371427059060633</v>
       </c>
     </row>
     <row r="280">
@@ -11836,13 +11840,13 @@
         <v>110.2600021362305</v>
       </c>
       <c r="D280" t="n">
-        <v>111.2799987792969</v>
+        <v>111.1999969482422</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>1.019996643066378</v>
+        <v>0.9399948120116903</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.9250830975008802</v>
+        <v>0.8525256609829286</v>
       </c>
     </row>
     <row r="281">
@@ -11875,13 +11879,13 @@
         <v>1223.900024414062</v>
       </c>
       <c r="D281" t="n">
-        <v>1223.199951171875</v>
+        <v>1222.800048828125</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.7000732421870453</v>
+        <v>-1.099975585937045</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.05720019840037203</v>
+        <v>-0.08987462733842617</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2076.300048828125</v>
       </c>
       <c r="D272" t="n">
-        <v>2071.699951171875</v>
+        <v>2070.39990234375</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-4.60009765625</v>
+        <v>-5.900146484375</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.2215526440336174</v>
+        <v>-0.2841663702558344</v>
       </c>
     </row>
     <row r="273">
@@ -11637,13 +11637,13 @@
         <v>1387</v>
       </c>
       <c r="D275" t="n">
-        <v>1383</v>
+        <v>1385.400024414062</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-4</v>
+        <v>-1.5999755859375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.2883922134102379</v>
+        <v>-0.1153551251577145</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>620.3499755859375</v>
       </c>
       <c r="D276" t="n">
-        <v>618.75</v>
+        <v>617.0499877929688</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-1.5999755859375</v>
+        <v>-3.29998779296875</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.2579149913605266</v>
+        <v>-0.5319558189474936</v>
       </c>
     </row>
     <row r="277">
@@ -11758,13 +11758,13 @@
         <v>291.3999938964844</v>
       </c>
       <c r="D278" t="n">
-        <v>292</v>
+        <v>291.5</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.600006103515625</v>
+        <v>0.100006103515625</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.2059046383263716</v>
+        <v>0.03431918517855245</v>
       </c>
     </row>
     <row r="279">
@@ -11840,13 +11840,13 @@
         <v>110.2600021362305</v>
       </c>
       <c r="D280" t="n">
-        <v>111.1999969482422</v>
+        <v>111.4300003051758</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.9399948120116903</v>
+        <v>1.169998168945284</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.8525256609829286</v>
+        <v>1.061126561107541</v>
       </c>
     </row>
     <row r="281">
@@ -11879,13 +11879,13 @@
         <v>1223.900024414062</v>
       </c>
       <c r="D281" t="n">
-        <v>1222.800048828125</v>
+        <v>1222.199951171875</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-1.099975585937045</v>
+        <v>-1.700073242187045</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.08987462733842617</v>
+        <v>-0.1389062185043218</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2076.300048828125</v>
       </c>
       <c r="D272" t="n">
-        <v>2070.39990234375</v>
+        <v>2069.300048828125</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-5.900146484375</v>
+        <v>-7</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.2841663702558344</v>
+        <v>-0.3371381705621419</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>24.48999977111816</v>
       </c>
       <c r="D273" t="n">
-        <v>24.47999954223633</v>
+        <v>24.36000061035156</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.01000022888183238</v>
+        <v>-0.129999160766598</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.04083392803304953</v>
+        <v>-0.5308254878789758</v>
       </c>
     </row>
     <row r="274">
@@ -11637,13 +11637,13 @@
         <v>1387</v>
       </c>
       <c r="D275" t="n">
-        <v>1385.400024414062</v>
+        <v>1384</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-1.5999755859375</v>
+        <v>-3</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.1153551251577145</v>
+        <v>-0.2162941600576784</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>620.3499755859375</v>
       </c>
       <c r="D276" t="n">
-        <v>617.0499877929688</v>
+        <v>616.2000122070312</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-3.29998779296875</v>
+        <v>-4.14996337890625</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.5319558189474936</v>
+        <v>-0.6689713133278511</v>
       </c>
     </row>
     <row r="277">
@@ -11758,13 +11758,13 @@
         <v>291.3999938964844</v>
       </c>
       <c r="D278" t="n">
-        <v>291.5</v>
+        <v>290.6000061035156</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.100006103515625</v>
+        <v>-0.79998779296875</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.03431918517855245</v>
+        <v>-0.2745325359385334</v>
       </c>
     </row>
     <row r="279">
@@ -11840,13 +11840,13 @@
         <v>110.2600021362305</v>
       </c>
       <c r="D280" t="n">
-        <v>111.4300003051758</v>
+        <v>111.5</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>1.169998168945284</v>
+        <v>1.239997863769503</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>1.061126561107541</v>
+        <v>1.12461258819625</v>
       </c>
     </row>
     <row r="281">
@@ -11879,13 +11879,13 @@
         <v>1223.900024414062</v>
       </c>
       <c r="D281" t="n">
-        <v>1222.199951171875</v>
+        <v>1221.699951171875</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-1.700073242187045</v>
+        <v>-2.200073242187045</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.1389062185043218</v>
+        <v>-0.1797592285562967</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2076.300048828125</v>
       </c>
       <c r="D272" t="n">
-        <v>2069.300048828125</v>
+        <v>2073.60009765625</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-7</v>
+        <v>-2.699951171875</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.3371381705621419</v>
+        <v>-0.1300366569561498</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>24.48999977111816</v>
       </c>
       <c r="D273" t="n">
-        <v>24.36000061035156</v>
+        <v>24.45000076293945</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.129999160766598</v>
+        <v>-0.03999900817870738</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.5308254878789758</v>
+        <v>-0.1633279238568205</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>5.050000190734863</v>
       </c>
       <c r="D274" t="n">
-        <v>5.019999980926514</v>
+        <v>5.039999961853027</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.03000020980834961</v>
+        <v>-0.01000022888183594</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.5940635381240263</v>
+        <v>-0.1980243268145447</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>1387</v>
       </c>
       <c r="D275" t="n">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.2162941600576784</v>
+        <v>0.2883922134102379</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>620.3499755859375</v>
       </c>
       <c r="D276" t="n">
-        <v>616.2000122070312</v>
+        <v>618.8499755859375</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-4.14996337890625</v>
+        <v>-1.5</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.6689713133278511</v>
+        <v>-0.2417989939603381</v>
       </c>
     </row>
     <row r="277">
@@ -11758,13 +11758,13 @@
         <v>291.3999938964844</v>
       </c>
       <c r="D278" t="n">
-        <v>290.6000061035156</v>
+        <v>292.6499938964844</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.79998779296875</v>
+        <v>1.25</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.2745325359385334</v>
+        <v>0.4289636328695478</v>
       </c>
     </row>
     <row r="279">
@@ -11840,13 +11840,13 @@
         <v>110.2600021362305</v>
       </c>
       <c r="D280" t="n">
-        <v>111.5</v>
+        <v>110.9599990844727</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>1.239997863769503</v>
+        <v>0.6999969482421591</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>1.12461258819625</v>
+        <v>0.6348602708870672</v>
       </c>
     </row>
     <row r="281">
@@ -11879,13 +11879,13 @@
         <v>1223.900024414062</v>
       </c>
       <c r="D281" t="n">
-        <v>1221.699951171875</v>
+        <v>1220.900024414062</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-2.200073242187045</v>
+        <v>-2.999999999999545</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.1797592285562967</v>
+        <v>-0.2451180603118122</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,404 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>TCS.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>2076.300048828125</v>
-      </c>
-      <c r="D272" t="n">
-        <v>2073.60009765625</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>-2.699951171875</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.8861837983131409</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>-0.1300366569561498</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>BASML.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>24.48999977111816</v>
-      </c>
-      <c r="D273" t="n">
-        <v>24.45000076293945</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>-0.03999900817870738</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.8738353848457336</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>-0.1633279238568205</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>KRITIKA.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>5.050000190734863</v>
-      </c>
-      <c r="D274" t="n">
-        <v>5.039999961853027</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>-0.01000022888183594</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.870434582233429</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>-0.1980243268145447</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>SUMMITSEC.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>1387</v>
-      </c>
-      <c r="D275" t="n">
-        <v>1391</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>4</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.8668215274810791</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0.2883922134102379</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>IIFL.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>620.3499755859375</v>
-      </c>
-      <c r="D276" t="n">
-        <v>618.8499755859375</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.8119785189628601</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>-0.2417989939603381</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>ALIVUS.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>1367.900024414062</v>
-      </c>
-      <c r="D277" t="n">
-        <v>1369.699951171875</v>
-      </c>
-      <c r="E277" t="n">
-        <v>1369.699951171875</v>
-      </c>
-      <c r="F277" t="n">
-        <v>1.799926757812955</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.7810046076774597</v>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>0.1315832097147561</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>BORANA.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>291.3999938964844</v>
-      </c>
-      <c r="D278" t="n">
-        <v>292.6499938964844</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.748387336730957</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0.4289636328695478</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>GRAPHITE.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>808.2999877929688</v>
-      </c>
-      <c r="D279" t="n">
-        <v>813.4500122070312</v>
-      </c>
-      <c r="E279" t="n">
-        <v>813.4500122070312</v>
-      </c>
-      <c r="F279" t="n">
-        <v>5.1500244140625</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.7122712135314941</v>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>0.6371427059060633</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>REMSONSIND.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>110.2600021362305</v>
-      </c>
-      <c r="D280" t="n">
-        <v>110.9599990844727</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0.6999969482421591</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.6846562623977661</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0.6348602708870672</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>RELIANCE.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>1223.900024414062</v>
-      </c>
-      <c r="D281" t="n">
-        <v>1220.900024414062</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-2.999999999999545</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.6765978932380676</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>-0.2451180603118122</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>IIFL.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>619.2999877929688</v>
+      </c>
+      <c r="D272" t="n">
+        <v>619.2999877929688</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9258819222450256</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>INVENTURE.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>0.8700000047683716</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.8700000047683716</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9199509620666504</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>SUMMITSEC.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1389.599975585938</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1389.599975585938</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.8988993763923645</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>RELAXO.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>295.8500061035156</v>
+      </c>
+      <c r="D275" t="n">
+        <v>295.8500061035156</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.8859909176826477</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>EQUAL50ADD.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>331.260009765625</v>
+      </c>
+      <c r="D276" t="n">
+        <v>331.260009765625</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.7846503257751465</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>BHAGERIA.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>390.1000061035156</v>
+      </c>
+      <c r="D277" t="n">
+        <v>390.1000061035156</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.7622725367546082</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>DODLA.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>1048.400024414062</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1048.400024414062</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.7000704407691956</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>VEDL.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>265.9500122070312</v>
+      </c>
+      <c r="D279" t="n">
+        <v>265.9500122070312</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.6685378551483154</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>IGPL.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>594.7999877929688</v>
+      </c>
+      <c r="D280" t="n">
+        <v>594.7999877929688</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.6228582262992859</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>BAJAJELEC.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>319</v>
+      </c>
+      <c r="D281" t="n">
+        <v>319</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.5970136523246765</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>619.2999877929688</v>
       </c>
       <c r="D272" t="n">
-        <v>619.2999877929688</v>
+        <v>617.1500244140625</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>-2.14996337890625</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>-0.3471602488752156</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>0.8700000047683716</v>
       </c>
       <c r="D273" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>0.009999990463256836</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>1.149424184879083</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1389.599975585938</v>
       </c>
       <c r="D274" t="n">
-        <v>1389.599975585938</v>
+        <v>1389</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-0.5999755859379547</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.04317613676446485</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>295.8500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>295.8500061035156</v>
+        <v>296.4500122070312</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>0.600006103515625</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>0.20280753460782</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>331.260009765625</v>
       </c>
       <c r="D276" t="n">
-        <v>331.260009765625</v>
+        <v>331.1099853515625</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>-0.1500244140625</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>-0.04528902060005557</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>390.1000061035156</v>
       </c>
       <c r="D277" t="n">
-        <v>390.1000061035156</v>
+        <v>393</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>2.899993896484375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>0.7433975521945627</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>1048.400024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1048.400024414062</v>
+        <v>1044</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>-4.400024414062045</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>-0.4196894612360549</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>265.9500122070312</v>
       </c>
       <c r="D279" t="n">
-        <v>265.9500122070312</v>
+        <v>264.7999877929688</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>-1.150024414062443</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>-0.432421267635512</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>594.7999877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>594.7999877929688</v>
+        <v>594</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>-0.79998779296875</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>-0.1344969417260985</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>619.2999877929688</v>
       </c>
       <c r="D272" t="n">
-        <v>617.1500244140625</v>
+        <v>616.75</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-2.14996337890625</v>
+        <v>-2.54998779296875</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.3471602488752156</v>
+        <v>-0.411753244506959</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>1389.599975585938</v>
       </c>
       <c r="D274" t="n">
-        <v>1389</v>
+        <v>1390.699951171875</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.5999755859379547</v>
+        <v>1.099975585937045</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.04317613676446485</v>
+        <v>0.07915771482891903</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>295.8500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>296.4500122070312</v>
+        <v>295.8500061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.600006103515625</v>
+        <v>0</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.20280753460782</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>390.1000061035156</v>
       </c>
       <c r="D277" t="n">
-        <v>393</v>
+        <v>392.7999877929688</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>2.899993896484375</v>
+        <v>2.699981689453125</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.7433975521945627</v>
+        <v>0.6921255183822446</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>1048.400024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1044</v>
+        <v>1043.400024414062</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-4.400024414062045</v>
+        <v>-4.999999999999545</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.4196894612360549</v>
+        <v>-0.4769171960668337</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>265.9500122070312</v>
       </c>
       <c r="D279" t="n">
-        <v>264.7999877929688</v>
+        <v>264.8999938964844</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-1.150024414062443</v>
+        <v>-1.050018310546818</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.432421267635512</v>
+        <v>-0.3948179215458812</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>594.7999877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>594</v>
+        <v>593.7000122070312</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.79998779296875</v>
+        <v>-1.0999755859375</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.1344969417260985</v>
+        <v>-0.1849320121910236</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>619.2999877929688</v>
       </c>
       <c r="D272" t="n">
-        <v>616.75</v>
+        <v>617.7999877929688</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-2.54998779296875</v>
+        <v>-1.5</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.411753244506959</v>
+        <v>-0.2422089503579077</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>0.8700000047683716</v>
       </c>
       <c r="D273" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.009999990463256836</v>
+        <v>0</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>1.149424184879083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1389.599975585938</v>
       </c>
       <c r="D274" t="n">
-        <v>1390.699951171875</v>
+        <v>1385.300048828125</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>1.099975585937045</v>
+        <v>-4.299926757812955</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.07915771482891903</v>
+        <v>-0.3094363006159273</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>295.8500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>295.8500061035156</v>
+        <v>296.3500061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>0.1690045596365659</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>331.260009765625</v>
       </c>
       <c r="D276" t="n">
-        <v>331.1099853515625</v>
+        <v>331.260009765625</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.1500244140625</v>
+        <v>0</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.04528902060005557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>390.1000061035156</v>
       </c>
       <c r="D277" t="n">
-        <v>392.7999877929688</v>
+        <v>393.1000061035156</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>2.699981689453125</v>
+        <v>3</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.6921255183822446</v>
+        <v>0.7690335691007218</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>1048.400024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1043.400024414062</v>
+        <v>1042.599975585938</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-4.999999999999545</v>
+        <v>-5.800048828124545</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.4769171960668337</v>
+        <v>-0.553228604832027</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>265.9500122070312</v>
       </c>
       <c r="D279" t="n">
-        <v>264.8999938964844</v>
+        <v>265.4500122070312</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-1.050018310546818</v>
+        <v>-0.4999999999999432</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.3948179215458812</v>
+        <v>-0.1880052555179857</v>
       </c>
     </row>
     <row r="280">
@@ -11832,28 +11832,32 @@
         <v>594.7999877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>593.7000122070312</v>
+        <v>592.2000122070312</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>592.2000122070312</v>
       </c>
       <c r="F280" t="n">
-        <v>-1.0999755859375</v>
+        <v>-2.5999755859375</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H280" t="n">
         <v>0.6228582262992859</v>
       </c>
-      <c r="I280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.1849320121910236</v>
+        <v>-0.4371176259745436</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>619.2999877929688</v>
       </c>
       <c r="D272" t="n">
-        <v>617.7999877929688</v>
+        <v>618.2000122070312</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-1.5</v>
+        <v>-1.0999755859375</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.2422089503579077</v>
+        <v>-0.1776159547261642</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>0.8700000047683716</v>
       </c>
       <c r="D273" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>0.009999990463256836</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>1.149424184879083</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1389.599975585938</v>
       </c>
       <c r="D274" t="n">
-        <v>1385.300048828125</v>
+        <v>1376</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-4.299926757812955</v>
+        <v>-13.59997558593795</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.3094363006159273</v>
+        <v>-0.9786971664419752</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>295.8500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>296.3500061035156</v>
+        <v>297.8999938964844</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.5</v>
+        <v>2.04998779296875</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.1690045596365659</v>
+        <v>0.6929145684220386</v>
       </c>
     </row>
     <row r="276">
@@ -11676,28 +11676,32 @@
         <v>331.260009765625</v>
       </c>
       <c r="D276" t="n">
-        <v>331.260009765625</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>0.079986572265625</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H276" t="n">
         <v>0.7846503257751465</v>
       </c>
-      <c r="I276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.024146160088028</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11719,13 @@
         <v>390.1000061035156</v>
       </c>
       <c r="D277" t="n">
-        <v>393.1000061035156</v>
+        <v>394.7999877929688</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>3</v>
+        <v>4.699981689453125</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.7690335691007218</v>
+        <v>1.204814564449392</v>
       </c>
     </row>
     <row r="278">
@@ -11793,13 +11797,13 @@
         <v>265.9500122070312</v>
       </c>
       <c r="D279" t="n">
-        <v>265.4500122070312</v>
+        <v>265.7999877929688</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.4999999999999432</v>
+        <v>-0.1500244140624432</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.1880052555179857</v>
+        <v>-0.05641075659949784</v>
       </c>
     </row>
     <row r="280">
@@ -11875,13 +11879,13 @@
         <v>319</v>
       </c>
       <c r="D281" t="n">
-        <v>319</v>
+        <v>318.9500122070312</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>-0.04998779296875</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>-0.01567015453565831</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>619.2999877929688</v>
       </c>
       <c r="D272" t="n">
-        <v>618.2000122070312</v>
+        <v>616.2999877929688</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-1.0999755859375</v>
+        <v>-3</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.1776159547261642</v>
+        <v>-0.4844179007158154</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>1389.599975585938</v>
       </c>
       <c r="D274" t="n">
-        <v>1376</v>
+        <v>1389.800048828125</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-13.59997558593795</v>
+        <v>0.2000732421870453</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.9786971664419752</v>
+        <v>0.01439790196474942</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>295.8500061035156</v>
       </c>
       <c r="D275" t="n">
-        <v>297.8999938964844</v>
+        <v>296.8500061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>2.04998779296875</v>
+        <v>1</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.6929145684220386</v>
+        <v>0.3380091192731319</v>
       </c>
     </row>
     <row r="276">
@@ -11719,13 +11719,13 @@
         <v>390.1000061035156</v>
       </c>
       <c r="D277" t="n">
-        <v>394.7999877929688</v>
+        <v>394</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>4.699981689453125</v>
+        <v>3.899993896484375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>1.204814564449392</v>
+        <v>0.9997420752281367</v>
       </c>
     </row>
     <row r="278">
@@ -11758,13 +11758,13 @@
         <v>1048.400024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1042.599975585938</v>
+        <v>1042.099975585938</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-5.800048828124545</v>
+        <v>-6.300048828124545</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.553228604832027</v>
+        <v>-0.6009203244387146</v>
       </c>
     </row>
     <row r="279">
@@ -11879,13 +11879,13 @@
         <v>319</v>
       </c>
       <c r="D281" t="n">
-        <v>318.9500122070312</v>
+        <v>318.6000061035156</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.04998779296875</v>
+        <v>-0.399993896484375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.01567015453565831</v>
+        <v>-0.1253899362019984</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,404 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>IIFL.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>619.2999877929688</v>
-      </c>
-      <c r="D272" t="n">
-        <v>616.2999877929688</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9258819222450256</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>-0.4844179007158154</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>INVENTURE.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>0.8700000047683716</v>
-      </c>
-      <c r="D273" t="n">
-        <v>0.8799999952316284</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>0.009999990463256836</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9199509620666504</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>1.149424184879083</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>SUMMITSEC.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>1389.599975585938</v>
-      </c>
-      <c r="D274" t="n">
-        <v>1389.800048828125</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0.2000732421870453</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.8988993763923645</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0.01439790196474942</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>RELAXO.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>295.8500061035156</v>
-      </c>
-      <c r="D275" t="n">
-        <v>296.8500061035156</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>1</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.8859909176826477</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0.3380091192731319</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>EQUAL50ADD.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>331.260009765625</v>
-      </c>
-      <c r="D276" t="n">
-        <v>331.3399963378906</v>
-      </c>
-      <c r="E276" t="n">
-        <v>331.3399963378906</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0.079986572265625</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.7846503257751465</v>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0.024146160088028</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>BHAGERIA.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>390.1000061035156</v>
-      </c>
-      <c r="D277" t="n">
-        <v>394</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>3.899993896484375</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.7622725367546082</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>0.9997420752281367</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>DODLA.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>1048.400024414062</v>
-      </c>
-      <c r="D278" t="n">
-        <v>1042.099975585938</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>-6.300048828124545</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.7000704407691956</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>-0.6009203244387146</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>VEDL.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>265.9500122070312</v>
-      </c>
-      <c r="D279" t="n">
-        <v>265.7999877929688</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-0.1500244140624432</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.6685378551483154</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-0.05641075659949784</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>IGPL.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>594.7999877929688</v>
-      </c>
-      <c r="D280" t="n">
-        <v>592.2000122070312</v>
-      </c>
-      <c r="E280" t="n">
-        <v>592.2000122070312</v>
-      </c>
-      <c r="F280" t="n">
-        <v>-2.5999755859375</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.6228582262992859</v>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>-0.4371176259745436</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>BAJAJELEC.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>319</v>
-      </c>
-      <c r="D281" t="n">
-        <v>318.6000061035156</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-0.399993896484375</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.5970136523246765</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>-0.1253899362019984</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ALLDIGI.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>756.3499755859375</v>
+      </c>
+      <c r="D272" t="n">
+        <v>756.3499755859375</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9731022119522095</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>MUFTI.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>70.23999786376953</v>
+      </c>
+      <c r="D273" t="n">
+        <v>70.23999786376953</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9554929733276367</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>MANGALAM.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>29.14999961853027</v>
+      </c>
+      <c r="D274" t="n">
+        <v>29.14999961853027</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9240130186080933</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>GABRIEL.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1315</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1315</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9122010469436646</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>INVENTURE.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>0.8500000238418579</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.8500000238418579</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.9081759452819824</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>SJS.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>2159.800048828125</v>
+      </c>
+      <c r="D277" t="n">
+        <v>2159.800048828125</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.8269456028938293</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>CONFIPET.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>86.05000305175781</v>
+      </c>
+      <c r="D278" t="n">
+        <v>86.05000305175781</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.7555005550384521</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>BOHRAIND.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>14.73999977111816</v>
+      </c>
+      <c r="D279" t="n">
+        <v>14.73999977111816</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.7528395652770996</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ASHOKAMET.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>14.52999973297119</v>
+      </c>
+      <c r="D280" t="n">
+        <v>14.52999973297119</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.7401092052459717</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>IMFA.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>1176.800048828125</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1176.800048828125</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.5849515795707703</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,396 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>ALLDIGI.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>756.3499755859375</v>
-      </c>
-      <c r="D272" t="n">
-        <v>756.3499755859375</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9731022119522095</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>MUFTI.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>70.23999786376953</v>
-      </c>
-      <c r="D273" t="n">
-        <v>70.23999786376953</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9554929733276367</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>MANGALAM.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>29.14999961853027</v>
-      </c>
-      <c r="D274" t="n">
-        <v>29.14999961853027</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9240130186080933</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>GABRIEL.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>1315</v>
-      </c>
-      <c r="D275" t="n">
-        <v>1315</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9122010469436646</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>INVENTURE.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>0.8500000238418579</v>
-      </c>
-      <c r="D276" t="n">
-        <v>0.8500000238418579</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.9081759452819824</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>SJS.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>2159.800048828125</v>
-      </c>
-      <c r="D277" t="n">
-        <v>2159.800048828125</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.8269456028938293</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>CONFIPET.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>86.05000305175781</v>
-      </c>
-      <c r="D278" t="n">
-        <v>86.05000305175781</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.7555005550384521</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>BOHRAIND.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>14.73999977111816</v>
-      </c>
-      <c r="D279" t="n">
-        <v>14.73999977111816</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.7528395652770996</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>ASHOKAMET.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>14.52999973297119</v>
-      </c>
-      <c r="D280" t="n">
-        <v>14.52999973297119</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.7401092052459717</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>IMFA.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>1176.800048828125</v>
-      </c>
-      <c r="D281" t="n">
-        <v>1176.800048828125</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.5849515795707703</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>PRSMJOHNSN.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>97.47000122070312</v>
+      </c>
+      <c r="D272" t="n">
+        <v>97.47000122070312</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9887386560440063</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>DPABHUSHAN.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2363.800048828125</v>
+      </c>
+      <c r="D273" t="n">
+        <v>2363.800048828125</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9739829301834106</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>FINCABLES.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1388.699951171875</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1388.699951171875</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9711943864822388</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ASHOKLEY.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>145.0599975585938</v>
+      </c>
+      <c r="D275" t="n">
+        <v>145.0599975585938</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9438129067420959</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>REPL.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>56.65999984741211</v>
+      </c>
+      <c r="D276" t="n">
+        <v>56.65999984741211</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.9357903599739075</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>CARRARO.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>508.5</v>
+      </c>
+      <c r="D277" t="n">
+        <v>508.5</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.9047292470932007</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>2460.800048828125</v>
+      </c>
+      <c r="D278" t="n">
+        <v>2460.800048828125</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.8619181513786316</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SONACOMS.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>783.2999877929688</v>
+      </c>
+      <c r="D279" t="n">
+        <v>783.2999877929688</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.8560822606086731</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>AMJLAND.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>36.2599983215332</v>
+      </c>
+      <c r="D280" t="n">
+        <v>36.2599983215332</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.8239243626594543</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>BHAGERIA.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>364.8999938964844</v>
+      </c>
+      <c r="D281" t="n">
+        <v>364.8999938964844</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.8027164936065674</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>97.47000122070312</v>
       </c>
       <c r="D272" t="n">
-        <v>97.47000122070312</v>
+        <v>97.76000213623047</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>0.2900009155273438</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.297528379907054</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>2363.800048828125</v>
       </c>
       <c r="D273" t="n">
-        <v>2363.800048828125</v>
+        <v>2370.10009765625</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>6.300048828125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>0.2665220703099784</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1388.699951171875</v>
       </c>
       <c r="D274" t="n">
-        <v>1388.699951171875</v>
+        <v>1442</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>53.300048828125</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>3.838125635645552</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>145.0599975585938</v>
       </c>
       <c r="D275" t="n">
-        <v>145.0599975585938</v>
+        <v>144.25</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-0.8099975585938068</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-0.5583879582423308</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>56.65999984741211</v>
       </c>
       <c r="D276" t="n">
-        <v>56.65999984741211</v>
+        <v>57.09000015258789</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>0.4300003051757812</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.7589133539247991</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>508.5</v>
       </c>
       <c r="D277" t="n">
-        <v>508.5</v>
+        <v>505.2000122070312</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-3.29998779296875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.6489651510263029</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>2460.800048828125</v>
       </c>
       <c r="D278" t="n">
-        <v>2460.800048828125</v>
+        <v>2428</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>-32.800048828125</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>-1.332901827750895</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>783.2999877929688</v>
       </c>
       <c r="D279" t="n">
-        <v>783.2999877929688</v>
+        <v>798</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>14.70001220703125</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>1.876677190874227</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>36.2599983215332</v>
       </c>
       <c r="D280" t="n">
-        <v>36.2599983215332</v>
+        <v>36.47000122070312</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>0.2100028991699219</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>0.5791586014641663</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>364.8999938964844</v>
       </c>
       <c r="D281" t="n">
-        <v>364.8999938964844</v>
+        <v>380.3500061035156</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>15.45001220703125</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>4.234040138519197</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,396 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>PRSMJOHNSN.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>97.47000122070312</v>
-      </c>
-      <c r="D272" t="n">
-        <v>97.76000213623047</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>0.2900009155273438</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9887386560440063</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.297528379907054</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>DPABHUSHAN.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>2363.800048828125</v>
-      </c>
-      <c r="D273" t="n">
-        <v>2370.10009765625</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>6.300048828125</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9739829301834106</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0.2665220703099784</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>FINCABLES.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>1388.699951171875</v>
-      </c>
-      <c r="D274" t="n">
-        <v>1442</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>53.300048828125</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9711943864822388</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>3.838125635645552</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>ASHOKLEY.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>145.0599975585938</v>
-      </c>
-      <c r="D275" t="n">
-        <v>144.25</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-0.8099975585938068</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9438129067420959</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-0.5583879582423308</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>REPL.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>56.65999984741211</v>
-      </c>
-      <c r="D276" t="n">
-        <v>57.09000015258789</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0.4300003051757812</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.9357903599739075</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0.7589133539247991</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>CARRARO.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>508.5</v>
-      </c>
-      <c r="D277" t="n">
-        <v>505.2000122070312</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>-3.29998779296875</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.9047292470932007</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>-0.6489651510263029</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>CAPLIPOINT.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>2460.800048828125</v>
-      </c>
-      <c r="D278" t="n">
-        <v>2428</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>-32.800048828125</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.8619181513786316</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>-1.332901827750895</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>SONACOMS.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>783.2999877929688</v>
-      </c>
-      <c r="D279" t="n">
-        <v>798</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>14.70001220703125</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.8560822606086731</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>1.876677190874227</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>AMJLAND.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>36.2599983215332</v>
-      </c>
-      <c r="D280" t="n">
-        <v>36.47000122070312</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0.2100028991699219</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.8239243626594543</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0.5791586014641663</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>BHAGERIA.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>364.8999938964844</v>
-      </c>
-      <c r="D281" t="n">
-        <v>380.3500061035156</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>15.45001220703125</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.8027164936065674</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>4.234040138519197</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>BHAGYANGR.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>50.20000076293945</v>
+      </c>
+      <c r="D272" t="n">
+        <v>50.20000076293945</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.963873565196991</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>PRSMJOHNSN.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>98.86000061035156</v>
+      </c>
+      <c r="D273" t="n">
+        <v>98.86000061035156</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9328135251998901</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>FINCABLES.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1452.900024414062</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1452.900024414062</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9217203259468079</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ACUTAAS.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>3173.5</v>
+      </c>
+      <c r="D275" t="n">
+        <v>3173.5</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9105457067489624</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>TIRUMALCHM.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>142.5299987792969</v>
+      </c>
+      <c r="D276" t="n">
+        <v>142.5299987792969</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.8861793875694275</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>KOPRAN.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>278.4500122070312</v>
+      </c>
+      <c r="D277" t="n">
+        <v>278.4500122070312</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.881228506565094</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>HINDOILEXP.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>176.5500030517578</v>
+      </c>
+      <c r="D278" t="n">
+        <v>176.5500030517578</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.8534770011901855</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>MOTOUR.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>74.33999633789062</v>
+      </c>
+      <c r="D279" t="n">
+        <v>74.33999633789062</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.7550492882728577</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SYRMA.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1688.599975585938</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1688.599975585938</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.7318592071533203</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>MAXIND.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>160.1999969482422</v>
+      </c>
+      <c r="D281" t="n">
+        <v>160.1999969482422</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.6710360050201416</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>98.86000061035156</v>
       </c>
       <c r="D273" t="n">
-        <v>98.86000061035156</v>
+        <v>98.90000152587891</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>0.04000091552734375</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>0.04046218418003457</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1452.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1452.900024414062</v>
+        <v>1450.599975585938</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-2.300048828124545</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.1583074395674354</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>3173.5</v>
       </c>
       <c r="D275" t="n">
-        <v>3173.5</v>
+        <v>3153.5</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-0.6302190011028832</v>
       </c>
     </row>
     <row r="276">
@@ -11676,28 +11676,32 @@
         <v>142.5299987792969</v>
       </c>
       <c r="D276" t="n">
-        <v>142.5299987792969</v>
+        <v>141.6699981689453</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>141.6699981689453</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>-0.8600006103515909</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H276" t="n">
         <v>0.8861793875694275</v>
       </c>
-      <c r="I276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>-0.6033821775886451</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11719,13 @@
         <v>278.4500122070312</v>
       </c>
       <c r="D277" t="n">
-        <v>278.4500122070312</v>
+        <v>281.2000122070312</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>2.750000000000057</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>0.9876099405430789</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11758,13 @@
         <v>176.5500030517578</v>
       </c>
       <c r="D278" t="n">
-        <v>176.5500030517578</v>
+        <v>175.8000030517578</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>-0.4248088286807496</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11797,13 @@
         <v>74.33999633789062</v>
       </c>
       <c r="D279" t="n">
-        <v>74.33999633789062</v>
+        <v>74.27999877929688</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>-0.05999755859375</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>-0.08070697006904429</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11836,13 @@
         <v>1688.599975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1688.599975585938</v>
+        <v>1679.300048828125</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>-9.299926757812955</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>-0.5507477728457217</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11875,13 @@
         <v>160.1999969482422</v>
       </c>
       <c r="D281" t="n">
-        <v>160.1999969482422</v>
+        <v>159.1000061035156</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>-1.099990844726562</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>-0.6866359960555745</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>98.86000061035156</v>
       </c>
       <c r="D273" t="n">
-        <v>98.90000152587891</v>
+        <v>98.73000335693359</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.04000091552734375</v>
+        <v>-0.1299972534179688</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.04046218418003457</v>
+        <v>-0.1314963105557141</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1452.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1450.599975585938</v>
+        <v>1450.900024414062</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-2.300048828124545</v>
+        <v>-1.999999999999545</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.1583074395674354</v>
+        <v>-0.1376557207235317</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>3173.5</v>
       </c>
       <c r="D275" t="n">
-        <v>3153.5</v>
+        <v>3158.300048828125</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-20</v>
+        <v>-15.199951171875</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.6302190011028832</v>
+        <v>-0.4789649022175831</v>
       </c>
     </row>
     <row r="276">
@@ -11719,13 +11719,13 @@
         <v>278.4500122070312</v>
       </c>
       <c r="D277" t="n">
-        <v>281.2000122070312</v>
+        <v>281.3999938964844</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>2.750000000000057</v>
+        <v>2.949981689453182</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.9876099405430789</v>
+        <v>1.05942954215417</v>
       </c>
     </row>
     <row r="278">
@@ -11758,13 +11758,13 @@
         <v>176.5500030517578</v>
       </c>
       <c r="D278" t="n">
-        <v>175.8000030517578</v>
+        <v>175.7799987792969</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.75</v>
+        <v>-0.7700042724609375</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.4248088286807496</v>
+        <v>-0.4361394840844048</v>
       </c>
     </row>
     <row r="279">
@@ -11836,13 +11836,13 @@
         <v>1688.599975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1679.300048828125</v>
+        <v>1682.300048828125</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-9.299926757812955</v>
+        <v>-6.299926757812955</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.5507477728457217</v>
+        <v>-0.3730858017824443</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>98.86000061035156</v>
       </c>
       <c r="D273" t="n">
-        <v>98.73000335693359</v>
+        <v>99</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.1299972534179688</v>
+        <v>0.1399993896484375</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.1314963105557141</v>
+        <v>0.1416137859438555</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1452.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1450.900024414062</v>
+        <v>1445.900024414062</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-1.999999999999545</v>
+        <v>-6.999999999999545</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.1376557207235317</v>
+        <v>-0.4817950225324392</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>3173.5</v>
       </c>
       <c r="D275" t="n">
-        <v>3158.300048828125</v>
+        <v>3160</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-15.199951171875</v>
+        <v>-13.5</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.4789649022175831</v>
+        <v>-0.4253978257444462</v>
       </c>
     </row>
     <row r="276">
@@ -11719,13 +11719,13 @@
         <v>278.4500122070312</v>
       </c>
       <c r="D277" t="n">
-        <v>281.3999938964844</v>
+        <v>283.1499938964844</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>2.949981689453182</v>
+        <v>4.699981689453182</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>1.05942954215417</v>
+        <v>1.687908595227026</v>
       </c>
     </row>
     <row r="278">
@@ -11758,13 +11758,13 @@
         <v>176.5500030517578</v>
       </c>
       <c r="D278" t="n">
-        <v>175.7799987792969</v>
+        <v>175.8000030517578</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.7700042724609375</v>
+        <v>-0.75</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.4361394840844048</v>
+        <v>-0.4248088286807496</v>
       </c>
     </row>
     <row r="279">
@@ -11797,13 +11797,13 @@
         <v>74.33999633789062</v>
       </c>
       <c r="D279" t="n">
-        <v>74.27999877929688</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.05999755859375</v>
+        <v>-0.4399948120117188</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.08070697006904429</v>
+        <v>-0.5918682185722091</v>
       </c>
     </row>
     <row r="280">
@@ -11836,13 +11836,13 @@
         <v>1688.599975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1682.300048828125</v>
+        <v>1693.300048828125</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-6.299926757812955</v>
+        <v>4.700073242187045</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.3730858017824443</v>
+        <v>0.2783414254495732</v>
       </c>
     </row>
     <row r="281">
@@ -11875,13 +11875,13 @@
         <v>160.1999969482422</v>
       </c>
       <c r="D281" t="n">
-        <v>159.1000061035156</v>
+        <v>159.8000030517578</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-1.099990844726562</v>
+        <v>-0.399993896484375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.6866359960555745</v>
+        <v>-0.2496840849588818</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>98.86000061035156</v>
       </c>
       <c r="D273" t="n">
-        <v>99</v>
+        <v>98.98999786376953</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.1399993896484375</v>
+        <v>0.1299972534179688</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.1416137859438555</v>
+        <v>0.1314963105557141</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1452.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1445.900024414062</v>
+        <v>1447</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-6.999999999999545</v>
+        <v>-5.900024414062045</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.4817950225324392</v>
+        <v>-0.4060860565021642</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>3173.5</v>
       </c>
       <c r="D275" t="n">
-        <v>3160</v>
+        <v>3158</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-13.5</v>
+        <v>-15.5</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.4253978257444462</v>
+        <v>-0.4884197258547345</v>
       </c>
     </row>
     <row r="276">
@@ -11719,13 +11719,13 @@
         <v>278.4500122070312</v>
       </c>
       <c r="D277" t="n">
-        <v>283.1499938964844</v>
+        <v>284.1499938964844</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>4.699981689453182</v>
+        <v>5.699981689453182</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>1.687908595227026</v>
+        <v>2.047039482697229</v>
       </c>
     </row>
     <row r="278">
@@ -11758,13 +11758,13 @@
         <v>176.5500030517578</v>
       </c>
       <c r="D278" t="n">
-        <v>175.8000030517578</v>
+        <v>175.4400024414062</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.75</v>
+        <v>-1.110000610351562</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.4248088286807496</v>
+        <v>-0.6287174121578192</v>
       </c>
     </row>
     <row r="279">
@@ -11797,28 +11797,32 @@
         <v>74.33999633789062</v>
       </c>
       <c r="D279" t="n">
-        <v>73.90000152587891</v>
+        <v>75.29000091552734</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>75.29000091552734</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.4399948120117188</v>
+        <v>0.9500045776367188</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H279" t="n">
         <v>0.7550492882728577</v>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.5918682185722091</v>
+        <v>1.277918515517208</v>
       </c>
     </row>
     <row r="280">
@@ -11836,13 +11840,13 @@
         <v>1688.599975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1693.300048828125</v>
+        <v>1688.599975585938</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>4.700073242187045</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.2783414254495732</v>
+        <v>-2.69304368980977e-14</v>
       </c>
     </row>
     <row r="281">
@@ -11875,13 +11879,13 @@
         <v>160.1999969482422</v>
       </c>
       <c r="D281" t="n">
-        <v>159.8000030517578</v>
+        <v>159.8200073242188</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.399993896484375</v>
+        <v>-0.3799896240234375</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.2496840849588818</v>
+        <v>-0.2371970232597479</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>98.86000061035156</v>
       </c>
       <c r="D273" t="n">
-        <v>98.98999786376953</v>
+        <v>98.65000152587891</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.1299972534179688</v>
+        <v>-0.2099990844726562</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.1314963105557141</v>
+        <v>-0.2124206789157832</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1452.900024414062</v>
       </c>
       <c r="D274" t="n">
-        <v>1447</v>
+        <v>1445.800048828125</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-5.900024414062045</v>
+        <v>-7.099975585937045</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.4060860565021642</v>
+        <v>-0.4886761282009327</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>3173.5</v>
       </c>
       <c r="D275" t="n">
-        <v>3158</v>
+        <v>3158.89990234375</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-15.5</v>
+        <v>-14.60009765625</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.4884197258547345</v>
+        <v>-0.4600629480463211</v>
       </c>
     </row>
     <row r="276">
@@ -11719,13 +11719,13 @@
         <v>278.4500122070312</v>
       </c>
       <c r="D277" t="n">
-        <v>284.1499938964844</v>
+        <v>284.6000061035156</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>5.699981689453182</v>
+        <v>6.149993896484432</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>2.047039482697229</v>
+        <v>2.208652765980786</v>
       </c>
     </row>
     <row r="278">
@@ -11758,13 +11758,13 @@
         <v>176.5500030517578</v>
       </c>
       <c r="D278" t="n">
-        <v>175.4400024414062</v>
+        <v>175.3000030517578</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-1.110000610351562</v>
+        <v>-1.25</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.6287174121578192</v>
+        <v>-0.708014714467916</v>
       </c>
     </row>
     <row r="279">
@@ -11840,13 +11840,13 @@
         <v>1688.599975585938</v>
       </c>
       <c r="D280" t="n">
-        <v>1688.599975585938</v>
+        <v>1693.099975585938</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>4.499999999999545</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-2.69304368980977e-14</v>
+        <v>0.2664929565948893</v>
       </c>
     </row>
     <row r="281">
@@ -11879,13 +11879,13 @@
         <v>160.1999969482422</v>
       </c>
       <c r="D281" t="n">
-        <v>159.8200073242188</v>
+        <v>160.7899932861328</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.3799896240234375</v>
+        <v>0.589996337890625</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.2371970232597479</v>
+        <v>0.3682873590074053</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,404 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>BHAGYANGR.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>50.20000076293945</v>
-      </c>
-      <c r="D272" t="n">
-        <v>50.20000076293945</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.963873565196991</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>PRSMJOHNSN.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>98.86000061035156</v>
-      </c>
-      <c r="D273" t="n">
-        <v>98.65000152587891</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>-0.2099990844726562</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9328135251998901</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>-0.2124206789157832</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>FINCABLES.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>1452.900024414062</v>
-      </c>
-      <c r="D274" t="n">
-        <v>1445.800048828125</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>-7.099975585937045</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9217203259468079</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>-0.4886761282009327</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>ACUTAAS.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>3173.5</v>
-      </c>
-      <c r="D275" t="n">
-        <v>3158.89990234375</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-14.60009765625</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9105457067489624</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-0.4600629480463211</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>TIRUMALCHM.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>142.5299987792969</v>
-      </c>
-      <c r="D276" t="n">
-        <v>141.6699981689453</v>
-      </c>
-      <c r="E276" t="n">
-        <v>141.6699981689453</v>
-      </c>
-      <c r="F276" t="n">
-        <v>-0.8600006103515909</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.8861793875694275</v>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>-0.6033821775886451</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>KOPRAN.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>278.4500122070312</v>
-      </c>
-      <c r="D277" t="n">
-        <v>284.6000061035156</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>6.149993896484432</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.881228506565094</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>2.208652765980786</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>HINDOILEXP.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>176.5500030517578</v>
-      </c>
-      <c r="D278" t="n">
-        <v>175.3000030517578</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.8534770011901855</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>-0.708014714467916</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>MOTOUR.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>74.33999633789062</v>
-      </c>
-      <c r="D279" t="n">
-        <v>75.29000091552734</v>
-      </c>
-      <c r="E279" t="n">
-        <v>75.29000091552734</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0.9500045776367188</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.7550492882728577</v>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>1.277918515517208</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>SYRMA.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>1688.599975585938</v>
-      </c>
-      <c r="D280" t="n">
-        <v>1693.099975585938</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>4.499999999999545</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.7318592071533203</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0.2664929565948893</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>MAXIND.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>160.1999969482422</v>
-      </c>
-      <c r="D281" t="n">
-        <v>160.7899932861328</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>0.589996337890625</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.6710360050201416</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>0.3682873590074053</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>HITECHCORP.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>411.4500122070312</v>
+      </c>
+      <c r="D272" t="n">
+        <v>411.4500122070312</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9846413731575012</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>GLOSTERLTD.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>538.4000244140625</v>
+      </c>
+      <c r="D273" t="n">
+        <v>538.4000244140625</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9778445959091187</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>GEEKAYWIRE.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>29.30999946594238</v>
+      </c>
+      <c r="D274" t="n">
+        <v>29.30999946594238</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9672104120254517</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>AROGRANITE.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>23.45000076293945</v>
+      </c>
+      <c r="D275" t="n">
+        <v>23.45000076293945</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9535797834396362</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ARVINDFASN.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>395.7000122070312</v>
+      </c>
+      <c r="D276" t="n">
+        <v>395.7000122070312</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.9422463178634644</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>KSHITIJPOL.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>3.430000066757202</v>
+      </c>
+      <c r="D277" t="n">
+        <v>3.430000066757202</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.8854528069496155</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>CENTEXT.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>19.32999992370605</v>
+      </c>
+      <c r="D278" t="n">
+        <v>19.32999992370605</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.8301858305931091</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ICIL.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>440.5</v>
+      </c>
+      <c r="D279" t="n">
+        <v>440.5</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.791745126247406</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SSDL.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>71.08000183105469</v>
+      </c>
+      <c r="D280" t="n">
+        <v>71.08000183105469</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.5371690988540649</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>TORNTPOWER.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>1235.199951171875</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1235.199951171875</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.4373399019241333</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11526,7 +11526,7 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>1.381538878949063e-14</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>29.30999946594238</v>
       </c>
       <c r="D274" t="n">
-        <v>29.30999946594238</v>
+        <v>29.43000030517578</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>0.120000839233402</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>0.4094194521321657</v>
       </c>
     </row>
     <row r="275">
@@ -11643,7 +11643,7 @@
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>1.515016444867343e-14</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>395.7000122070312</v>
       </c>
       <c r="D276" t="n">
-        <v>395.7000122070312</v>
+        <v>396.8500061035156</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>1.149993896484432</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.290622658834479</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>3.430000066757202</v>
       </c>
       <c r="D277" t="n">
-        <v>3.430000066757202</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-0.06000018119812012</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-1.749276385724552</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>19.32999992370605</v>
       </c>
       <c r="D278" t="n">
-        <v>19.32999992370605</v>
+        <v>19.11000061035156</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>-0.2199993133544886</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>-1.138123715586178</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>440.5</v>
       </c>
       <c r="D279" t="n">
-        <v>440.5</v>
+        <v>437.9500122070312</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>-2.54998779296875</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>-0.57888485651958</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>71.08000183105469</v>
       </c>
       <c r="D280" t="n">
-        <v>71.08000183105469</v>
+        <v>71.5</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>0.4199981689453125</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>0.5908809202672478</v>
       </c>
     </row>
     <row r="281">
@@ -11871,28 +11871,32 @@
         <v>1235.199951171875</v>
       </c>
       <c r="D281" t="n">
-        <v>1235.199951171875</v>
+        <v>1240</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>1240</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>4.800048828125</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H281" t="n">
         <v>0.4373399019241333</v>
       </c>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>0.3886050046853576</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11676,13 +11676,13 @@
         <v>395.7000122070312</v>
       </c>
       <c r="D276" t="n">
-        <v>396.8500061035156</v>
+        <v>396.9500122070312</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>1.149993896484432</v>
+        <v>1.250000000000057</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.290622658834479</v>
+        <v>0.3158958709725928</v>
       </c>
     </row>
     <row r="277">
@@ -11793,13 +11793,13 @@
         <v>440.5</v>
       </c>
       <c r="D279" t="n">
-        <v>437.9500122070312</v>
+        <v>438.3500061035156</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-2.54998779296875</v>
+        <v>-2.149993896484375</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.57888485651958</v>
+        <v>-0.4880803397240352</v>
       </c>
     </row>
     <row r="280">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>538.4000244140625</v>
       </c>
       <c r="D273" t="n">
-        <v>538.4000244140625</v>
+        <v>537</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-1.4000244140625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-0.2600342404490301</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>29.30999946594238</v>
       </c>
       <c r="D274" t="n">
-        <v>29.43000030517578</v>
+        <v>29.34000015258789</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.120000839233402</v>
+        <v>0.03000068664551137</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.4094194521321657</v>
+        <v>0.1023564899084067</v>
       </c>
     </row>
     <row r="275">
@@ -11676,13 +11676,13 @@
         <v>395.7000122070312</v>
       </c>
       <c r="D276" t="n">
-        <v>396.9500122070312</v>
+        <v>398.7000122070312</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>1.250000000000057</v>
+        <v>3.000000000000057</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.3158958709725928</v>
+        <v>0.7581500903342024</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>3.430000066757202</v>
       </c>
       <c r="D277" t="n">
-        <v>3.369999885559082</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.06000018119812012</v>
+        <v>-0.01999998092651367</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-1.749276385724552</v>
+        <v>-0.5830898115819017</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>19.32999992370605</v>
       </c>
       <c r="D278" t="n">
-        <v>19.11000061035156</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.2199993133544886</v>
+        <v>-0.2299995422363246</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-1.138123715586178</v>
+        <v>-1.189857957289779</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>440.5</v>
       </c>
       <c r="D279" t="n">
-        <v>438.3500061035156</v>
+        <v>437.75</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-2.149993896484375</v>
+        <v>-2.75</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.4880803397240352</v>
+        <v>-0.6242905788876276</v>
       </c>
     </row>
     <row r="280">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>538.4000244140625</v>
       </c>
       <c r="D273" t="n">
-        <v>537</v>
+        <v>530.0999755859375</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-1.4000244140625</v>
+        <v>-8.300048828125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.2600342404490301</v>
+        <v>-1.541613754040575</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>29.30999946594238</v>
       </c>
       <c r="D274" t="n">
-        <v>29.34000015258789</v>
+        <v>29.38999938964844</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.03000068664551137</v>
+        <v>0.07999992370605824</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.1023564899084067</v>
+        <v>0.2729441322543063</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>23.45000076293945</v>
       </c>
       <c r="D275" t="n">
-        <v>23.45000076293945</v>
+        <v>23.5</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>0.04999923706055043</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>1.515016444867343e-14</v>
+        <v>0.2132163557946215</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>395.7000122070312</v>
       </c>
       <c r="D276" t="n">
-        <v>398.7000122070312</v>
+        <v>398.2000122070312</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>3.000000000000057</v>
+        <v>2.500000000000057</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.7581500903342024</v>
+        <v>0.6317917419451711</v>
       </c>
     </row>
     <row r="277">
@@ -11754,13 +11754,13 @@
         <v>19.32999992370605</v>
       </c>
       <c r="D278" t="n">
-        <v>19.10000038146973</v>
+        <v>19</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.2299995422363246</v>
+        <v>-0.3299999237060511</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-1.189857957289779</v>
+        <v>-1.707190507028113</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>440.5</v>
       </c>
       <c r="D279" t="n">
-        <v>437.75</v>
+        <v>437.6000061035156</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-2.75</v>
+        <v>-2.899993896484375</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.6242905788876276</v>
+        <v>-0.6583414066933883</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>71.08000183105469</v>
       </c>
       <c r="D280" t="n">
-        <v>71.5</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.4199981689453125</v>
+        <v>0.3199996948242188</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.5908809202672478</v>
+        <v>0.4501965202319559</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11598,13 +11598,13 @@
         <v>29.30999946594238</v>
       </c>
       <c r="D274" t="n">
-        <v>29.38999938964844</v>
+        <v>29.3700008392334</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.07999992370605824</v>
+        <v>0.06000137329101918</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.2729441322543063</v>
+        <v>0.2047129798168013</v>
       </c>
     </row>
     <row r="275">
@@ -11676,13 +11676,13 @@
         <v>395.7000122070312</v>
       </c>
       <c r="D276" t="n">
-        <v>398.2000122070312</v>
+        <v>398.3500061035156</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>2.500000000000057</v>
+        <v>2.649993896484432</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.6317917419451711</v>
+        <v>0.6696977040015729</v>
       </c>
     </row>
     <row r="277">
@@ -11793,13 +11793,13 @@
         <v>440.5</v>
       </c>
       <c r="D279" t="n">
-        <v>437.6000061035156</v>
+        <v>438.3999938964844</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-2.899993896484375</v>
+        <v>-2.100006103515625</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.6583414066933883</v>
+        <v>-0.4767323731022985</v>
       </c>
     </row>
     <row r="280">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>538.4000244140625</v>
       </c>
       <c r="D273" t="n">
-        <v>530.0999755859375</v>
+        <v>541.5499877929688</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-8.300048828125</v>
+        <v>3.14996337890625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-1.541613754040575</v>
+        <v>0.585060036417037</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>29.30999946594238</v>
       </c>
       <c r="D274" t="n">
-        <v>29.3700008392334</v>
+        <v>29.11000061035156</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.06000137329101918</v>
+        <v>-0.1999988555908168</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.2047129798168013</v>
+        <v>-0.682357076885011</v>
       </c>
     </row>
     <row r="275">
@@ -11676,13 +11676,13 @@
         <v>395.7000122070312</v>
       </c>
       <c r="D276" t="n">
-        <v>398.3500061035156</v>
+        <v>398.5</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>2.649993896484432</v>
+        <v>2.799987792968807</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.6696977040015729</v>
+        <v>0.7076036660579749</v>
       </c>
     </row>
     <row r="277">
@@ -11754,28 +11754,32 @@
         <v>19.32999992370605</v>
       </c>
       <c r="D278" t="n">
-        <v>19</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.3299999237060511</v>
+        <v>-0.4799995422363246</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H278" t="n">
         <v>0.8301858305931091</v>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-1.707190507028113</v>
+        <v>-2.483184397986777</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11797,13 @@
         <v>440.5</v>
       </c>
       <c r="D279" t="n">
-        <v>438.3999938964844</v>
+        <v>437</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-2.100006103515625</v>
+        <v>-3.5</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.4767323731022985</v>
+        <v>-0.7945516458569807</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11836,13 @@
         <v>71.08000183105469</v>
       </c>
       <c r="D280" t="n">
-        <v>71.40000152587891</v>
+        <v>71.88999938964844</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.3199996948242188</v>
+        <v>0.80999755859375</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.4501965202319559</v>
+        <v>1.139557593877078</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,404 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>HITECHCORP.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>411.4500122070312</v>
-      </c>
-      <c r="D272" t="n">
-        <v>411.4500122070312</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>5.684341886080801e-14</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9846413731575012</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>1.381538878949063e-14</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>GLOSTERLTD.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>538.4000244140625</v>
-      </c>
-      <c r="D273" t="n">
-        <v>541.5499877929688</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>3.14996337890625</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9778445959091187</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0.585060036417037</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>GEEKAYWIRE.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>29.30999946594238</v>
-      </c>
-      <c r="D274" t="n">
-        <v>29.11000061035156</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>-0.1999988555908168</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9672104120254517</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>-0.682357076885011</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>AROGRANITE.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>23.45000076293945</v>
-      </c>
-      <c r="D275" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>0.04999923706055043</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9535797834396362</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0.2132163557946215</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>ARVINDFASN.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>395.7000122070312</v>
-      </c>
-      <c r="D276" t="n">
-        <v>398.5</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>2.799987792968807</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.9422463178634644</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0.7076036660579749</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>KSHITIJPOL.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>3.430000066757202</v>
-      </c>
-      <c r="D277" t="n">
-        <v>3.410000085830688</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>-0.01999998092651367</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.8854528069496155</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>-0.5830898115819017</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>CENTEXT.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>19.32999992370605</v>
-      </c>
-      <c r="D278" t="n">
-        <v>18.85000038146973</v>
-      </c>
-      <c r="E278" t="n">
-        <v>18.85000038146973</v>
-      </c>
-      <c r="F278" t="n">
-        <v>-0.4799995422363246</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.8301858305931091</v>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>-2.483184397986777</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>ICIL.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>440.5</v>
-      </c>
-      <c r="D279" t="n">
-        <v>437</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.791745126247406</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-0.7945516458569807</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>SSDL.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>71.08000183105469</v>
-      </c>
-      <c r="D280" t="n">
-        <v>71.88999938964844</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0.80999755859375</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.5371690988540649</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>1.139557593877078</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>TORNTPOWER.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>1235.199951171875</v>
-      </c>
-      <c r="D281" t="n">
-        <v>1240</v>
-      </c>
-      <c r="E281" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F281" t="n">
-        <v>4.800048828125</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.4373399019241333</v>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>0.3886050046853576</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>BHARATRAS.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>990.0999755859375</v>
+      </c>
+      <c r="D272" t="n">
+        <v>990.0999755859375</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9934127926826477</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>KSHITIJPOL.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>3.450000047683716</v>
+      </c>
+      <c r="D273" t="n">
+        <v>3.450000047683716</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9644628763198853</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>BHAGERIA.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>362</v>
+      </c>
+      <c r="D274" t="n">
+        <v>362</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.8312525153160095</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HESTERBIO.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>2226</v>
+      </c>
+      <c r="D275" t="n">
+        <v>2226</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.7777103781700134</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>1628.5</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1628.5</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.5443735718727112</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>VEDL.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>248.6999969482422</v>
+      </c>
+      <c r="D277" t="n">
+        <v>248.6999969482422</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.4257383942604065</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>MAHAPEXLTD.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>48.7599983215332</v>
+      </c>
+      <c r="D278" t="n">
+        <v>48.7599983215332</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.410766065120697</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>TBZ.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>759.1500244140625</v>
+      </c>
+      <c r="D279" t="n">
+        <v>759.1500244140625</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.3346276581287384</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SIS.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>404.6000061035156</v>
+      </c>
+      <c r="D280" t="n">
+        <v>404.6000061035156</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.3320491313934326</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SIYSIL.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>530.5499877929688</v>
+      </c>
+      <c r="D281" t="n">
+        <v>530.5499877929688</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.3200563788414001</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,28 +11559,32 @@
         <v>3.450000047683716</v>
       </c>
       <c r="D273" t="n">
-        <v>3.450000047683716</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>0.009999990463256836</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H273" t="n">
         <v>0.9644628763198853</v>
       </c>
-      <c r="I273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>0.2898547920302406</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11602,13 @@
         <v>362</v>
       </c>
       <c r="D274" t="n">
-        <v>362</v>
+        <v>361.2000122070312</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-0.79998779296875</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11623,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.2209911030300414</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11641,13 @@
         <v>2226</v>
       </c>
       <c r="D275" t="n">
-        <v>2226</v>
+        <v>2226.89990234375</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>0.89990234375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11662,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>0.04042687977313567</v>
       </c>
     </row>
     <row r="276">
@@ -11676,28 +11680,32 @@
         <v>1628.5</v>
       </c>
       <c r="D276" t="n">
-        <v>1628.5</v>
+        <v>1623.5</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>1623.5</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H276" t="n">
         <v>0.5443735718727112</v>
       </c>
-      <c r="I276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>-0.3070310101320233</v>
       </c>
     </row>
     <row r="277">
@@ -11715,28 +11723,32 @@
         <v>248.6999969482422</v>
       </c>
       <c r="D277" t="n">
-        <v>248.6999969482422</v>
+        <v>247.9499969482422</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>247.9499969482422</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H277" t="n">
         <v>0.4257383942604065</v>
       </c>
-      <c r="I277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.3015681581033895</v>
       </c>
     </row>
     <row r="278">
@@ -11754,28 +11766,32 @@
         <v>48.7599983215332</v>
       </c>
       <c r="D278" t="n">
-        <v>48.7599983215332</v>
+        <v>49.7400016784668</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>49.7400016784668</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>0.9800033569335938</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H278" t="n">
         <v>0.410766065120697</v>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>2.009851088327065</v>
       </c>
     </row>
     <row r="279">
@@ -11796,20 +11812,24 @@
         <v>759.1500244140625</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>759.1500244140625</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H279" t="n">
         <v>0.3346276581287384</v>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
@@ -11832,28 +11852,32 @@
         <v>404.6000061035156</v>
       </c>
       <c r="D280" t="n">
-        <v>404.6000061035156</v>
+        <v>404.3500061035156</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>404.3500061035156</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H280" t="n">
         <v>0.3320491313934326</v>
       </c>
-      <c r="I280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>-0.0617894207189009</v>
       </c>
     </row>
     <row r="281">
@@ -11871,28 +11895,32 @@
         <v>530.5499877929688</v>
       </c>
       <c r="D281" t="n">
-        <v>530.5499877929688</v>
+        <v>530.9500122070312</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>530.9500122070312</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>0.4000244140625</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H281" t="n">
         <v>0.3200563788414001</v>
       </c>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>0.07539806300374424</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11602,13 +11602,13 @@
         <v>362</v>
       </c>
       <c r="D274" t="n">
-        <v>361.2000122070312</v>
+        <v>361.0499877929688</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.79998779296875</v>
+        <v>-0.95001220703125</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.2209911030300414</v>
+        <v>-0.2624343113345994</v>
       </c>
     </row>
     <row r="275">
@@ -11641,13 +11641,13 @@
         <v>2226</v>
       </c>
       <c r="D275" t="n">
-        <v>2226.89990234375</v>
+        <v>2222.10009765625</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.89990234375</v>
+        <v>-3.89990234375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.04042687977313567</v>
+        <v>-0.1751977692610063</v>
       </c>
     </row>
     <row r="276">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>990.0999755859375</v>
       </c>
       <c r="D272" t="n">
-        <v>990.0999755859375</v>
+        <v>992.4000244140625</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>2.300048828125</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.2323047050641365</v>
       </c>
     </row>
     <row r="273">
@@ -11602,13 +11602,13 @@
         <v>362</v>
       </c>
       <c r="D274" t="n">
-        <v>361.0499877929688</v>
+        <v>362.9500122070312</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.95001220703125</v>
+        <v>0.95001220703125</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.2624343113345994</v>
+        <v>0.2624343113345994</v>
       </c>
     </row>
     <row r="275">
@@ -11641,13 +11641,13 @@
         <v>2226</v>
       </c>
       <c r="D275" t="n">
-        <v>2222.10009765625</v>
+        <v>2225</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-3.89990234375</v>
+        <v>-1</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.1751977692610063</v>
+        <v>-0.04492362982929021</v>
       </c>
     </row>
     <row r="276">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>990.0999755859375</v>
       </c>
       <c r="D272" t="n">
-        <v>992.4000244140625</v>
+        <v>993.7999877929688</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>2.300048828125</v>
+        <v>3.70001220703125</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.2323047050641365</v>
+        <v>0.3737008684240797</v>
       </c>
     </row>
     <row r="273">
@@ -11602,13 +11602,13 @@
         <v>362</v>
       </c>
       <c r="D274" t="n">
-        <v>362.9500122070312</v>
+        <v>363.7000122070312</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.95001220703125</v>
+        <v>1.70001220703125</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.2624343113345994</v>
+        <v>0.4696166317765884</v>
       </c>
     </row>
     <row r="275">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>990.0999755859375</v>
       </c>
       <c r="D272" t="n">
-        <v>993.7999877929688</v>
+        <v>994.5</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>3.70001220703125</v>
+        <v>4.4000244140625</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.3737008684240797</v>
+        <v>0.4444020323764357</v>
       </c>
     </row>
     <row r="273">
@@ -11602,13 +11602,13 @@
         <v>362</v>
       </c>
       <c r="D274" t="n">
-        <v>363.7000122070312</v>
+        <v>364.25</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>1.70001220703125</v>
+        <v>2.25</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.4696166317765884</v>
+        <v>0.6215469613259669</v>
       </c>
     </row>
     <row r="275">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>990.0999755859375</v>
       </c>
       <c r="D272" t="n">
-        <v>994.5</v>
+        <v>994</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>4.4000244140625</v>
+        <v>3.9000244140625</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.4444020323764357</v>
+        <v>0.3939020816311484</v>
       </c>
     </row>
     <row r="273">
@@ -11602,13 +11602,13 @@
         <v>362</v>
       </c>
       <c r="D274" t="n">
-        <v>364.25</v>
+        <v>364</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.6215469613259669</v>
+        <v>0.5524861878453038</v>
       </c>
     </row>
     <row r="275">
@@ -11641,13 +11641,13 @@
         <v>2226</v>
       </c>
       <c r="D275" t="n">
-        <v>2225</v>
+        <v>2226.199951171875</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-1</v>
+        <v>0.199951171875</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.04492362982929021</v>
+        <v>0.008982532429245283</v>
       </c>
     </row>
     <row r="276">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,424 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>BHARATRAS.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>990.0999755859375</v>
-      </c>
-      <c r="D272" t="n">
-        <v>994</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>3.9000244140625</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9934127926826477</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.3939020816311484</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>KSHITIJPOL.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>3.450000047683716</v>
-      </c>
-      <c r="D273" t="n">
-        <v>3.460000038146973</v>
-      </c>
-      <c r="E273" t="n">
-        <v>3.460000038146973</v>
-      </c>
-      <c r="F273" t="n">
-        <v>0.009999990463256836</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9644628763198853</v>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0.2898547920302406</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>BHAGERIA.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>362</v>
-      </c>
-      <c r="D274" t="n">
-        <v>364</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>2</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.8312525153160095</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0.5524861878453038</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>HESTERBIO.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>2226</v>
-      </c>
-      <c r="D275" t="n">
-        <v>2226.199951171875</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>0.199951171875</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.7777103781700134</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0.008982532429245283</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>ASTRAMICRO.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>1628.5</v>
-      </c>
-      <c r="D276" t="n">
-        <v>1623.5</v>
-      </c>
-      <c r="E276" t="n">
-        <v>1623.5</v>
-      </c>
-      <c r="F276" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.5443735718727112</v>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>-0.3070310101320233</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>VEDL.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>248.6999969482422</v>
-      </c>
-      <c r="D277" t="n">
-        <v>247.9499969482422</v>
-      </c>
-      <c r="E277" t="n">
-        <v>247.9499969482422</v>
-      </c>
-      <c r="F277" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.4257383942604065</v>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>-0.3015681581033895</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>MAHAPEXLTD.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>48.7599983215332</v>
-      </c>
-      <c r="D278" t="n">
-        <v>49.7400016784668</v>
-      </c>
-      <c r="E278" t="n">
-        <v>49.7400016784668</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0.9800033569335938</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.410766065120697</v>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>2.009851088327065</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>TBZ.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>759.1500244140625</v>
-      </c>
-      <c r="D279" t="n">
-        <v>759.1500244140625</v>
-      </c>
-      <c r="E279" t="n">
-        <v>759.1500244140625</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.3346276581287384</v>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>SIS.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>404.6000061035156</v>
-      </c>
-      <c r="D280" t="n">
-        <v>404.3500061035156</v>
-      </c>
-      <c r="E280" t="n">
-        <v>404.3500061035156</v>
-      </c>
-      <c r="F280" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.3320491313934326</v>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>-0.0617894207189009</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>SIYSIL.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>530.5499877929688</v>
-      </c>
-      <c r="D281" t="n">
-        <v>530.9500122070312</v>
-      </c>
-      <c r="E281" t="n">
-        <v>530.9500122070312</v>
-      </c>
-      <c r="F281" t="n">
-        <v>0.4000244140625</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.3200563788414001</v>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>0.07539806300374424</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>WHEELS.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2451.5</v>
+      </c>
+      <c r="D272" t="n">
+        <v>2451.5</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.8655768036842346</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>TATAPOWER.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="D273" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.701501727104187</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>V2RETAIL.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>174.3399963378906</v>
+      </c>
+      <c r="D274" t="n">
+        <v>174.3399963378906</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.6936626434326172</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>DABUR.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>378.4500122070312</v>
+      </c>
+      <c r="D275" t="n">
+        <v>378.4500122070312</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.6802741289138794</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>JINDWORLD.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>39.95999908447266</v>
+      </c>
+      <c r="D276" t="n">
+        <v>39.95999908447266</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.6489769220352173</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>JAYSREETEA.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>83.12999725341797</v>
+      </c>
+      <c r="D277" t="n">
+        <v>83.12999725341797</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.6180486679077148</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>TEGA.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>1870.900024414062</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1870.900024414062</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.6004972457885742</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>RPPL.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>18</v>
+      </c>
+      <c r="D279" t="n">
+        <v>18</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.5885659456253052</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>AFFORDABLE.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>162.9900054931641</v>
+      </c>
+      <c r="D280" t="n">
+        <v>162.9900054931641</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.564505934715271</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>ADROITINFO.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>12.76000022888184</v>
+      </c>
+      <c r="D281" t="n">
+        <v>12.76000022888184</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.5587844252586365</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2451.5</v>
       </c>
       <c r="D272" t="n">
-        <v>2451.5</v>
+        <v>2450.199951171875</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>-1.300048828125</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>-0.05303074966857026</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>351.5</v>
       </c>
       <c r="D273" t="n">
-        <v>351.5</v>
+        <v>350.6499938964844</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-0.850006103515625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-0.2418225045563656</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>174.3399963378906</v>
       </c>
       <c r="D274" t="n">
-        <v>174.3399963378906</v>
+        <v>175.0399932861328</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>0.6999969482422159</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>0.4015125404072757</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>378.4500122070312</v>
       </c>
       <c r="D275" t="n">
-        <v>378.4500122070312</v>
+        <v>377.1000061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-1.350006103515568</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-0.3567197938884057</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>39.95999908447266</v>
       </c>
       <c r="D276" t="n">
-        <v>39.95999908447266</v>
+        <v>39.86000061035156</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>-0.09999847412110086</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>-0.2502464374679064</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>83.12999725341797</v>
       </c>
       <c r="D277" t="n">
-        <v>83.12999725341797</v>
+        <v>83</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-0.1299972534179688</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.1563782722398969</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>1870.900024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1870.900024414062</v>
+        <v>1865.5</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>-5.400024414062045</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>-0.2886324412633033</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>18</v>
       </c>
       <c r="D279" t="n">
-        <v>18</v>
+        <v>17.89999961853027</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>-0.1000003814697266</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>-0.5555576748318142</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>162.9900054931641</v>
       </c>
       <c r="D280" t="n">
-        <v>162.9900054931641</v>
+        <v>161.5099945068359</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>-1.480010986328153</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>-0.9080378774453297</v>
       </c>
     </row>
     <row r="281">
@@ -11877,7 +11877,7 @@
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>-2.78425831902342e-14</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>2451.5</v>
       </c>
       <c r="D272" t="n">
-        <v>2450.199951171875</v>
+        <v>2450.800048828125</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>-1.300048828125</v>
+        <v>-0.699951171875</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>-0.05303074966857026</v>
+        <v>-0.02855195479808281</v>
       </c>
     </row>
     <row r="273">
@@ -11598,13 +11598,13 @@
         <v>174.3399963378906</v>
       </c>
       <c r="D274" t="n">
-        <v>175.0399932861328</v>
+        <v>174.9700012207031</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.6999969482422159</v>
+        <v>0.6300048828125284</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.4015125404072757</v>
+        <v>0.3613656625250283</v>
       </c>
     </row>
     <row r="275">
@@ -11676,13 +11676,13 @@
         <v>39.95999908447266</v>
       </c>
       <c r="D276" t="n">
-        <v>39.86000061035156</v>
+        <v>40.0099983215332</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.09999847412110086</v>
+        <v>0.04999923706053977</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.2502464374679064</v>
+        <v>0.1251232187339265</v>
       </c>
     </row>
     <row r="277">
@@ -11754,13 +11754,13 @@
         <v>1870.900024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1865.5</v>
+        <v>1866.5</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-5.400024414062045</v>
+        <v>-4.400024414062045</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.2886324412633033</v>
+        <v>-0.2351822308324608</v>
       </c>
     </row>
     <row r="279">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,396 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>WHEELS.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>2451.5</v>
-      </c>
-      <c r="D272" t="n">
-        <v>2450.800048828125</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>-0.699951171875</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.8655768036842346</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>-0.02855195479808281</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>TATAPOWER.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>351.5</v>
-      </c>
-      <c r="D273" t="n">
-        <v>350.6499938964844</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>-0.850006103515625</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.701501727104187</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>-0.2418225045563656</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>V2RETAIL.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>174.3399963378906</v>
-      </c>
-      <c r="D274" t="n">
-        <v>174.9700012207031</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0.6300048828125284</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.6936626434326172</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0.3613656625250283</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>DABUR.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>378.4500122070312</v>
-      </c>
-      <c r="D275" t="n">
-        <v>377.1000061035156</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-1.350006103515568</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.6802741289138794</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-0.3567197938884057</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>JINDWORLD.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>39.95999908447266</v>
-      </c>
-      <c r="D276" t="n">
-        <v>40.0099983215332</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0.04999923706053977</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.6489769220352173</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0.1251232187339265</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>JAYSREETEA.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>83.12999725341797</v>
-      </c>
-      <c r="D277" t="n">
-        <v>83</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>-0.1299972534179688</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.6180486679077148</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>-0.1563782722398969</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>TEGA.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>1870.900024414062</v>
-      </c>
-      <c r="D278" t="n">
-        <v>1866.5</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>-4.400024414062045</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.6004972457885742</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>-0.2351822308324608</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>RPPL.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>18</v>
-      </c>
-      <c r="D279" t="n">
-        <v>17.89999961853027</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-0.1000003814697266</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.5885659456253052</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-0.5555576748318142</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>AFFORDABLE.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>162.9900054931641</v>
-      </c>
-      <c r="D280" t="n">
-        <v>161.5099945068359</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>-1.480010986328153</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.564505934715271</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>-0.9080378774453297</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>ADROITINFO.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>12.76000022888184</v>
-      </c>
-      <c r="D281" t="n">
-        <v>12.76000022888184</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-3.552713678800501e-15</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.5587844252586365</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>-2.78425831902342e-14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>BOHRAIND.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>13.72000026702881</v>
+      </c>
+      <c r="D272" t="n">
+        <v>13.72000026702881</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9078314900398254</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SUMMITSEC.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>1317</v>
+      </c>
+      <c r="D273" t="n">
+        <v>1317</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.8878104090690613</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>WHEELS.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>2439.39990234375</v>
+      </c>
+      <c r="D274" t="n">
+        <v>2439.39990234375</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.8655768036842346</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>PEARLPOLY.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>16.20999908447266</v>
+      </c>
+      <c r="D275" t="n">
+        <v>16.20999908447266</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.8062462210655212</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>FMGOETZE.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>450.1499938964844</v>
+      </c>
+      <c r="D276" t="n">
+        <v>450.1499938964844</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.7859806418418884</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ROSSARI.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="D277" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.7120435833930969</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>JAYSREETEA.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>82.93000030517578</v>
+      </c>
+      <c r="D278" t="n">
+        <v>82.93000030517578</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.707740843296051</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>TATAPOWER.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>352.25</v>
+      </c>
+      <c r="D279" t="n">
+        <v>352.25</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.701501727104187</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>V2RETAIL.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>174.8000030517578</v>
+      </c>
+      <c r="D280" t="n">
+        <v>174.8000030517578</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.6936626434326172</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>DABUR.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="D281" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.6802741289138794</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11526,7 +11526,7 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>-1.294720703227024e-14</v>
       </c>
     </row>
     <row r="273">
@@ -11643,7 +11643,7 @@
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-2.191680369805571e-14</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>437.5</v>
       </c>
       <c r="D277" t="n">
-        <v>437.5</v>
+        <v>435</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
     </row>
     <row r="278">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,396 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>BOHRAIND.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>13.72000026702881</v>
-      </c>
-      <c r="D272" t="n">
-        <v>13.72000026702881</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>-1.77635683940025e-15</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9078314900398254</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>-1.294720703227024e-14</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>SUMMITSEC.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>1317</v>
-      </c>
-      <c r="D273" t="n">
-        <v>1317</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.8878104090690613</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>WHEELS.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>2439.39990234375</v>
-      </c>
-      <c r="D274" t="n">
-        <v>2439.39990234375</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.8655768036842346</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>PEARLPOLY.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>16.20999908447266</v>
-      </c>
-      <c r="D275" t="n">
-        <v>16.20999908447266</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-3.552713678800501e-15</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.8062462210655212</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-2.191680369805571e-14</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>FMGOETZE.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>450.1499938964844</v>
-      </c>
-      <c r="D276" t="n">
-        <v>450.1499938964844</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.7859806418418884</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>ROSSARI.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="D277" t="n">
-        <v>435</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.7120435833930969</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>-0.5714285714285714</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>JAYSREETEA.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>82.93000030517578</v>
-      </c>
-      <c r="D278" t="n">
-        <v>82.93000030517578</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.707740843296051</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>TATAPOWER.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>352.25</v>
-      </c>
-      <c r="D279" t="n">
-        <v>352.25</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.701501727104187</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>V2RETAIL.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>174.8000030517578</v>
-      </c>
-      <c r="D280" t="n">
-        <v>174.8000030517578</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.6936626434326172</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>DABUR.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>378.5</v>
-      </c>
-      <c r="D281" t="n">
-        <v>378.5</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.6802741289138794</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>IGPL.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>538.2000122070312</v>
+      </c>
+      <c r="D272" t="n">
+        <v>538.2000122070312</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9654151201248169</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>VIDHIING.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>329.8999938964844</v>
+      </c>
+      <c r="D273" t="n">
+        <v>329.8999938964844</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.8531627655029297</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ADANIPORTS.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1732.199951171875</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1732.199951171875</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.7835102677345276</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>IMPAL.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1012.200012207031</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1012.200012207031</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.7790709733963013</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>DABUR.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="D276" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.7664585113525391</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>JAYSREETEA.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>80.02999877929688</v>
+      </c>
+      <c r="D277" t="n">
+        <v>80.02999877929688</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.7576889991760254</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>KIRLOSENG.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>1904.5</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1904.5</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.7110822796821594</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>PLAZACABLE.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>52.2400016784668</v>
+      </c>
+      <c r="D279" t="n">
+        <v>52.2400016784668</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.700596034526825</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>COASTCORP.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>34.52999877929688</v>
+      </c>
+      <c r="D280" t="n">
+        <v>34.52999877929688</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.6898040771484375</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>RHL.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>160.5099945068359</v>
+      </c>
+      <c r="D281" t="n">
+        <v>160.5099945068359</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.6755099296569824</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>538.2000122070312</v>
       </c>
       <c r="D272" t="n">
-        <v>538.2000122070312</v>
+        <v>538.25</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>0.04998779296875</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.009287958349120405</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>329.8999938964844</v>
       </c>
       <c r="D273" t="n">
-        <v>329.8999938964844</v>
+        <v>323.4500122070312</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-6.449981689453125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-1.955132406421624</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>1732.199951171875</v>
       </c>
       <c r="D274" t="n">
-        <v>1732.199951171875</v>
+        <v>1727.400024414062</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-4.7999267578125</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.2771000400135812</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>1012.200012207031</v>
       </c>
       <c r="D275" t="n">
-        <v>1012.200012207031</v>
+        <v>1012</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-0.2000122070310226</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-0.01976014667248522</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>372.5</v>
       </c>
       <c r="D276" t="n">
-        <v>372.5</v>
+        <v>372.6499938964844</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>0.149993896484375</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.04026681784815436</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>80.02999877929688</v>
       </c>
       <c r="D277" t="n">
-        <v>80.02999877929688</v>
+        <v>80</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-0.029998779296875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.03748441803629696</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>1904.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1904.5</v>
+        <v>1906.5</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.1050144394854293</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>52.2400016784668</v>
       </c>
       <c r="D279" t="n">
-        <v>52.2400016784668</v>
+        <v>51.95000076293945</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>-0.2900009155273438</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>-0.5551319031578084</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>34.52999877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>34.52999877929688</v>
+        <v>35.11000061035156</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>0.5800018310546804</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>1.679704174801279</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>160.5099945068359</v>
       </c>
       <c r="D281" t="n">
-        <v>160.5099945068359</v>
+        <v>160.5500030517578</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>0.04000854492190342</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>0.02492589015707649</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,28 +11559,32 @@
         <v>329.8999938964844</v>
       </c>
       <c r="D273" t="n">
-        <v>323.4500122070312</v>
+        <v>323</v>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="F273" t="n">
-        <v>-6.449981689453125</v>
+        <v>-6.899993896484375</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H273" t="n">
         <v>0.8531627655029297</v>
       </c>
-      <c r="I273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-1.955132406421624</v>
+        <v>-2.091541080370388</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11602,13 @@
         <v>1732.199951171875</v>
       </c>
       <c r="D274" t="n">
-        <v>1727.400024414062</v>
+        <v>1726.099975585938</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-4.7999267578125</v>
+        <v>-6.0999755859375</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11623,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.2771000400135812</v>
+        <v>-0.352151931525614</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11641,13 @@
         <v>1012.200012207031</v>
       </c>
       <c r="D275" t="n">
-        <v>1012</v>
+        <v>1012.599975585938</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.2000122070310226</v>
+        <v>0.3999633789064774</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11662,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.01976014667248522</v>
+        <v>0.03951426339487838</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11680,13 @@
         <v>372.5</v>
       </c>
       <c r="D276" t="n">
-        <v>372.6499938964844</v>
+        <v>372.7000122070312</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.149993896484375</v>
+        <v>0.20001220703125</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11701,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.04026681784815436</v>
+        <v>0.05369455222315436</v>
       </c>
     </row>
     <row r="277">
@@ -11754,13 +11758,13 @@
         <v>1904.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1906.5</v>
+        <v>1904.5</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.1050144394854293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11797,13 @@
         <v>52.2400016784668</v>
       </c>
       <c r="D279" t="n">
-        <v>51.95000076293945</v>
+        <v>51.59999847412109</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.2900009155273438</v>
+        <v>-0.6400032043457031</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.5551319031578084</v>
+        <v>-1.225120949047578</v>
       </c>
     </row>
     <row r="280">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>538.2000122070312</v>
       </c>
       <c r="D272" t="n">
-        <v>538.25</v>
+        <v>538.9500122070312</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.04998779296875</v>
+        <v>0.75</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.009287958349120405</v>
+        <v>0.1393533970622607</v>
       </c>
     </row>
     <row r="273">
@@ -11602,13 +11602,13 @@
         <v>1732.199951171875</v>
       </c>
       <c r="D274" t="n">
-        <v>1726.099975585938</v>
+        <v>1729.300048828125</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-6.0999755859375</v>
+        <v>-2.89990234375</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.352151931525614</v>
+        <v>-0.1674115243905963</v>
       </c>
     </row>
     <row r="275">
@@ -11641,13 +11641,13 @@
         <v>1012.200012207031</v>
       </c>
       <c r="D275" t="n">
-        <v>1012.599975585938</v>
+        <v>1015.900024414062</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.3999633789064774</v>
+        <v>3.700012207031477</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.03951426339487838</v>
+        <v>0.3655416086158566</v>
       </c>
     </row>
     <row r="276">
@@ -11680,13 +11680,13 @@
         <v>372.5</v>
       </c>
       <c r="D276" t="n">
-        <v>372.7000122070312</v>
+        <v>373</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.20001220703125</v>
+        <v>0.5</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.05369455222315436</v>
+        <v>0.1342281879194631</v>
       </c>
     </row>
     <row r="277">
@@ -11719,13 +11719,13 @@
         <v>80.02999877929688</v>
       </c>
       <c r="D277" t="n">
-        <v>80</v>
+        <v>80.05000305175781</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.029998779296875</v>
+        <v>0.0200042724609375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.03748441803629696</v>
+        <v>0.0249959674697789</v>
       </c>
     </row>
     <row r="278">
@@ -11758,13 +11758,13 @@
         <v>1904.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1904.5</v>
+        <v>1908.5</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.2100288789708585</v>
       </c>
     </row>
     <row r="279">
@@ -11797,13 +11797,13 @@
         <v>52.2400016784668</v>
       </c>
       <c r="D279" t="n">
-        <v>51.59999847412109</v>
+        <v>52.43999862670898</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.6400032043457031</v>
+        <v>0.1999969482421875</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-1.225120949047578</v>
+        <v>0.382842537933198</v>
       </c>
     </row>
     <row r="280">
@@ -11836,13 +11836,13 @@
         <v>34.52999877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>35.11000061035156</v>
+        <v>34.52000045776367</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.5800018310546804</v>
+        <v>-0.00999832153321023</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>1.679704174801279</v>
+        <v>-0.02895546448499996</v>
       </c>
     </row>
     <row r="281">
@@ -11875,13 +11875,13 @@
         <v>160.5099945068359</v>
       </c>
       <c r="D281" t="n">
-        <v>160.5500030517578</v>
+        <v>162.8800048828125</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0.04000854492190342</v>
+        <v>2.370010375976591</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0.02492589015707649</v>
+        <v>1.476550032450257</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>538.2000122070312</v>
       </c>
       <c r="D272" t="n">
-        <v>538.9500122070312</v>
+        <v>539.5</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.75</v>
+        <v>1.29998779296875</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.1393533970622607</v>
+        <v>0.241543620119555</v>
       </c>
     </row>
     <row r="273">
@@ -11641,28 +11641,32 @@
         <v>1012.200012207031</v>
       </c>
       <c r="D275" t="n">
-        <v>1015.900024414062</v>
+        <v>1020</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="F275" t="n">
-        <v>3.700012207031477</v>
+        <v>7.799987792968977</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H275" t="n">
         <v>0.7790709733963013</v>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.3655416086158566</v>
+        <v>0.7705974806265465</v>
       </c>
     </row>
     <row r="276">
@@ -11680,13 +11684,13 @@
         <v>372.5</v>
       </c>
       <c r="D276" t="n">
-        <v>373</v>
+        <v>373.7000122070312</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.5</v>
+        <v>1.20001220703125</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11701,7 +11705,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.1342281879194631</v>
+        <v>0.3221509280620805</v>
       </c>
     </row>
     <row r="277">
@@ -11719,13 +11723,13 @@
         <v>80.02999877929688</v>
       </c>
       <c r="D277" t="n">
-        <v>80.05000305175781</v>
+        <v>80.09999847412109</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.0200042724609375</v>
+        <v>0.06999969482421875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11740,7 +11744,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.0249959674697789</v>
+        <v>0.08746681980748339</v>
       </c>
     </row>
     <row r="278">
@@ -11758,13 +11762,13 @@
         <v>1904.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1908.5</v>
+        <v>1912</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11779,7 +11783,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.2100288789708585</v>
+        <v>0.3938041480703596</v>
       </c>
     </row>
     <row r="279">
@@ -11797,13 +11801,13 @@
         <v>52.2400016784668</v>
       </c>
       <c r="D279" t="n">
-        <v>52.43999862670898</v>
+        <v>51.75</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.1999969482421875</v>
+        <v>-0.4900016784667969</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11818,7 +11822,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.382842537933198</v>
+        <v>-0.9379817433443429</v>
       </c>
     </row>
     <row r="280">
@@ -11836,13 +11840,13 @@
         <v>34.52999877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>34.52000045776367</v>
+        <v>35.22000122070312</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.00999832153321023</v>
+        <v>0.6900024414062429</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11857,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.02895546448499996</v>
+        <v>1.998269521573071</v>
       </c>
     </row>
     <row r="281">
@@ -11875,13 +11879,13 @@
         <v>160.5099945068359</v>
       </c>
       <c r="D281" t="n">
-        <v>162.8800048828125</v>
+        <v>162.8899993896484</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>2.370010375976591</v>
+        <v>2.380004882812528</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11896,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.476550032450257</v>
+        <v>1.482776751768668</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>538.2000122070312</v>
       </c>
       <c r="D272" t="n">
-        <v>539.5</v>
+        <v>539.9500122070312</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>1.29998779296875</v>
+        <v>1.75</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.241543620119555</v>
+        <v>0.3251579264786084</v>
       </c>
     </row>
     <row r="273">
@@ -11602,13 +11602,13 @@
         <v>1732.199951171875</v>
       </c>
       <c r="D274" t="n">
-        <v>1729.300048828125</v>
+        <v>1734</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-2.89990234375</v>
+        <v>1.800048828125</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.1674115243905963</v>
+        <v>0.1039169194588202</v>
       </c>
     </row>
     <row r="275">
@@ -11684,13 +11684,13 @@
         <v>372.5</v>
       </c>
       <c r="D276" t="n">
-        <v>373.7000122070312</v>
+        <v>374.9500122070312</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>1.20001220703125</v>
+        <v>2.45001220703125</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.3221509280620805</v>
+        <v>0.6577213978607382</v>
       </c>
     </row>
     <row r="277">
@@ -11723,13 +11723,13 @@
         <v>80.02999877929688</v>
       </c>
       <c r="D277" t="n">
-        <v>80.09999847412109</v>
+        <v>80.15000152587891</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.06999969482421875</v>
+        <v>0.1200027465820312</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.08746681980748339</v>
+        <v>0.1499472053135592</v>
       </c>
     </row>
     <row r="278">
@@ -11762,13 +11762,13 @@
         <v>1904.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.3938041480703596</v>
+        <v>0.3412969283276451</v>
       </c>
     </row>
     <row r="279">
@@ -11801,13 +11801,13 @@
         <v>52.2400016784668</v>
       </c>
       <c r="D279" t="n">
-        <v>51.75</v>
+        <v>51.31000137329102</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.4900016784667969</v>
+        <v>-0.9300003051757812</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.9379817433443429</v>
+        <v>-1.78024554995205</v>
       </c>
     </row>
     <row r="280">
@@ -11840,13 +11840,13 @@
         <v>34.52999877929688</v>
       </c>
       <c r="D280" t="n">
-        <v>35.22000122070312</v>
+        <v>35.06000137329102</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.6900024414062429</v>
+        <v>0.5300025939941335</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>1.998269521573071</v>
+        <v>1.534904757401575</v>
       </c>
     </row>
     <row r="281">
@@ -11879,13 +11879,13 @@
         <v>160.5099945068359</v>
       </c>
       <c r="D281" t="n">
-        <v>162.8899993896484</v>
+        <v>160.1000061035156</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>2.380004882812528</v>
+        <v>-0.4099884033202841</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.482776751768668</v>
+        <v>-0.255428582238736</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,404 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>IGPL.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>538.2000122070312</v>
-      </c>
-      <c r="D272" t="n">
-        <v>539.9500122070312</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9654151201248169</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.3251579264786084</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>VIDHIING.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>329.8999938964844</v>
-      </c>
-      <c r="D273" t="n">
-        <v>323</v>
-      </c>
-      <c r="E273" t="n">
-        <v>323</v>
-      </c>
-      <c r="F273" t="n">
-        <v>-6.899993896484375</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.8531627655029297</v>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>-2.091541080370388</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>ADANIPORTS.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>1732.199951171875</v>
-      </c>
-      <c r="D274" t="n">
-        <v>1734</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>1.800048828125</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.7835102677345276</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0.1039169194588202</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>IMPAL.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>1012.200012207031</v>
-      </c>
-      <c r="D275" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E275" t="n">
-        <v>1020</v>
-      </c>
-      <c r="F275" t="n">
-        <v>7.799987792968977</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.7790709733963013</v>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0.7705974806265465</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>DABUR.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>372.5</v>
-      </c>
-      <c r="D276" t="n">
-        <v>374.9500122070312</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>2.45001220703125</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.7664585113525391</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0.6577213978607382</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>JAYSREETEA.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>80.02999877929688</v>
-      </c>
-      <c r="D277" t="n">
-        <v>80.15000152587891</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0.1200027465820312</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.7576889991760254</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>0.1499472053135592</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>KIRLOSENG.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>1904.5</v>
-      </c>
-      <c r="D278" t="n">
-        <v>1911</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.7110822796821594</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0.3412969283276451</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>PLAZACABLE.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>52.2400016784668</v>
-      </c>
-      <c r="D279" t="n">
-        <v>51.31000137329102</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-0.9300003051757812</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.700596034526825</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-1.78024554995205</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>COASTCORP.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>34.52999877929688</v>
-      </c>
-      <c r="D280" t="n">
-        <v>35.06000137329102</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0.5300025939941335</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.6898040771484375</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>1.534904757401575</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>RHL.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>160.5099945068359</v>
-      </c>
-      <c r="D281" t="n">
-        <v>160.1000061035156</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-0.4099884033202841</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.6755099296569824</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>-0.255428582238736</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>PSUBANK.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>82.33000183105469</v>
+      </c>
+      <c r="D272" t="n">
+        <v>82.33000183105469</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9637702703475952</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>IGPL.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>540.5999755859375</v>
+      </c>
+      <c r="D273" t="n">
+        <v>540.5999755859375</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9596155881881714</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>BOHRAIND.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>13.61999988555908</v>
+      </c>
+      <c r="D274" t="n">
+        <v>13.61999988555908</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9554425477981567</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SADBHAV.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>6.230000019073486</v>
+      </c>
+      <c r="D275" t="n">
+        <v>6.230000019073486</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9308521747589111</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>HESTERBIO.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>2149.199951171875</v>
+      </c>
+      <c r="D276" t="n">
+        <v>2149.199951171875</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.9301720857620239</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ITI.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>227.2799987792969</v>
+      </c>
+      <c r="D277" t="n">
+        <v>227.2799987792969</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.9280794858932495</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>MINDACORP.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>614.2000122070312</v>
+      </c>
+      <c r="D278" t="n">
+        <v>614.2000122070312</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.9085599780082703</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>DNAMEDIA.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2.329999923706055</v>
+      </c>
+      <c r="D279" t="n">
+        <v>2.329999923706055</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.9072692394256592</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>FAZE3Q.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>430.9500122070312</v>
+      </c>
+      <c r="D280" t="n">
+        <v>430.9500122070312</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.7489162683486938</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>195</v>
+      </c>
+      <c r="D281" t="n">
+        <v>195</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.6862685084342957</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>82.33000183105469</v>
       </c>
       <c r="D272" t="n">
-        <v>82.33000183105469</v>
+        <v>82.36000061035156</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>0.029998779296875</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>0.03643723870969177</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>540.5999755859375</v>
       </c>
       <c r="D273" t="n">
-        <v>540.5999755859375</v>
+        <v>539.7999877929688</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-0.79998779296875</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-0.1479814704212058</v>
       </c>
     </row>
     <row r="274">
@@ -11604,7 +11604,7 @@
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>1.304226765290706e-14</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>6.230000019073486</v>
       </c>
       <c r="D275" t="n">
-        <v>6.230000019073486</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-0.05000019073486328</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-0.8025712773962271</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>2149.199951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>2149.199951171875</v>
+        <v>2154.10009765625</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>4.900146484375</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.2279986318491744</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>227.2799987792969</v>
       </c>
       <c r="D277" t="n">
-        <v>227.2799987792969</v>
+        <v>227.3399963378906</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>0.05999755859372158</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>0.02639808118442616</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>614.2000122070312</v>
       </c>
       <c r="D278" t="n">
-        <v>614.2000122070312</v>
+        <v>612.8499755859375</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>-1.35003662109375</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>-0.2198040694012046</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>2.329999923706055</v>
       </c>
       <c r="D279" t="n">
-        <v>2.329999923706055</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>0.009999990463256392</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>0.4291841541072066</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>430.9500122070312</v>
       </c>
       <c r="D280" t="n">
-        <v>430.9500122070312</v>
+        <v>429.4500122070312</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>-1.499999999999943</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>-0.3480682115120427</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>195</v>
       </c>
       <c r="D281" t="n">
-        <v>195</v>
+        <v>197.9499969482422</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>2.949996948242188</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>1.512818947816506</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>540.5999755859375</v>
       </c>
       <c r="D273" t="n">
-        <v>539.7999877929688</v>
+        <v>539.7000122070312</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.79998779296875</v>
+        <v>-0.89996337890625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.1479814704212058</v>
+        <v>-0.1664749203754238</v>
       </c>
     </row>
     <row r="274">
@@ -11637,13 +11637,13 @@
         <v>6.230000019073486</v>
       </c>
       <c r="D275" t="n">
-        <v>6.179999828338623</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.05000019073486328</v>
+        <v>-0.03000020980834961</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.8025712773962271</v>
+        <v>-0.4815442972151256</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>2149.199951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>2154.10009765625</v>
+        <v>2153.89990234375</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>4.900146484375</v>
+        <v>4.699951171875</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.2279986318491744</v>
+        <v>0.2186837557534979</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>227.2799987792969</v>
       </c>
       <c r="D277" t="n">
-        <v>227.3399963378906</v>
+        <v>227.3200073242188</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.05999755859372158</v>
+        <v>0.04000854492184658</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.02639808118442616</v>
+        <v>0.01760319655787106</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>614.2000122070312</v>
       </c>
       <c r="D278" t="n">
-        <v>612.8499755859375</v>
+        <v>611.75</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-1.35003662109375</v>
+        <v>-2.45001220703125</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.2198040694012046</v>
+        <v>-0.3988948483129325</v>
       </c>
     </row>
     <row r="279">
@@ -11832,13 +11832,13 @@
         <v>430.9500122070312</v>
       </c>
       <c r="D280" t="n">
-        <v>429.4500122070312</v>
+        <v>429.1499938964844</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-1.499999999999943</v>
+        <v>-1.800018310546818</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.3480682115120427</v>
+        <v>-0.4176861026939889</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>195</v>
       </c>
       <c r="D281" t="n">
-        <v>197.9499969482422</v>
+        <v>198</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>2.949996948242188</v>
+        <v>3</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.512818947816506</v>
+        <v>1.538461538461539</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>540.5999755859375</v>
       </c>
       <c r="D273" t="n">
-        <v>539.7000122070312</v>
+        <v>541.4000244140625</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.89996337890625</v>
+        <v>0.800048828125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.1664749203754238</v>
+        <v>0.1479927606836931</v>
       </c>
     </row>
     <row r="274">
@@ -11637,13 +11637,13 @@
         <v>6.230000019073486</v>
       </c>
       <c r="D275" t="n">
-        <v>6.199999809265137</v>
+        <v>6.210000038146973</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.03000020980834961</v>
+        <v>-0.01999998092651367</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.4815442972151256</v>
+        <v>-0.3210269801811017</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>2149.199951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>2153.89990234375</v>
+        <v>2153.300048828125</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>4.699951171875</v>
+        <v>4.10009765625</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.2186837557534979</v>
+        <v>0.1907732062814526</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>227.2799987792969</v>
       </c>
       <c r="D277" t="n">
-        <v>227.3200073242188</v>
+        <v>227.9799957275391</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.04000854492184658</v>
+        <v>0.6999969482421591</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.01760319655787106</v>
+        <v>0.307988803239083</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>614.2000122070312</v>
       </c>
       <c r="D278" t="n">
-        <v>611.75</v>
+        <v>613</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-2.45001220703125</v>
+        <v>-1.20001220703125</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.3988948483129325</v>
+        <v>-0.195378082575934</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>2.329999923706055</v>
       </c>
       <c r="D279" t="n">
-        <v>2.339999914169312</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.009999990463256392</v>
+        <v>-0.01999998092651412</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.4291841541072066</v>
+        <v>-0.8583683082144704</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>430.9500122070312</v>
       </c>
       <c r="D280" t="n">
-        <v>429.1499938964844</v>
+        <v>426.8500061035156</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-1.800018310546818</v>
+        <v>-4.100006103515568</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.4176861026939889</v>
+        <v>-0.9513878610927846</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>540.5999755859375</v>
       </c>
       <c r="D273" t="n">
-        <v>541.4000244140625</v>
+        <v>542.4000244140625</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.800048828125</v>
+        <v>1.800048828125</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.1479927606836931</v>
+        <v>0.3329724212758223</v>
       </c>
     </row>
     <row r="274">
@@ -11637,13 +11637,13 @@
         <v>6.230000019073486</v>
       </c>
       <c r="D275" t="n">
-        <v>6.210000038146973</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.01999998092651367</v>
+        <v>-0.03000020980834961</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.3210269801811017</v>
+        <v>-0.4815442972151256</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>2149.199951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>2153.300048828125</v>
+        <v>2142.199951171875</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>4.10009765625</v>
+        <v>-7</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.1907732062814526</v>
+        <v>-0.3257025944088252</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>227.2799987792969</v>
       </c>
       <c r="D277" t="n">
-        <v>227.9799957275391</v>
+        <v>227.7599945068359</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.6999969482421591</v>
+        <v>0.4799957275390341</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.307988803239083</v>
+        <v>0.2111913631278835</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>614.2000122070312</v>
       </c>
       <c r="D278" t="n">
-        <v>613</v>
+        <v>612.75</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-1.20001220703125</v>
+        <v>-1.45001220703125</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.195378082575934</v>
+        <v>-0.2360814357233337</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>2.329999923706055</v>
       </c>
       <c r="D279" t="n">
-        <v>2.309999942779541</v>
+        <v>2.299999952316284</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.01999998092651412</v>
+        <v>-0.02999997138977095</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.8583683082144704</v>
+        <v>-1.287552462321696</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>430.9500122070312</v>
       </c>
       <c r="D280" t="n">
-        <v>426.8500061035156</v>
+        <v>431.25</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-4.100006103515568</v>
+        <v>0.2999877929688068</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.9513878610927846</v>
+        <v>0.06961080971606766</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>195</v>
       </c>
       <c r="D281" t="n">
-        <v>198</v>
+        <v>193.1499938964844</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>-1.850006103515625</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>1.538461538461539</v>
+        <v>-0.9487210787259615</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>82.33000183105469</v>
       </c>
       <c r="D272" t="n">
-        <v>82.36000061035156</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.029998779296875</v>
+        <v>-0.1300048828125</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.03643723870969177</v>
+        <v>-0.1579070568700782</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>540.5999755859375</v>
       </c>
       <c r="D273" t="n">
-        <v>542.4000244140625</v>
+        <v>541.5999755859375</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>1.800048828125</v>
+        <v>1</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.3329724212758223</v>
+        <v>0.1849796605921291</v>
       </c>
     </row>
     <row r="274">
@@ -11637,13 +11637,13 @@
         <v>6.230000019073486</v>
       </c>
       <c r="D275" t="n">
-        <v>6.199999809265137</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.03000020980834961</v>
+        <v>-0.03999996185302734</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.4815442972151256</v>
+        <v>-0.6420539603622034</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>2149.199951171875</v>
       </c>
       <c r="D276" t="n">
-        <v>2142.199951171875</v>
+        <v>2142.5</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>-7</v>
+        <v>-6.699951171875</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>-0.3257025944088252</v>
+        <v>-0.3117416398703051</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>227.2799987792969</v>
       </c>
       <c r="D277" t="n">
-        <v>227.7599945068359</v>
+        <v>227.3999938964844</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.4799957275390341</v>
+        <v>0.1199951171874716</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0.2111913631278835</v>
+        <v>0.05279616236886482</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>614.2000122070312</v>
       </c>
       <c r="D278" t="n">
-        <v>612.75</v>
+        <v>612.7999877929688</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-1.45001220703125</v>
+        <v>-1.4000244140625</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.2360814357233337</v>
+        <v>-0.2279427525622691</v>
       </c>
     </row>
     <row r="279">
@@ -11793,28 +11793,32 @@
         <v>2.329999923706055</v>
       </c>
       <c r="D279" t="n">
-        <v>2.299999952316284</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.02999997138977095</v>
+        <v>-0.1099998950958256</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H279" t="n">
         <v>0.9072692394256592</v>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-1.287552462321696</v>
+        <v>-4.721025695179501</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11836,13 @@
         <v>430.9500122070312</v>
       </c>
       <c r="D280" t="n">
-        <v>431.25</v>
+        <v>429.1499938964844</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.2999877929688068</v>
+        <v>-1.800018310546818</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11857,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.06961080971606766</v>
+        <v>-0.4176861026939889</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11875,13 @@
         <v>195</v>
       </c>
       <c r="D281" t="n">
-        <v>193.1499938964844</v>
+        <v>198.4499969482422</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>-1.850006103515625</v>
+        <v>3.449996948242188</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11896,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>-0.9487210787259615</v>
+        <v>1.769229204226763</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,400 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>PSUBANK.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>82.33000183105469</v>
-      </c>
-      <c r="D272" t="n">
-        <v>82.19999694824219</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>-0.1300048828125</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9637702703475952</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>-0.1579070568700782</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>IGPL.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>540.5999755859375</v>
-      </c>
-      <c r="D273" t="n">
-        <v>541.5999755859375</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>1</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9596155881881714</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0.1849796605921291</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>BOHRAIND.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>13.61999988555908</v>
-      </c>
-      <c r="D274" t="n">
-        <v>13.61999988555908</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>1.77635683940025e-15</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9554425477981567</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>1.304226765290706e-14</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>SADBHAV.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>6.230000019073486</v>
-      </c>
-      <c r="D275" t="n">
-        <v>6.190000057220459</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>-0.03999996185302734</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9308521747589111</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>-0.6420539603622034</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>HESTERBIO.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>2149.199951171875</v>
-      </c>
-      <c r="D276" t="n">
-        <v>2142.5</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>-6.699951171875</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.9301720857620239</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>-0.3117416398703051</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>ITI.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>227.2799987792969</v>
-      </c>
-      <c r="D277" t="n">
-        <v>227.3999938964844</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0.1199951171874716</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.9280794858932495</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>0.05279616236886482</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>MINDACORP.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>614.2000122070312</v>
-      </c>
-      <c r="D278" t="n">
-        <v>612.7999877929688</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>-1.4000244140625</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.9085599780082703</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>-0.2279427525622691</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>DNAMEDIA.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>2.329999923706055</v>
-      </c>
-      <c r="D279" t="n">
-        <v>2.220000028610229</v>
-      </c>
-      <c r="E279" t="n">
-        <v>2.220000028610229</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-0.1099998950958256</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.9072692394256592</v>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-4.721025695179501</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>FAZE3Q.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>430.9500122070312</v>
-      </c>
-      <c r="D280" t="n">
-        <v>429.1499938964844</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>-1.800018310546818</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.7489162683486938</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>-0.4176861026939889</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>KRONOX.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>195</v>
-      </c>
-      <c r="D281" t="n">
-        <v>198.4499969482422</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>3.449996948242188</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.6862685084342957</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>1.769229204226763</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>NAGREEKEXP.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>20</v>
+      </c>
+      <c r="D272" t="n">
+        <v>20</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9963831901550293</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>AARON.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>118.0800018310547</v>
+      </c>
+      <c r="D273" t="n">
+        <v>118.0800018310547</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.981620728969574</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>GEEKAYWIRE.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>27.19000053405762</v>
+      </c>
+      <c r="D274" t="n">
+        <v>27.19000053405762</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9767982959747314</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HDFCMID150.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>20.81999969482422</v>
+      </c>
+      <c r="D275" t="n">
+        <v>20.81999969482422</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9543577432632446</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>KOTHARIPRO.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>59.04999923706055</v>
+      </c>
+      <c r="D276" t="n">
+        <v>59.04999923706055</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.8663833737373352</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>BBTCL.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>198.3999938964844</v>
+      </c>
+      <c r="D277" t="n">
+        <v>198.3999938964844</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.8314144611358643</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>MANCREDIT.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>205.3500061035156</v>
+      </c>
+      <c r="D278" t="n">
+        <v>205.3500061035156</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.8004423975944519</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SRF.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2305.300048828125</v>
+      </c>
+      <c r="D279" t="n">
+        <v>2305.300048828125</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.7832119464874268</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>GLOBALVECT.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>111.5999984741211</v>
+      </c>
+      <c r="D280" t="n">
+        <v>111.5999984741211</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.7818477749824524</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SILVERTUC.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>123.7099990844727</v>
+      </c>
+      <c r="D281" t="n">
+        <v>123.7099990844727</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.680140495300293</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>20</v>
       </c>
       <c r="D272" t="n">
-        <v>20</v>
+        <v>20.70000076293945</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>0.7000007629394531</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>3.500003814697265</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>118.0800018310547</v>
       </c>
       <c r="D273" t="n">
-        <v>118.0800018310547</v>
+        <v>118.6699981689453</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>0.5899963378906108</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>0.4996581374844148</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>27.19000053405762</v>
       </c>
       <c r="D274" t="n">
-        <v>27.19000053405762</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>0.1999988555908168</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>0.7355603224071379</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>20.81999969482422</v>
       </c>
       <c r="D275" t="n">
-        <v>20.81999969482422</v>
+        <v>20.80999946594238</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>-0.01000022888183594</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>-0.04803183971382075</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>59.04999923706055</v>
       </c>
       <c r="D276" t="n">
-        <v>59.04999923706055</v>
+        <v>58.2599983215332</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>-0.7900009155273438</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>-1.337850847983634</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>198.3999938964844</v>
       </c>
       <c r="D277" t="n">
-        <v>198.3999938964844</v>
+        <v>202</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>3.600006103515597</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>1.81451926122231</v>
       </c>
     </row>
     <row r="278">
@@ -11760,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>1.384061776753822e-14</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>2305.300048828125</v>
       </c>
       <c r="D279" t="n">
-        <v>2305.300048828125</v>
+        <v>2305.800048828125</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>0.02168915062723266</v>
       </c>
     </row>
     <row r="280">
@@ -11871,28 +11871,32 @@
         <v>123.7099990844727</v>
       </c>
       <c r="D281" t="n">
-        <v>123.7099990844727</v>
+        <v>123.0899963378906</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>123.0899963378906</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>-0.6200027465820739</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H281" t="n">
         <v>0.680140495300293</v>
       </c>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>-0.5011743199179223</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11559,13 +11559,13 @@
         <v>118.0800018310547</v>
       </c>
       <c r="D273" t="n">
-        <v>118.6699981689453</v>
+        <v>119.9599990844727</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.5899963378906108</v>
+        <v>1.879997253417955</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.4996581374844148</v>
+        <v>1.592138570685151</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>27.19000053405762</v>
       </c>
       <c r="D274" t="n">
-        <v>27.38999938964844</v>
+        <v>27.3799991607666</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.1999988555908168</v>
+        <v>0.1899986267089808</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.7355603224071379</v>
+        <v>0.698781254053278</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>20.81999969482422</v>
       </c>
       <c r="D275" t="n">
-        <v>20.80999946594238</v>
+        <v>20.81999969482422</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.01000022888183594</v>
+        <v>0</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>-0.04803183971382075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -11754,13 +11754,13 @@
         <v>205.3500061035156</v>
       </c>
       <c r="D278" t="n">
-        <v>205.3500061035156</v>
+        <v>205.4900054931641</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0.1399993896484659</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>1.384061776753822e-14</v>
+        <v>0.06817598514114148</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>2305.300048828125</v>
       </c>
       <c r="D279" t="n">
-        <v>2305.800048828125</v>
+        <v>2307.5</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.5</v>
+        <v>2.199951171875</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.02168915062723266</v>
+        <v>0.09543014467870775</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>111.5999984741211</v>
       </c>
       <c r="D280" t="n">
-        <v>111.5999984741211</v>
+        <v>111.9899978637695</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>0.3899993896484375</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>0.3494618234594998</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>20</v>
       </c>
       <c r="D272" t="n">
-        <v>20.70000076293945</v>
+        <v>20.45000076293945</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.7000007629394531</v>
+        <v>0.4500007629394531</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>3.500003814697265</v>
+        <v>2.250003814697266</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>118.0800018310547</v>
       </c>
       <c r="D273" t="n">
-        <v>119.9599990844727</v>
+        <v>119.370002746582</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>1.879997253417955</v>
+        <v>1.29000091552733</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>1.592138570685151</v>
+        <v>1.092480433200724</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>27.19000053405762</v>
       </c>
       <c r="D274" t="n">
-        <v>27.3799991607666</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.1899986267089808</v>
+        <v>0.3599987030029261</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.698781254053278</v>
+        <v>1.324011386288865</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>20.81999969482422</v>
       </c>
       <c r="D275" t="n">
-        <v>20.81999969482422</v>
+        <v>20.84000015258789</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>0.02000045776367188</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>0.0960636794276415</v>
       </c>
     </row>
     <row r="276">
@@ -11793,13 +11793,13 @@
         <v>2305.300048828125</v>
       </c>
       <c r="D279" t="n">
-        <v>2307.5</v>
+        <v>2306.199951171875</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>2.199951171875</v>
+        <v>0.89990234375</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.09543014467870775</v>
+        <v>0.0390362349667869</v>
       </c>
     </row>
     <row r="280">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11598,13 +11598,13 @@
         <v>27.19000053405762</v>
       </c>
       <c r="D274" t="n">
-        <v>27.54999923706055</v>
+        <v>27.15999984741211</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.3599987030029261</v>
+        <v>-0.03000068664551137</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>1.324011386288865</v>
+        <v>-0.1103372050615929</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>20.81999969482422</v>
       </c>
       <c r="D275" t="n">
-        <v>20.84000015258789</v>
+        <v>20.82999992370605</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.02000045776367188</v>
+        <v>0.01000022888183594</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.0960636794276415</v>
+        <v>0.04803183971382075</v>
       </c>
     </row>
     <row r="276">
@@ -11754,13 +11754,13 @@
         <v>205.3500061035156</v>
       </c>
       <c r="D278" t="n">
-        <v>205.4900054931641</v>
+        <v>205.1999969482422</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.1399993896484659</v>
+        <v>-0.1500091552734091</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.06817598514114148</v>
+        <v>-0.07305047519589089</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>2305.300048828125</v>
       </c>
       <c r="D279" t="n">
-        <v>2306.199951171875</v>
+        <v>2304.5</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.89990234375</v>
+        <v>-0.800048828125</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0.0390362349667869</v>
+        <v>-0.03470475908468819</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>111.5999984741211</v>
       </c>
       <c r="D280" t="n">
-        <v>111.9899978637695</v>
+        <v>111.1999969482422</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.3899993896484375</v>
+        <v>-0.4000015258789062</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.3494618234594998</v>
+        <v>-0.358424311243752</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>20</v>
       </c>
       <c r="D272" t="n">
-        <v>20.45000076293945</v>
+        <v>20.04999923706055</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.4500007629394531</v>
+        <v>0.04999923706054688</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>2.250003814697266</v>
+        <v>0.2499961853027344</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>118.0800018310547</v>
       </c>
       <c r="D273" t="n">
-        <v>119.370002746582</v>
+        <v>119</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>1.29000091552733</v>
+        <v>0.9199981689452983</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>1.092480433200724</v>
+        <v>0.7791312285560461</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>27.19000053405762</v>
       </c>
       <c r="D274" t="n">
-        <v>27.15999984741211</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.03000068664551137</v>
+        <v>0.1999988555908168</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.1103372050615929</v>
+        <v>0.7355603224071379</v>
       </c>
     </row>
     <row r="275">
@@ -11715,13 +11715,13 @@
         <v>198.3999938964844</v>
       </c>
       <c r="D277" t="n">
-        <v>202</v>
+        <v>198.0200042724609</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>3.600006103515597</v>
+        <v>-0.3799896240234659</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>1.81451926122231</v>
+        <v>-0.1915270341297119</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>205.3500061035156</v>
       </c>
       <c r="D278" t="n">
-        <v>205.1999969482422</v>
+        <v>203.6300048828125</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.1500091552734091</v>
+        <v>-1.720001220703097</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>-0.07305047519589089</v>
+        <v>-0.8375949206624591</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>2305.300048828125</v>
       </c>
       <c r="D279" t="n">
-        <v>2304.5</v>
+        <v>2303.199951171875</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.800048828125</v>
+        <v>-2.10009765625</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>-0.03470475908468819</v>
+        <v>-0.09109866879660904</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>111.5999984741211</v>
       </c>
       <c r="D280" t="n">
-        <v>111.1999969482422</v>
+        <v>112.4000015258789</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.4000015258789062</v>
+        <v>0.8000030517578125</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>-0.358424311243752</v>
+        <v>0.7168486224875039</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,400 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>NAGREEKEXP.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>20</v>
-      </c>
-      <c r="D272" t="n">
-        <v>20.04999923706055</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>0.04999923706054688</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9963831901550293</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.2499961853027344</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>AARON.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>118.0800018310547</v>
-      </c>
-      <c r="D273" t="n">
-        <v>119</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>0.9199981689452983</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.981620728969574</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0.7791312285560461</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>GEEKAYWIRE.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>27.19000053405762</v>
-      </c>
-      <c r="D274" t="n">
-        <v>27.38999938964844</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0.1999988555908168</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9767982959747314</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0.7355603224071379</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>HDFCMID150.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>20.81999969482422</v>
-      </c>
-      <c r="D275" t="n">
-        <v>20.82999992370605</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>0.01000022888183594</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9543577432632446</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0.04803183971382075</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>KOTHARIPRO.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>59.04999923706055</v>
-      </c>
-      <c r="D276" t="n">
-        <v>58.2599983215332</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>-0.7900009155273438</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.8663833737373352</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>-1.337850847983634</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>BBTCL.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>198.3999938964844</v>
-      </c>
-      <c r="D277" t="n">
-        <v>198.0200042724609</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>-0.3799896240234659</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.8314144611358643</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>-0.1915270341297119</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>MANCREDIT.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>205.3500061035156</v>
-      </c>
-      <c r="D278" t="n">
-        <v>203.6300048828125</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>-1.720001220703097</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.8004423975944519</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>-0.8375949206624591</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>SRF.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>2305.300048828125</v>
-      </c>
-      <c r="D279" t="n">
-        <v>2303.199951171875</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>-2.10009765625</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.7832119464874268</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>-0.09109866879660904</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>GLOBALVECT.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>111.5999984741211</v>
-      </c>
-      <c r="D280" t="n">
-        <v>112.4000015258789</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0.8000030517578125</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.7818477749824524</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0.7168486224875039</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>SILVERTUC.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>123.7099990844727</v>
-      </c>
-      <c r="D281" t="n">
-        <v>123.0899963378906</v>
-      </c>
-      <c r="E281" t="n">
-        <v>123.0899963378906</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-0.6200027465820739</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.680140495300293</v>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>-0.5011743199179223</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>DIGIDRIVE.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>17.29999923706055</v>
+      </c>
+      <c r="D272" t="n">
+        <v>17.29999923706055</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9871108531951904</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>NILAINFRA.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="D273" t="n">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9812927842140198</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>GOACARBON.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>391.2999877929688</v>
+      </c>
+      <c r="D274" t="n">
+        <v>391.2999877929688</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9465465545654297</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>PALASHSECU.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>78.44999694824219</v>
+      </c>
+      <c r="D275" t="n">
+        <v>78.44999694824219</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9391481876373291</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>186.7899932861328</v>
+      </c>
+      <c r="D276" t="n">
+        <v>186.7899932861328</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.9191054105758667</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>VIKASECO.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>0.9900000095367432</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.9900000095367432</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.9165941476821899</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>MCLEODRUSS.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>46.15000152587891</v>
+      </c>
+      <c r="D278" t="n">
+        <v>46.15000152587891</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.9051005840301514</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>GEOJITFSL.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>67.80000305175781</v>
+      </c>
+      <c r="D279" t="n">
+        <v>67.80000305175781</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.8558327555656433</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>TGBHOTELS.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>8.699999809265137</v>
+      </c>
+      <c r="D280" t="n">
+        <v>8.699999809265137</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.819219708442688</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>BAJAJHFL.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>79</v>
+      </c>
+      <c r="D281" t="n">
+        <v>79</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.7955463528633118</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,396 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>DIGIDRIVE.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>17.29999923706055</v>
-      </c>
-      <c r="D272" t="n">
-        <v>17.29999923706055</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9871108531951904</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>NILAINFRA.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>6.079999923706055</v>
-      </c>
-      <c r="D273" t="n">
-        <v>6.079999923706055</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9812927842140198</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>GOACARBON.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>391.2999877929688</v>
-      </c>
-      <c r="D274" t="n">
-        <v>391.2999877929688</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9465465545654297</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>PALASHSECU.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>78.44999694824219</v>
-      </c>
-      <c r="D275" t="n">
-        <v>78.44999694824219</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9391481876373291</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>KRONOX.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>186.7899932861328</v>
-      </c>
-      <c r="D276" t="n">
-        <v>186.7899932861328</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.9191054105758667</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>VIKASECO.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>0.9900000095367432</v>
-      </c>
-      <c r="D277" t="n">
-        <v>0.9900000095367432</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.9165941476821899</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>MCLEODRUSS.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>46.15000152587891</v>
-      </c>
-      <c r="D278" t="n">
-        <v>46.15000152587891</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.9051005840301514</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>GEOJITFSL.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>67.80000305175781</v>
-      </c>
-      <c r="D279" t="n">
-        <v>67.80000305175781</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.8558327555656433</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>TGBHOTELS.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>8.699999809265137</v>
-      </c>
-      <c r="D280" t="n">
-        <v>8.699999809265137</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.819219708442688</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>BAJAJHFL.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>79</v>
-      </c>
-      <c r="D281" t="n">
-        <v>79</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.7955463528633118</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,6 +11505,396 @@
         <v>5.053057190453876</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>NAVKARCORP.NS</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>75.59999847412109</v>
+      </c>
+      <c r="D272" t="n">
+        <v>75.59999847412109</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9936648607254028</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>HESTERBIO.NS</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2136</v>
+      </c>
+      <c r="D273" t="n">
+        <v>2136</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9841788411140442</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>SILINV.NS</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>427.25</v>
+      </c>
+      <c r="D274" t="n">
+        <v>427.25</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9830631017684937</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>EMSLIMITED.NS</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>290.75</v>
+      </c>
+      <c r="D275" t="n">
+        <v>290.75</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0.9640476703643799</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ACE.NS</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>1034.300048828125</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1034.300048828125</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.9519619941711426</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>RPEL.NS</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>1724</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1724</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0.9405257105827332</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>OSWALPUMPS.NS</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>210.1499938964844</v>
+      </c>
+      <c r="D278" t="n">
+        <v>210.1499938964844</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0.9243459701538086</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>BDL.NS</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>999</v>
+      </c>
+      <c r="D279" t="n">
+        <v>999</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0.9138988256454468</v>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ARVINDFASN.NS</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>364.8999938964844</v>
+      </c>
+      <c r="D280" t="n">
+        <v>364.8999938964844</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0.8941214680671692</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>NAGREEKEXP.NS</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>20.3700008392334</v>
+      </c>
+      <c r="D281" t="n">
+        <v>20.3700008392334</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0.8931605815887451</v>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>75.59999847412109</v>
       </c>
       <c r="D272" t="n">
-        <v>75.59999847412109</v>
+        <v>76.38999938964844</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>0.7900009155273438</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>1.044974777079886</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>2136</v>
       </c>
       <c r="D273" t="n">
-        <v>2136</v>
+        <v>2133.89990234375</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>-2.10009765625</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>-0.09831917866338952</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>427.25</v>
       </c>
       <c r="D274" t="n">
-        <v>427.25</v>
+        <v>425</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>-0.5266237565827969</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>290.75</v>
       </c>
       <c r="D275" t="n">
-        <v>290.75</v>
+        <v>291.3999938964844</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>0.649993896484375</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>0.2235576600118228</v>
       </c>
     </row>
     <row r="276">
@@ -11676,13 +11676,13 @@
         <v>1034.300048828125</v>
       </c>
       <c r="D276" t="n">
-        <v>1034.300048828125</v>
+        <v>1036.099975585938</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>1.7999267578125</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>0.1740236558870745</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>1724</v>
       </c>
       <c r="D277" t="n">
-        <v>1724</v>
+        <v>1720.099975585938</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>-3.9000244140625</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>-0.2262195135767111</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>210.1499938964844</v>
       </c>
       <c r="D278" t="n">
-        <v>210.1499938964844</v>
+        <v>211.6999969482422</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>1.550003051757784</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>0.73756987712371</v>
       </c>
     </row>
     <row r="279">
@@ -11793,13 +11793,13 @@
         <v>999</v>
       </c>
       <c r="D279" t="n">
-        <v>999</v>
+        <v>999.4000244140625</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>0.4000244140625</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>0.04004248389014014</v>
       </c>
     </row>
     <row r="280">
@@ -11832,13 +11832,13 @@
         <v>364.8999938964844</v>
       </c>
       <c r="D280" t="n">
-        <v>364.8999938964844</v>
+        <v>366</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>1.100006103515625</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>0.3014541304233831</v>
       </c>
     </row>
     <row r="281">
@@ -11871,13 +11871,13 @@
         <v>20.3700008392334</v>
       </c>
       <c r="D281" t="n">
-        <v>20.3700008392334</v>
+        <v>20.35000038146973</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>-0.02000045776367188</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>-0.09818584653737583</v>
       </c>
     </row>
   </sheetData>

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>75.59999847412109</v>
       </c>
       <c r="D272" t="n">
-        <v>76.38999938964844</v>
+        <v>76.34999847412109</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.7900009155273438</v>
+        <v>0.75</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>1.044974777079886</v>
+        <v>0.9920635120868887</v>
       </c>
     </row>
     <row r="273">
@@ -11676,13 +11676,13 @@
         <v>1034.300048828125</v>
       </c>
       <c r="D276" t="n">
-        <v>1036.099975585938</v>
+        <v>1035.5</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>1.7999267578125</v>
+        <v>1.199951171875</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>0.1740236558870745</v>
+        <v>0.116015770591383</v>
       </c>
     </row>
     <row r="277">
@@ -11715,13 +11715,13 @@
         <v>1724</v>
       </c>
       <c r="D277" t="n">
-        <v>1720.099975585938</v>
+        <v>1720.300048828125</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-3.9000244140625</v>
+        <v>-3.699951171875</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.2262195135767111</v>
+        <v>-0.2146143371157193</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>210.1499938964844</v>
       </c>
       <c r="D278" t="n">
-        <v>211.6999969482422</v>
+        <v>211.1999969482422</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>1.550003051757784</v>
+        <v>1.050003051757784</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.73756987712371</v>
+        <v>0.4996445787550173</v>
       </c>
     </row>
     <row r="279">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -11520,13 +11520,13 @@
         <v>75.59999847412109</v>
       </c>
       <c r="D272" t="n">
-        <v>76.34999847412109</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.75</v>
+        <v>0.7399978637695312</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.9920635120868887</v>
+        <v>0.9788331728906616</v>
       </c>
     </row>
     <row r="273">
@@ -11559,13 +11559,13 @@
         <v>2136</v>
       </c>
       <c r="D273" t="n">
-        <v>2133.89990234375</v>
+        <v>2168</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>-2.10009765625</v>
+        <v>32</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>-0.09831917866338952</v>
+        <v>1.49812734082397</v>
       </c>
     </row>
     <row r="274">
@@ -11598,13 +11598,13 @@
         <v>427.25</v>
       </c>
       <c r="D274" t="n">
-        <v>425</v>
+        <v>424.7999877929688</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>-2.25</v>
+        <v>-2.45001220703125</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>-0.5266237565827969</v>
+        <v>-0.5734376142846694</v>
       </c>
     </row>
     <row r="275">
@@ -11637,13 +11637,13 @@
         <v>290.75</v>
       </c>
       <c r="D275" t="n">
-        <v>291.3999938964844</v>
+        <v>292.8500061035156</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.649993896484375</v>
+        <v>2.100006103515625</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>0.2235576600118228</v>
+        <v>0.7222720906330611</v>
       </c>
     </row>
     <row r="276">
@@ -11715,13 +11715,13 @@
         <v>1724</v>
       </c>
       <c r="D277" t="n">
-        <v>1720.300048828125</v>
+        <v>1759.099975585938</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>-3.699951171875</v>
+        <v>35.0999755859375</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>-0.2146143371157193</v>
+        <v>2.035961460901247</v>
       </c>
     </row>
     <row r="278">
@@ -11754,13 +11754,13 @@
         <v>210.1499938964844</v>
       </c>
       <c r="D278" t="n">
-        <v>211.1999969482422</v>
+        <v>211</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>1.050003051757784</v>
+        <v>0.8500061035155966</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
-        <v>0.4996445787550173</v>
+        <v>0.4044759115883164</v>
       </c>
     </row>
     <row r="279">
@@ -11832,13 +11832,13 @@
         <v>364.8999938964844</v>
       </c>
       <c r="D280" t="n">
-        <v>366</v>
+        <v>366.1499938964844</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>1.100006103515625</v>
+        <v>1.25</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
-        <v>0.3014541304233831</v>
+        <v>0.3425596111011728</v>
       </c>
     </row>
     <row r="281">

--- a/trading_log.xlsx
+++ b/trading_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,396 +11505,6 @@
         <v>5.053057190453876</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>NAVKARCORP.NS</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>75.59999847412109</v>
-      </c>
-      <c r="D272" t="n">
-        <v>76.33999633789062</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>0.7399978637695312</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>0.9936648607254028</v>
-      </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="n">
-        <v>0.9788331728906616</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>HESTERBIO.NS</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>2136</v>
-      </c>
-      <c r="D273" t="n">
-        <v>2168</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>32</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>0.9841788411140442</v>
-      </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="n">
-        <v>1.49812734082397</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>SILINV.NS</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>427.25</v>
-      </c>
-      <c r="D274" t="n">
-        <v>424.7999877929688</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>-2.45001220703125</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>0.9830631017684937</v>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="n">
-        <v>-0.5734376142846694</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>EMSLIMITED.NS</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>290.75</v>
-      </c>
-      <c r="D275" t="n">
-        <v>292.8500061035156</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>2.100006103515625</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>0.9640476703643799</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="n">
-        <v>0.7222720906330611</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>ACE.NS</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>1034.300048828125</v>
-      </c>
-      <c r="D276" t="n">
-        <v>1035.5</v>
-      </c>
-      <c r="E276" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" t="n">
-        <v>1.199951171875</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>0.9519619941711426</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="n">
-        <v>0.116015770591383</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>RPEL.NS</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>1724</v>
-      </c>
-      <c r="D277" t="n">
-        <v>1759.099975585938</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>35.0999755859375</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>0.9405257105827332</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="n">
-        <v>2.035961460901247</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>OSWALPUMPS.NS</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>210.1499938964844</v>
-      </c>
-      <c r="D278" t="n">
-        <v>211</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0.8500061035155966</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>0.9243459701538086</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="n">
-        <v>0.4044759115883164</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>BDL.NS</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>999</v>
-      </c>
-      <c r="D279" t="n">
-        <v>999.4000244140625</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0.4000244140625</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>0.9138988256454468</v>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="n">
-        <v>0.04004248389014014</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>ARVINDFASN.NS</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>364.8999938964844</v>
-      </c>
-      <c r="D280" t="n">
-        <v>366.1499938964844</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>0.8941214680671692</v>
-      </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="n">
-        <v>0.3425596111011728</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>NAGREEKEXP.NS</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>20.3700008392334</v>
-      </c>
-      <c r="D281" t="n">
-        <v>20.35000038146973</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-0.02000045776367188</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>0.8931605815887451</v>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="n">
-        <v>-0.09818584653737583</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
